--- a/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
+++ b/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T666"/>
+  <dimension ref="A1:T671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69209,6 +69209,545 @@
         </is>
       </c>
     </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>69462cb0000000001b0250e2</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69462cb0000000001b0250e2?xsec_token=ABfAKOv9KzAlnD02ddaivXvWpZ0WwLhDXjPe2BwC8skmk=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>简单点</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>我平安姑娘A20％
+平安姑娘tvb10％
+那么≈30％
+格局掉10％tvb后
+30％≈格局掉了3/1了
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>2081</t>
+        </is>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="L667" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="M667" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N667" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O667" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P667" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112034/8fe06beda8f2124ec05f7c1184e89cd3/1040g00831qa6dv9pga5g4a7r1e8cb33vk4vb088!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q667" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R667" t="inlineStr">
+        <is>
+          <t>2025-12-20 12:57:20</t>
+        </is>
+      </c>
+      <c r="S667" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T667" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>694626a1000000001b023e32</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/694626a1000000001b023e32?xsec_token=ABfAKOv9KzAlnD02ddaivXvRS0LXe637eBtwvvKrDCVUo=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>很多事真的不必勉强
+认知 资源 决定以后结果
+变异电是需要用以后来兑现的
+so 我认为好 但依然不推荐
+很多人下面也别唧唧歪歪
+你照照镜子 没人硬塞给你
+你是谁 其实我根本不认识你
+所以不要搞的像真的一样
+一句句为什么 一句句要我分析
+我分析给毛线给你听要么</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>2366</t>
+        </is>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="M668" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N668" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O668" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P668" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112040/77527399bb1401c02b909c91d6a45b20/1040g00831qa6dv9pga6g4a7r1e8cb33vmi8d66g!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q668" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R668" t="inlineStr">
+        <is>
+          <t>2025-12-20 12:31:29</t>
+        </is>
+      </c>
+      <c r="S668" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T668" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>6945e7e9000000000d03d348</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6945e7e9000000000d03d348?xsec_token=ABEi58ShmTcQxkgcxX0gUzNXSFkgGttjX6857ZKWzbJcQ=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>好运一直眷顾你？ 呵呵 呵呵呵 呵呵呵呵</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>很奇怪的逻辑
+凭什么很多人就点点赞
+夸几句 不学习 不提高
+就可以心安理得的免费获取 你们以为的财富密码？
+人不是要靠自己吗？
+真把自己当天选之子了？
+什么我只要每年10％就满足了  说这话时 托下巴了吗</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>2606</t>
+        </is>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="M669" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="N669" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O669" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P669" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112045/e02d2f07a3bbc1aa8d5de1ad7705f0d0/1040g00831q9ug5emga104a7r1e8cb33v4c35mp8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q669" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R669" t="inlineStr">
+        <is>
+          <t>2025-12-20 08:03:53</t>
+        </is>
+      </c>
+      <c r="S669" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T669" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>6945e57b000000000d00f1e1</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6945e57b000000000d00f1e1?xsec_token=ABEi58ShmTcQxkgcxX0gUzNeEivOriL25rvHXBjHjdloA=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>赠品＋业绩涨  A＋
+赠品＋业绩横  A-
+赠品＋业绩跌  B
+赠品＋ 业绩差 B-
+没赠品＋强成长B＋
+没赠品＋业绩横[汗颜R]
+没赠品＋业绩差[汗颜R][汗颜R][汗颜R]</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>2520</t>
+        </is>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>728</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="M670" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="N670" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O670" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P670" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112051/a4acd970b7ad4f6e6d43050c3a9cb7a6/1040g00831q9ug5emga5g4a7r1e8cb33vv0u8ibg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q670" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R670" t="inlineStr">
+        <is>
+          <t>2025-12-20 07:53:31</t>
+        </is>
+      </c>
+      <c r="S670" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T670" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>69457e15000000000d036f28</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69457e15000000000d036f28?xsec_token=ABEi58ShmTcQxkgcxX0gUzNTF4gNt0Dq1ykFdjK1t4uog=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>一年啊又一年</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>2023年初是四大行
+2024年是股份制
+2025年是保险
+2026年是 券商＋变异电#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>4078</t>
+        </is>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>1945</t>
+        </is>
+      </c>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="M671" t="inlineStr">
+        <is>
+          <t>458</t>
+        </is>
+      </c>
+      <c r="N671" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O671" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P671" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112057/68778836ee53a9fb9968f64fc9594983/1040g00831q92gsko0a1g4a7r1e8cb33vbbtud9o!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q671" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R671" t="inlineStr">
+        <is>
+          <t>2025-12-20 00:32:21</t>
+        </is>
+      </c>
+      <c r="S671" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T671" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
+++ b/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T671"/>
+  <dimension ref="A1:T683"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69748,6 +69748,1265 @@
         </is>
       </c>
     </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>69453095000000001b02307b</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69453095000000001b02307b?xsec_token=ABEi58ShmTcQxkgcxX0gUzNVbs0gC8nyzuiCjCAPQuubU=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>投资
+真的要老老实实
+看看平什么潭水的
+今晚睡不着了
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="M672" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="N672" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O672" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P672" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112102/db4970117559fb3dfbcf6552ce5a7366/1040g00831q92gsko0a4g4a7r1e8cb33v3tgtc58!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q672" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R672" t="inlineStr">
+        <is>
+          <t>2025-12-19 19:01:41</t>
+        </is>
+      </c>
+      <c r="S672" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T672" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>694526ec0000000019026b34</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/694526ec0000000019026b34?xsec_token=ABEi58ShmTcQxkgcxX0gUzNcX14DqgsStecTLE_pv2iQk=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>收益差 晚上只能空喝了</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>[泪崩R][泪崩R][泪崩R]#招商银行[话题]#</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>1610</t>
+        </is>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="M673" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N673" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O673" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P673" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112108/3ad83a73c08967704193944feabb37d3/notes_pre_post/1040g3k031q9771vo7u604a7r1e8cb33vku33gao!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q673" t="inlineStr">
+        <is>
+          <t>['招商银行']</t>
+        </is>
+      </c>
+      <c r="R673" t="inlineStr">
+        <is>
+          <t>2025-12-19 18:20:28</t>
+        </is>
+      </c>
+      <c r="S673" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T673" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>6945004e000000000d0379ec</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6945004e000000000d0379ec?xsec_token=ABEi58ShmTcQxkgcxX0gUzNaOYdGjMa2CAcmWVCItRHPs=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>仙境好啊</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>冷知识
+仙境仓并不意味着空着浪费
+假设渣猫赠品5
+周中to周下
+41 40 39 38 37吧？赠品越来越高 平均格局
+37 38 39 40 41
+滚一圈 一次1w份额
+一次一万金币 YYdssss</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>2514</t>
+        </is>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="M674" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="N674" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O674" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P674" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112115/4a31ffe78b6f63673313552c809b72f4/1040g00831q92gsko0a6g4a7r1e8cb33vgfi12oo!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q674" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R674" t="inlineStr">
+        <is>
+          <t>2025-12-19 15:35:42</t>
+        </is>
+      </c>
+      <c r="S674" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T674" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>6944f8f8000000001b0312e4</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6944f8f8000000001b0312e4?xsec_token=ABA_dJKonpO0UDUvXFbSA0n_ijafQyQlk85TIJhT-Jz3U=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>仙境15％
+我很快乐
+#快乐似神仙[话题]# #寻找快乐能量[话题]#</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>1740</t>
+        </is>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="M675" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N675" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O675" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P675" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112121/ff28b69dad61835674def53e3e79ba39/1040g00831q8pv99qng3g4a7r1e8cb33v0qidto8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q675" t="inlineStr">
+        <is>
+          <t>['快乐似神仙', '寻找快乐能量']</t>
+        </is>
+      </c>
+      <c r="R675" t="inlineStr">
+        <is>
+          <t>2025-12-19 15:04:24</t>
+        </is>
+      </c>
+      <c r="S675" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T675" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>6944f2be000000001b021729</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6944f2be000000001b021729?xsec_token=ABA_dJKonpO0UDUvXFbSA0n4tm1rJINihUUYdgdzFKbSg=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>想抵抗下市场#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>1614</t>
+        </is>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="M676" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N676" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O676" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P676" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112126/0db8a6439ef87af4cc4bbcb3f1e526aa/1040g00831q8pv99qng4g4a7r1e8cb33vgrk5ro0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q676" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R676" t="inlineStr">
+        <is>
+          <t>2025-12-19 14:37:50</t>
+        </is>
+      </c>
+      <c r="S676" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T676" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>6944d1c6000000000d037487</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6944d1c6000000000d037487?xsec_token=ABA_dJKonpO0UDUvXFbSA0n7hB-9UilzcKQUhwDZlliqQ=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>收益差…哎 中午就这个吧</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>[泪崩R][泪崩R]#中国核电[话题]#
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>1669</t>
+        </is>
+      </c>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>457</t>
+        </is>
+      </c>
+      <c r="M677" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N677" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O677" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P677" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112133/365e27e950eb5a6b05f86ba279272be3/notes_pre_post/1040g3k031q8sr7ta006g4a7r1e8cb33vcnab9d8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q677" t="inlineStr">
+        <is>
+          <t>['中国核电', '我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R677" t="inlineStr">
+        <is>
+          <t>2025-12-19 12:17:10</t>
+        </is>
+      </c>
+      <c r="S677" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T677" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>6944ba3a000000000d03d4b8</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6944ba3a000000000d03d4b8?xsec_token=ABA_dJKonpO0UDUvXFbSA0n3IvlGCb9ReKNhjbIvRP8_c=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>三哥A要周上咯
+懂得噢你们
+不用我多说什么</t>
+        </is>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="M678" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N678" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O678" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P678" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112138/8f191bc829e23dbc544f6b1d19a65268/1040g00831q8pv99qng6g4a7r1e8cb33v2hr8qog!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q678" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R678" t="inlineStr">
+        <is>
+          <t>2025-12-19 10:36:42</t>
+        </is>
+      </c>
+      <c r="S678" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T678" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>6944b4aa000000001b023934</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6944b4aa000000001b023934?xsec_token=ABA_dJKonpO0UDUvXFbSA0n0dpTkFTBmIScytwkCm7JIQ=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>信大牛牛市
+就信
+券商会来
+但还是要风险提示
+我是做好亏金币的准备
+你们别学我  让我一个人难受😣</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>2157</t>
+        </is>
+      </c>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="L679" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="M679" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N679" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O679" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P679" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112144/39d77340166e872e95b11101d5ed5c75/1040g00831q8ke9lqnu0g4a7r1e8cb33vl4jh6lg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q679" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R679" t="inlineStr">
+        <is>
+          <t>2025-12-19 10:12:58</t>
+        </is>
+      </c>
+      <c r="S679" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T679" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>6944ac9d000000000d035fdc</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6944ac9d000000000d035fdc?xsec_token=ABA_dJKonpO0UDUvXFbSA0n8Q-7qovEXghCQiNusZU2yk=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>多少次 迎着冷眼与嘲笑
+从没有放弃过心中的理想
+一刹那恍惚 若有所失的感觉
+不知不觉已变淡
+谁明白我
+原谅我这一生不羁放纵爱自由
+也会怕有一天会跌倒
+背弃了理想 谁人都可以</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="M680" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N680" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O680" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P680" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112150/4d4ef5d39d7332f8ec24bb2e16de4770/1040g00831q8ke9lqnu1g4a7r1e8cb33vrb7ufb0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q680" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R680" t="inlineStr">
+        <is>
+          <t>2025-12-19 09:38:37</t>
+        </is>
+      </c>
+      <c r="S680" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T680" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>6944a2b9000000000d03e515</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6944a2b9000000000d03e515?xsec_token=ABA_dJKonpO0UDUvXFbSA0n4bo6ilnpbwOEZ6C_G8Mnvw=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>冷知识
+连你都知道业绩要释放 对 别转头 说的就是你 你！！你！！
+连你都知道了 意味着什么
+你以为的 跟 实际的
+是有区别的</t>
+        </is>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>1891</t>
+        </is>
+      </c>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="M681" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N681" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O681" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P681" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112156/026e9023901ae5bfc800b4fffe4070f8/1040g00831q8ke9lqnu204a7r1e8cb33vvr8fpg8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q681" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R681" t="inlineStr">
+        <is>
+          <t>2025-12-19 08:56:25</t>
+        </is>
+      </c>
+      <c r="S681" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T681" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>69449dc2000000001b021a6a</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69449dc2000000001b021a6a?xsec_token=ABA_dJKonpO0UDUvXFbSA0n69TISdpDrG3yjUOJLtrbFg=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>再复习一次</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>2123</t>
+        </is>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="M682" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="N682" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O682" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P682" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112202/ce2f1d8559eb2a09c28ed29748e09221/notes_pre_post/1040g3k031q8mg2q7g0604a7r1e8cb33vaf078m0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q682" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R682" t="inlineStr">
+        <is>
+          <t>2025-12-19 08:35:14</t>
+        </is>
+      </c>
+      <c r="S682" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T682" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>6944947f000000001b0279a7</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6944947f000000001b0279a7?xsec_token=ABA_dJKonpO0UDUvXFbSA0n-7cIu1bbbPbKlpBPgnhjNQ=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>冷知识
+平安姑娘
+赠品3.75了
+#保护自己的利益[话题]#</t>
+        </is>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>2095</t>
+        </is>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="M683" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="N683" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O683" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P683" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112208/8a49d4488ad2fb0831e002934a6dcd2b/1040g00831q8ke9lqnu6g4a7r1e8cb33vcr72a1g!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q683" t="inlineStr">
+        <is>
+          <t>['保护自己的利益']</t>
+        </is>
+      </c>
+      <c r="R683" t="inlineStr">
+        <is>
+          <t>2025-12-19 07:55:43</t>
+        </is>
+      </c>
+      <c r="S683" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T683" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
+++ b/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T683"/>
+  <dimension ref="A1:T743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71007,6 +71007,6293 @@
         </is>
       </c>
     </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>69441aa9000000000d0394a3</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69441aa9000000000d0394a3?xsec_token=ABA_dJKonpO0UDUvXFbSA0nz6g0luINFSH765WswZyzEI=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>想回到过去</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>回想2007年
+我一身是胆 七进七出
+每次都游刃有余的冲进去取金币   出来
+再冲进去取金币 出来
+再进去取金币 出来
+再…
+2026年了  我已老矣… 我……我还想再来一次
+富贵七进七出大法
+不知 时间的发动机里 还剩余多少油
+我觉得 我可以的  我想对抗下年龄 时间
+实在不行 保本出就好了
+#过去的回忆[话题]# #怀念过去的时光[话题]# #你想过要回到过去吗[话题]# #曾经的记忆[话题]# #要是能回到过去就好了[话题]#</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>2160</t>
+        </is>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="M684" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N684" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O684" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P684" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112214/00440cb459a55b815a9965201365d29a/notes_pre_post/1040g3k031q7vrqhlno604a7r1e8cb33vmk16900!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q684" t="inlineStr">
+        <is>
+          <t>['过去的回忆', '怀念过去的时光', '你想过要回到过去吗', '曾经的记忆', '要是能回到过去就好了']</t>
+        </is>
+      </c>
+      <c r="R684" t="inlineStr">
+        <is>
+          <t>2025-12-18 23:15:53</t>
+        </is>
+      </c>
+      <c r="S684" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T684" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>6944006d000000000d00e8cd</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6944006d000000000d00e8cd?xsec_token=ABA_dJKonpO0UDUvXFbSA0n2GSM0Zmap4wsif3mGPT78s=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>再说一遍
+我不是什么你们说的
+吃赠品 赞份额的
+我是[石化R][石化R][石化R]
+我说吃赠品其实只是口号</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="M685" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N685" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O685" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P685" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112220/d97db892edc27cc084d9e0bbed1bb99a/1040g00831q7vr8f27g304a7r1e8cb33vfb4uogg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q685" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R685" t="inlineStr">
+        <is>
+          <t>2025-12-18 21:23:57</t>
+        </is>
+      </c>
+      <c r="S685" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T685" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>6943e459000000000d00c1bc</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6943e459000000000d00c1bc?xsec_token=ABcIRDdprh5ih3dc7KnX5T_VX1tjhAMH10F_JqQnMi8Rw=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>别太认真</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>别太认真～
+横跳的精髓在于
+我随时会回来
+[偷笑R]#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>1778</t>
+        </is>
+      </c>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N686" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O686" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P686" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112226/1516e499bfeadffcc446e4fa4caf806b/notes_pre_post/1040g3k031q7vrqhlno6g4a7r1e8cb33v0b1vc6g!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q686" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R686" t="inlineStr">
+        <is>
+          <t>2025-12-18 19:24:09</t>
+        </is>
+      </c>
+      <c r="S686" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T686" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>6943cafe000000000d00df96</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6943cafe000000000d00df96?xsec_token=ABcIRDdprh5ih3dc7KnX5T_aAnpaOdas6T-nTQA2znQjo=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>1：赠品4＋20％税
+2：滚动单次手续费是A的N倍
+3：连拉那么多天🐑
+4：给赠品不爽快 滞后一个月
+5：如果都下来 我要两边都接受回撤 两边都要格局 累不累
+6：最最关键 滚动不方便 #我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>2162</t>
+        </is>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="N687" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O687" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P687" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112232/7b25fc939a48e27fe4206f8a4671195a/1040g00831q7pe8r00a004a7r1e8cb33vmj0lsi0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q687" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R687" t="inlineStr">
+        <is>
+          <t>2025-12-18 17:35:58</t>
+        </is>
+      </c>
+      <c r="S687" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T687" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>6943c07e000000000d03f8cf</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6943c07e000000000d03f8cf?xsec_token=ABcIRDdprh5ih3dc7KnX5T_eglNDIipMACOE2ZGsmS66g=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>2026加油我要</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>#我的炒股日记[话题]# #明年会更好[话题]# #朝目标努力[话题]# #加油加油[话题]# #有目标才有方向[话题]# #让我们一起加油[话题]# #向着目标前进[话题]# #好好努力吧[话题]# #努力实现目标[话题]# #加油每一个有梦想的人[话题]#</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>2328</t>
+        </is>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="M688" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="N688" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O688" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P688" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112238/eb8649c25b6c9664dc8fc03d48def513/notes_pre_post/1040g3k831q7pemkj7oag4a7r1e8cb33vkteqapo!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q688" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '明年会更好', '朝目标努力', '加油加油', '有目标才有方向', '让我们一起加油', '向着目标前进', '好好努力吧', '努力实现目标', '加油每一个有梦想的人']</t>
+        </is>
+      </c>
+      <c r="R688" t="inlineStr">
+        <is>
+          <t>2025-12-18 16:51:10</t>
+        </is>
+      </c>
+      <c r="S688" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T688" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>6943bbb90000000019025626</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6943bbb90000000019025626?xsec_token=ABcIRDdprh5ih3dc7KnX5T_aVVpo4jo8c7Cxt95P86G8E=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>冷知识</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>一般我走了
+后续一定会涨噢
+这是惯例
+所以有能力的
+还能赚最后一大波金币的高手  还是很多的[暗中观察R]
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="M689" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N689" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O689" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P689" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112243/958918e0d55480bfb72d5a3d280f5c8f/1040g00831q7pe8r00a104a7r1e8cb33v2ea1h8o!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q689" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R689" t="inlineStr">
+        <is>
+          <t>2025-12-18 16:30:49</t>
+        </is>
+      </c>
+      <c r="S689" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T689" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>6943b288000000001b025764</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6943b288000000001b025764?xsec_token=ABcIRDdprh5ih3dc7KnX5T_RXNBwILQVRJRvcLHaNk-YQ=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>嗖～
+收走安姑娘tvb所有金币
+机会留给能力强的人
+我休息
+姑娘A不动
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="M690" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="N690" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O690" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P690" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112249/7aeb72bea7aeb35a2346378c6c503154/1040g00831q7pe8r00a5g4a7r1e8cb33v6gvbo8o!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q690" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R690" t="inlineStr">
+        <is>
+          <t>2025-12-18 15:51:36</t>
+        </is>
+      </c>
+      <c r="S690" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T690" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>6943afd6000000001b0328de</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6943afd6000000001b0328de?xsec_token=ABcIRDdprh5ih3dc7KnX5T_UWp44tRwKGgZHw7VleT3L0=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>富贵擒牛第一式 首突</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>1925</t>
+        </is>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="M691" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="N691" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O691" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P691" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112255/bbca78c19d3c6862017d832387b8b06b/notes_pre_post/1040g3k831q7pemkj7od04a7r1e8cb33v8mr12dg!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q691" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R691" t="inlineStr">
+        <is>
+          <t>2025-12-18 15:40:07</t>
+        </is>
+      </c>
+      <c r="S691" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T691" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>6943a423000000001b0240f9</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6943a423000000001b0240f9?xsec_token=ABcIRDdprh5ih3dc7KnX5T_V_sx4H597DxaEavcQDyzM4=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>嗖～
+猫猫收小金币</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>1748</t>
+        </is>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="M692" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="N692" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O692" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P692" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112301/e5e0a776d93eb431f9c3c620a2dcda9c/1040g00831q7c0p4og0004a7r1e8cb33ve1v84ng!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q692" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R692" t="inlineStr">
+        <is>
+          <t>2025-12-18 14:50:11</t>
+        </is>
+      </c>
+      <c r="S692" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T692" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>69439a5a000000000d00f0a1</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69439a5a000000000d00f0a1?xsec_token=ABcIRDdprh5ih3dc7KnX5T_SnIQ1TqONmdkD2JJ4VnIu4=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>这几天闭嘴
+也不说牙膏了</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="M693" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N693" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O693" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P693" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112307/da8f5a72ad31848d5386ae4b8b660377/1040g00831q7c0p4og02g4a7r1e8cb33vvei8cto!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q693" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R693" t="inlineStr">
+        <is>
+          <t>2025-12-18 14:08:26</t>
+        </is>
+      </c>
+      <c r="S693" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T693" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>69439001000000000d03dbdf</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69439001000000000d03dbdf?xsec_token=ABcIRDdprh5ih3dc7KnX5T_Rx6SJsllOL2PK8EbSbhDd4=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>我要以为相信
+有些猫我永远可以等
+所以我明白
+再灯火阑珊处为什么会跌</t>
+        </is>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="M694" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N694" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O694" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P694" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112313/3205b34776da172491c42c6ca614b490/1040g00831q7c0p4og0204a7r1e8cb33v5hjo2h8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q694" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R694" t="inlineStr">
+        <is>
+          <t>2025-12-18 13:24:17</t>
+        </is>
+      </c>
+      <c r="S694" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T694" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>69436a7f000000001b024110</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69436a7f000000001b024110?xsec_token=ABcIRDdprh5ih3dc7KnX5T_VQrEnfWEU2wczYgwagQ4dI=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>晃来晃去</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>#我的炒股日记[话题]# #没事走两步[话题]# #原地踏步走[话题]# #快步走起来[话题]# #到处趴趴走[话题]# #跟着感觉走[话题]# #到处去走走[话题]# #走一步看一步[话题]# #一步两步三步四步[话题]# #走到哪算哪[话题]#</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="M695" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N695" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O695" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P695" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112319/5ab0f8b52200dd526dd4ae640c71b211/notes_pre_post/1040g3k031q7gvr5h7u604a7r1e8cb33v3i44s88!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q695" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '没事走两步', '原地踏步走', '快步走起来', '到处趴趴走', '跟着感觉走', '到处去走走', '走一步看一步', '一步两步三步四步', '走到哪算哪']</t>
+        </is>
+      </c>
+      <c r="R695" t="inlineStr">
+        <is>
+          <t>2025-12-18 10:44:16</t>
+        </is>
+      </c>
+      <c r="S695" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T695" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>694362aa00000000190259b2</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/694362aa00000000190259b2?xsec_token=ABcIRDdprh5ih3dc7KnX5T_RUz5bcOvKyF1rj5mIX3juc=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>真的很煞风景
+什么只要红一点
+下面留言什么买少了
+能不能别这样
+虽然 但是 怎么就一点没变呢 #我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="M696" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N696" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O696" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P696" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112324/420e584eeecd871c2a13e66a93b340db/1040g00831q7c0p4og06g4a7r1e8cb33v90ctiu8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q696" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R696" t="inlineStr">
+        <is>
+          <t>2025-12-18 10:10:50</t>
+        </is>
+      </c>
+      <c r="S696" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T696" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>694353d5000000001b0250eb</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/694353d5000000001b0250eb?xsec_token=ABcIRDdprh5ih3dc7KnX5T_eDoW9-sjvhMgq6ZKJq4Khs=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>三哥
+这次不一样
+我闭嘴[暗中观察R]
+如果问我
+我看去年10月新高
+以上观点都是我胡说的  谁看到了 是没经过我同意看到的  跟我没关系   鼠标再自己手上
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>1937</t>
+        </is>
+      </c>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="M697" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="N697" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O697" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P697" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112330/e758f4b1f4abc27c373eb85b033f94fb/1040g00831q7c0p4og04g4a7r1e8cb33vjqsa710!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q697" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R697" t="inlineStr">
+        <is>
+          <t>2025-12-18 09:07:33</t>
+        </is>
+      </c>
+      <c r="S697" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T697" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>694341cf00000000190267a6</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/694341cf00000000190267a6?xsec_token=ABcIRDdprh5ih3dc7KnX5T_XrUIw1xYlBCg6obdQKwcYs=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>本座掐指一算
+股份制银行最难受的阶段
+已经过了3/1了
+小级别 月小坑
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>2130</t>
+        </is>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>469</t>
+        </is>
+      </c>
+      <c r="M698" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="N698" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O698" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P698" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112336/6460abb8ab85563886a2eb6fc2bfcb17/1040g00831q7c0p4og0604a7r1e8cb33vbtfua9o!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q698" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R698" t="inlineStr">
+        <is>
+          <t>2025-12-18 07:50:39</t>
+        </is>
+      </c>
+      <c r="S698" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T698" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>6942b830000000001b03004f</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6942b830000000001b03004f?xsec_token=ABQAhpMhShfyN3_ovAzslk85LbsVD5rxAzYm146JR7C44=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>我可从来没承认过
+我是养鸡只吃股息噢[暗中观察R]
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="M699" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N699" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O699" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P699" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112341/b5b207b09ec46073f57f016654d56287/1040g2sg31q6r775o7ukg4a7r1e8cb33vnucrrco!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q699" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R699" t="inlineStr">
+        <is>
+          <t>2025-12-17 22:03:28</t>
+        </is>
+      </c>
+      <c r="S699" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T699" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>694289a1000000001b032811</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/694289a1000000001b032811?xsec_token=ABQAhpMhShfyN3_ovAzslk8-6AeM8bDHQ50kxm4dIQ0is=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>三哥也是
+某XJT
+最近也别问你
+周下我一直说
+现在周上附近
+我闭嘴
+我选择沉默
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>1864</t>
+        </is>
+      </c>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N700" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O700" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P700" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112347/c918f585ccd301ddd1b80a720154d425/1040g2sg31q6is6ft00f04a7r1e8cb33vcfqrclo!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q700" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R700" t="inlineStr">
+        <is>
+          <t>2025-12-17 18:44:50</t>
+        </is>
+      </c>
+      <c r="S700" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T700" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>694283d5000000001b0262ee</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/694283d5000000001b0262ee?xsec_token=ABQAhpMhShfyN3_ovAzslk84T84dFnUZeH7uPfPmF0r_U=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>最近
+平安姑娘
+不会再提
+不要问
+底部多说
+高了闭嘴</t>
+        </is>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>1872</t>
+        </is>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="M701" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N701" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O701" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P701" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112353/a7bb47b3925f741b22e45ef9a22026f1/1040g2sg31q6is6ft00dg4a7r1e8cb33v07j43t0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q701" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R701" t="inlineStr">
+        <is>
+          <t>2025-12-17 18:20:05</t>
+        </is>
+      </c>
+      <c r="S701" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T701" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>694273e7000000000d034a94</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/694273e7000000000d034a94?xsec_token=ABQAhpMhShfyN3_ovAzslk863jmo6LulU1E_htJH9ZxaY=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>恭喜大家 新年～</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>马上周上咯～#我的炒股日记[话题]# #年是越来越近了[话题]# #新年即将到来[话题]# #新的一年新的期待新的希望[话题]# #新年的钟声即将敲响[话题]# #明年会更好[话题]# #新的一年新的启程[话题]# #期待新的一年[话题]# #抓住新年的小尾巴[话题]# #愿新的一年越来越好[话题]#</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>1832</t>
+        </is>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N702" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O702" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P702" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602112359/27de32286dbe51cd7d68c71db10b44f7/notes_pre_post/1040g3k831q6isiojg0dg4a7r1e8cb33v448leeg!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q702" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '年是越来越近了', '新年即将到来', '新的一年新的期待新的希望', '新年的钟声即将敲响', '明年会更好', '新的一年新的启程', '期待新的一年', '抓住新年的小尾巴', '愿新的一年越来越好']</t>
+        </is>
+      </c>
+      <c r="R702" t="inlineStr">
+        <is>
+          <t>2025-12-17 17:12:07</t>
+        </is>
+      </c>
+      <c r="S702" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T702" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>69424a9c000000000d034a98</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69424a9c000000000d034a98?xsec_token=ABQAhpMhShfyN3_ovAzslk87rVAOiNRFrsWp6PRyRCERI=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>2026年 越来越好</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>分享方法策略
+与 简单报代码之间
+我选择了更累的分享策略 因为学到后
+未来能看到希望
+也能得到尊重
+所以
+我选择让更多家人看到希望
+而不是 一味地依赖我
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>4049</t>
+        </is>
+      </c>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="N703" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O703" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P703" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120004/bd27d6ca0c3d9e9d5f771e22178ec662/1040g00831q689038nu204a7r1e8cb33vul73e18!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q703" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R703" t="inlineStr">
+        <is>
+          <t>2025-12-17 14:15:56</t>
+        </is>
+      </c>
+      <c r="S703" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T703" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>69423d0d000000001b0313f7</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69423d0d000000001b0313f7?xsec_token=ABQAhpMhShfyN3_ovAzslk83K6lZoPkRBIKPkZhL3sYdM=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>谈论下</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>假设噢～
+渣猫到了周线中轨～
+那么我理解判断预计预判会去周下
+是不是可以 📉
+42.15格局
+41.15格局
+40.15格局
+前提是猫猫  前提是赠品4.75 前提龙头
+前提是永续
+那么是不是 📈
+40.15
+41.15格局掉
+42.15格局掉呢
+[捂嘴笑R]
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="N704" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O704" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P704" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120010/0d0afa1cfbdab0273a4be49b71121db1/1040g00831q689038nu2g4a7r1e8cb33vk2mc9b8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q704" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R704" t="inlineStr">
+        <is>
+          <t>2025-12-17 13:18:05</t>
+        </is>
+      </c>
+      <c r="S704" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T704" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>694233a3000000000d0384d9</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/694233a3000000000d0384d9?xsec_token=ABQAhpMhShfyN3_ovAzslk88OJUVbI62Zi_Y9v_UwYnwA=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>我并不认为
+小招猫渣
+看你怎么对她理解罢了
+如果横
+滚动周上 周下 难道不好吗？</t>
+        </is>
+      </c>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>1702</t>
+        </is>
+      </c>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="M705" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N705" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O705" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P705" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120015/f8468824f5e715d64c884a6c6ea0c096/1040g00831q689038nu1g4a7r1e8cb33vpsk8s0o!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q705" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R705" t="inlineStr">
+        <is>
+          <t>2025-12-17 12:37:55</t>
+        </is>
+      </c>
+      <c r="S705" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T705" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>69422425000000000d03f9f0</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69422425000000000d03f9f0?xsec_token=ABQAhpMhShfyN3_ovAzslk89IDQH0CuFAOp414dSCDTio=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>休息</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>提
+盈利金币的10％仙境
+今年完美收官了
+休息 过节了计划
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
+      </c>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="M706" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N706" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O706" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P706" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120021/6c0400aa2f1783aeb37e0605397dda91/1040g00831q689038nu404a7r1e8cb33vesu5vh8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q706" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R706" t="inlineStr">
+        <is>
+          <t>2025-12-17 11:31:49</t>
+        </is>
+      </c>
+      <c r="S706" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T706" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>6941fa41000000000d00c9f6</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6941fa41000000000d00c9f6?xsec_token=ABeaDkGvUdAMcNNTvXrpnwZQq7BT6SCLkuDi0_UAbuAo8=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>先考古 再说接下去结果</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>我有感觉
+2026成绩好不好
+要看
+牙膏
+变异电
+小招猫
+三哥
+等了……意思其实难度更大了</t>
+        </is>
+      </c>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>2068</t>
+        </is>
+      </c>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="L707" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="M707" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="N707" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O707" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P707" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120027/6a24d2d03cea1eceb87a10935f3414cb/notes_pre_post/1040g3k031q5ldj0vga404a7r1e8cb33v27plrgg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q707" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R707" t="inlineStr">
+        <is>
+          <t>2025-12-17 08:33:05</t>
+        </is>
+      </c>
+      <c r="S707" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T707" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>6941f7dd000000000d037779</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6941f7dd000000000d037779?xsec_token=ABeaDkGvUdAMcNNTvXrpnwZUOm8lhPwakVoDkkVf4_M88=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>券商刚周上都没到
+还是首突
+为什么会问
+还能不能格局着
+奇怪学到哪里去了都</t>
+        </is>
+      </c>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>1649</t>
+        </is>
+      </c>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="M708" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="N708" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O708" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P708" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120032/c26025e5b026c81fd49d2897e4a55397/1040g2sg31q5kb4duno0g4a7r1e8cb33ve61mlbg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q708" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R708" t="inlineStr">
+        <is>
+          <t>2025-12-17 08:22:53</t>
+        </is>
+      </c>
+      <c r="S708" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T708" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>6941ef0f000000001902536b</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6941ef0f000000001902536b?xsec_token=ABeaDkGvUdAMcNNTvXrpnwZZagfjDojc3Shr2Rnr9FDoQ=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>重走一遍</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>同一家公司
+1：估值更低
+2：份额数更多
+3：又享受一次 周下到周中～
+#要是能重来[话题]# #我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>1722</t>
+        </is>
+      </c>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="M709" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="N709" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O709" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P709" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120038/511ed805d54e140106c390273d9bc5f8/notes_pre_post/1040g3k031q62jpug7o004a7r1e8cb33v3tgnej8!nd_dft_wgth_jpg_3', 'http://sns-webpic-qc.xhscdn.com/202602120038/134e99e09d0aaaf033ada46dbc2fbddd/notes_pre_post/1040g3k031q5ldj0vga504a7r1e8cb33ve5t38t8!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q709" t="inlineStr">
+        <is>
+          <t>['要是能重来', '我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R709" t="inlineStr">
+        <is>
+          <t>2025-12-17 07:45:20</t>
+        </is>
+      </c>
+      <c r="S709" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T709" t="inlineStr">
+        <is>
+          <t>图1: OCR超时 | 图2: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>694182fc000000000d03e16a</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/694182fc000000000d03e16a?xsec_token=ABeaDkGvUdAMcNNTvXrpnwZZTREtLCrF-2ppP-Z9D-vm8=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>🎉在小红书获得的阅读量破1亿啦❗️</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>我是牛猛男[捂嘴笑R]
+#多谢大家的支持[话题]# #小红书运营[话题]# #我和小红书的故事[话题]# #小红书博主[话题]# #小红书笔记[话题]# #给点力更给力[话题]# #感谢大家支持[话题]# #小红书企业号运营[话题]# #感谢所有人[话题]# #我在小红书[话题]#</t>
+        </is>
+      </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>2138</t>
+        </is>
+      </c>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="L710" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="M710" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N710" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O710" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P710" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120044/aca7ec7ac9f3af1755173a08821acd77/notes_pre_post/1040g3k031q5ldj0vga604a7r1e8cb33vto0unig!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q710" t="inlineStr">
+        <is>
+          <t>['多谢大家的支持', '小红书运营', '我和小红书的故事', '小红书博主', '小红书笔记', '给点力更给力', '感谢大家支持', '小红书企业号运营', '感谢所有人', '我在小红书']</t>
+        </is>
+      </c>
+      <c r="R710" t="inlineStr">
+        <is>
+          <t>2025-12-17 00:04:12</t>
+        </is>
+      </c>
+      <c r="S710" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T710" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>69418292000000000d00f86c</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69418292000000000d00f86c?xsec_token=ABeaDkGvUdAMcNNTvXrpnwZSTER1o78rA1v7VD9cDKXlo=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>等待</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>#等待值得的等待[话题]#</t>
+        </is>
+      </c>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>1766</t>
+        </is>
+      </c>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="M711" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N711" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O711" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P711" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120050/0f043030c45314df1dcfb409155f304d/notes_pre_post/1040g3k031q5ldj0vga6g4a7r1e8cb33vjcoi6a8!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q711" t="inlineStr">
+        <is>
+          <t>['等待值得的等待']</t>
+        </is>
+      </c>
+      <c r="R711" t="inlineStr">
+        <is>
+          <t>2025-12-17 00:02:26</t>
+        </is>
+      </c>
+      <c r="S711" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T711" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>69413ef8000000001b026499</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69413ef8000000001b026499?xsec_token=ABeaDkGvUdAMcNNTvXrpnwZckewJpWsK06mMqyJKlCd7c=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>一起努力学习</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>今晚请假
+明天补交
+为什么
+三哥 换 三哥TVB的逻辑家人们
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>1937</t>
+        </is>
+      </c>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="L712" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="M712" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N712" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O712" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P712" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120056/203699f2bf80118224d79d5f83a886b6/1040g2sg31q5cicg5gajg4a7r1e8cb33vc69blao!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q712" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R712" t="inlineStr">
+        <is>
+          <t>2025-12-16 19:14:00</t>
+        </is>
+      </c>
+      <c r="S712" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T712" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>69413a13000000000d00e8ce</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69413a13000000000d00e8ce?xsec_token=ABeaDkGvUdAMcNNTvXrpnwZWbDVnlWrS5xoparBocpvdM=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>家人们～越来越好噢</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>[偷笑R][偷笑R][偷笑R][偷笑R][偷笑R][偷笑R]
+#越来越好的路上[话题]#</t>
+        </is>
+      </c>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>2307</t>
+        </is>
+      </c>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="L713" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="M713" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N713" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O713" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P713" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120102/d62719137bc42aeacbe30318e389533e/notes_pre_post/1040g3k031q5cilc27o604a7r1e8cb33vf4ef2b8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q713" t="inlineStr">
+        <is>
+          <t>['越来越好的路上']</t>
+        </is>
+      </c>
+      <c r="R713" t="inlineStr">
+        <is>
+          <t>2025-12-16 18:53:07</t>
+        </is>
+      </c>
+      <c r="S713" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T713" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>6940f1ae000000000d00eeab</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6940f1ae000000000d00eeab?xsec_token=ABkxOXMbSwxXcqBz2DU6t2OYaTO-DR5dmfJl8XHk7WTXs=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>牙膏好稳啊[暗中观察R]</t>
+        </is>
+      </c>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>1963</t>
+        </is>
+      </c>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="L714" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="N714" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O714" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P714" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120107/dd2eb8fc1ca0851d06fbac921dc91f75/1040g00831q50hn9mnu304a7r1e8cb33vi98fmro!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q714" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R714" t="inlineStr">
+        <is>
+          <t>2025-12-16 13:44:14</t>
+        </is>
+      </c>
+      <c r="S714" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T714" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>6940ebd6000000000d00d14d</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6940ebd6000000000d00d14d?xsec_token=ABkxOXMbSwxXcqBz2DU6t2OQZY8bgI6MsqKg4N7vJtDoU=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>人都有双面性的
+我只给你们看到的是我理性的一年
+凶悍的操作我都隐藏着 但慢慢 我也想分享给大家
+就不知道 比你们愿意学吗#互相学习互相进步[话题]#</t>
+        </is>
+      </c>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>2853</t>
+        </is>
+      </c>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>1088</t>
+        </is>
+      </c>
+      <c r="M715" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N715" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O715" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P715" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120113/b74ddd3c508948d87d51e6bfc8897bf2/1040g00831q50hn9mnu3g4a7r1e8cb33v3qn0pno!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q715" t="inlineStr">
+        <is>
+          <t>['互相学习互相进步']</t>
+        </is>
+      </c>
+      <c r="R715" t="inlineStr">
+        <is>
+          <t>2025-12-16 13:19:18</t>
+        </is>
+      </c>
+      <c r="S715" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T715" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>6940e9b8000000001902664f</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6940e9b8000000001902664f?xsec_token=ABkxOXMbSwxXcqBz2DU6t2OQpg93YH5fnNvJqjK9aHV0s=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>三哥高低切
+学会了吗#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>1642</t>
+        </is>
+      </c>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N716" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O716" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P716" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120119/8b15ab24a8771f4ec52d248bf3c75bcf/1040g00831q50hn9mnu504a7r1e8cb33vir28vpo!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q716" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R716" t="inlineStr">
+        <is>
+          <t>2025-12-16 13:10:16</t>
+        </is>
+      </c>
+      <c r="S716" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T716" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>6940d7a3000000001b03293b</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6940d7a3000000001b03293b?xsec_token=ABkxOXMbSwxXcqBz2DU6t2ORQT2stRZ7NpHmqFZXLDWAE=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>收益差 中午…就这个吧</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>[泪崩R][泪崩R][泪崩R][泪崩R]
+#中国平安[话题]#</t>
+        </is>
+      </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>1479</t>
+        </is>
+      </c>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N717" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O717" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P717" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120124/a7db2e1a6347d75aa100b7acb0a0292a/notes_pre_post/1040g3k831q4sm3menubg4a7r1e8cb33vnu79rrg!nd_dft_wgth_webp_3']</t>
+        </is>
+      </c>
+      <c r="Q717" t="inlineStr">
+        <is>
+          <t>['中国平安']</t>
+        </is>
+      </c>
+      <c r="R717" t="inlineStr">
+        <is>
+          <t>2025-12-16 11:53:07</t>
+        </is>
+      </c>
+      <c r="S717" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T717" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>6940d0ca000000001b022765</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6940d0ca000000001b022765?xsec_token=ABkxOXMbSwxXcqBz2DU6t2OUbuNh1B3rQbRIBI8YhjcEI=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>恢复2007年水平了</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>红利养鸡＋短线英雄[暗中观察R]
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>1916</t>
+        </is>
+      </c>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="M718" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N718" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O718" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P718" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120130/aeb1cb335588f4b190e18a3cced47ff2/1040g00831q4ql4f57o404a7r1e8cb33v8d4gl4g!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q718" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R718" t="inlineStr">
+        <is>
+          <t>2025-12-16 11:23:54</t>
+        </is>
+      </c>
+      <c r="S718" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T718" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>6940cbd6000000000d00e336</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6940cbd6000000000d00e336?xsec_token=ABkxOXMbSwxXcqBz2DU6t2Ofgb_3966ZpoOUTxyKmtfvg=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>嗖
+三哥全走
+换
+三哥TVB</t>
+        </is>
+      </c>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>1778</t>
+        </is>
+      </c>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="L719" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="M719" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="N719" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O719" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P719" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120136/f20fb35e80a16463f02a5773ba05f9b7/1040g00831q4ql4f57o104a7r1e8cb33vrp3kc28!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q719" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R719" t="inlineStr">
+        <is>
+          <t>2025-12-16 11:02:46</t>
+        </is>
+      </c>
+      <c r="S719" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T719" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>6940bcd9000000001b027342</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6940bcd9000000001b027342?xsec_token=ABkxOXMbSwxXcqBz2DU6t2OSYx66B0IvTkXQZqjdJQd4o=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>三哥 暂时比 一哥强</t>
+        </is>
+      </c>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>1581</t>
+        </is>
+      </c>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="M720" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N720" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O720" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P720" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120142/3d13dd738ca6f5bd158af7d2e0973586/1040g00831q4ql4f57o504a7r1e8cb33vnnidsi8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q720" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R720" t="inlineStr">
+        <is>
+          <t>2025-12-16 09:58:49</t>
+        </is>
+      </c>
+      <c r="S720" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T720" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>6940b7e1000000000d0370b9</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6940b7e1000000000d0370b9?xsec_token=ABkxOXMbSwxXcqBz2DU6t2OZOyltyh_kuqKHnXdD1sEng=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>新高了</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>大家苟住
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>1745</t>
+        </is>
+      </c>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="M721" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N721" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O721" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P721" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120147/202f23b64577e57fe2b6bb19e21a77f8/notes_pre_post/1040g3k831q4sm3menudg4a7r1e8cb33v7mn5eb8!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q721" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R721" t="inlineStr">
+        <is>
+          <t>2025-12-16 09:37:37</t>
+        </is>
+      </c>
+      <c r="S721" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T721" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>6940a7da000000000d03770d</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6940a7da000000000d03770d?xsec_token=ABkxOXMbSwxXcqBz2DU6t2OWl9vNOz37pIi2F-q6rLe34=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>2026新策略来了</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>富贵擒牛降本周线滚动大法2.0要来了
+算算时间差不多了
+2007年周医生教我的方法 算算时间 跟现在的阶段又对标上了
+我会一点一点分享 这个不难  很好学 是周上 周下的升级版
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>3674</t>
+        </is>
+      </c>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>956</t>
+        </is>
+      </c>
+      <c r="M722" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="N722" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O722" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P722" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120153/266e05651f662c2476ea616de621af66/notes_pre_post/1040g3k831q4qnggiga004a7r1e8cb33vs2a6q4g!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q722" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R722" t="inlineStr">
+        <is>
+          <t>2025-12-16 08:29:14</t>
+        </is>
+      </c>
+      <c r="S722" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T722" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>69402ad2000000001b032175</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69402ad2000000001b032175?xsec_token=ABkxOXMbSwxXcqBz2DU6t2OQ7X_qHWO4Ope3Y5dGqis8w=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>开始了</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>蛮好 蛮好
+开启月小坑了
+20 30 交叉60了
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>2107</t>
+        </is>
+      </c>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="N723" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O723" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P723" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120159/cbdc61366871580ff28788795abd2a1a/notes_pre_post/1040g3k831q4bed9ug06g4a7r1e8cb33v2rtvb4g!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q723" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R723" t="inlineStr">
+        <is>
+          <t>2025-12-15 23:35:46</t>
+        </is>
+      </c>
+      <c r="S723" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T723" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>6940124a000000000d0358b7</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6940124a000000000d0358b7?xsec_token=ABkxOXMbSwxXcqBz2DU6t2OSE8BfGgViHi05zfF_WEyJY=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>上海 深圳 当天来回</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>[暗中观察R]我又回到上海咯
+能不能明天稍微改善下生活  上去下[泪崩R][泪崩R]
+#云南白药[话题]#
+#东方海外国际[话题]#</t>
+        </is>
+      </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="M724" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N724" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O724" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P724" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120204/ba8b46d13bf3cc8c92c158e3c5eccd99/1040g2sg31q48ebn800rg4a7r1e8cb33vasehtpg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q724" t="inlineStr">
+        <is>
+          <t>['云南白药', '东方海外国际']</t>
+        </is>
+      </c>
+      <c r="R724" t="inlineStr">
+        <is>
+          <t>2025-12-15 21:51:06</t>
+        </is>
+      </c>
+      <c r="S724" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T724" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>693fdf5d00000000190252c1</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693fdf5d00000000190252c1?xsec_token=ABWIg2ygkFhhHM62ouFjlh2sCGzB6Rz7ggOUCdxNJh0xw=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>感谢大家</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>说明下
+我今天参加的不是平安的普通股东大会
+这是十几个名额 走进上市公司 股东或UP主邀请制 业绩分享会
+都是因为家人们支持
+我才能去的
+所以要感谢大家
+#感谢所有人[话题]#</t>
+        </is>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>4380</t>
+        </is>
+      </c>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
+      </c>
+      <c r="M725" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="N725" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O725" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P725" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120210/977374c796fbe9aff287b74761085ef6/1040g2sg31q40cve8ga304a7r1e8cb33v3ltu570!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q725" t="inlineStr">
+        <is>
+          <t>['感谢所有人']</t>
+        </is>
+      </c>
+      <c r="R725" t="inlineStr">
+        <is>
+          <t>2025-12-15 18:13:49</t>
+        </is>
+      </c>
+      <c r="S725" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T725" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>693fdd41000000001b024428</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693fdd41000000001b024428?xsec_token=ABWIg2ygkFhhHM62ouFjlh2lqlhj5zga0gbOI8VFvziuE=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>收益差 机场吃盒饭</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>[泪崩R][泪崩R][泪崩R]#云南白药[话题]#</t>
+        </is>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="M726" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N726" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O726" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P726" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120216/0e8e2761488396b4001fb93001bdd33d/notes_pre_post/1040g3k031q3pr3l87u504a7r1e8cb33vh9a0e6o!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q726" t="inlineStr">
+        <is>
+          <t>['云南白药']</t>
+        </is>
+      </c>
+      <c r="R726" t="inlineStr">
+        <is>
+          <t>2025-12-15 18:04:49</t>
+        </is>
+      </c>
+      <c r="S726" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T726" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>693fd904000000000d03f2ee</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693fd904000000000d03f2ee?xsec_token=ABWIg2ygkFhhHM62ouFjlh2tw2cUgU4UUJTzfRN-7rX_I=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>走了 深圳</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>虽然什么都没吃
+但挺好的 当天来回
+#短暂的旅途[话题]# #不一样的旅途[话题]# #说就走的旅程[话题]# #舍不得离开[话题]# #来来往往匆匆忙忙[话题]# #换个城市换个心情[话题]# #走到哪算哪[话题]#</t>
+        </is>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>1778</t>
+        </is>
+      </c>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L727" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="M727" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N727" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O727" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P727" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120222/b048058664aa09a66dd04767539c5c89/notes_pre_post/1040g3k031q3pr3l87u204a7r1e8cb33v981kqa0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q727" t="inlineStr">
+        <is>
+          <t>['短暂的旅途', '不一样的旅途', '说就走的旅程', '舍不得离开', '来来往往匆匆忙忙', '换个城市换个心情', '走到哪算哪']</t>
+        </is>
+      </c>
+      <c r="R727" t="inlineStr">
+        <is>
+          <t>2025-12-15 17:46:44</t>
+        </is>
+      </c>
+      <c r="S727" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T727" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>693fd071000000001b023500</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693fd071000000001b023500?xsec_token=ABWIg2ygkFhhHM62ouFjlh2kjo8I2Ut8cwvgoJ83x3FGo=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>2025年平安行 尊重投资者的企业</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>准备很详细
+集团董秘解说非常有水平
+赞一个
+今年跟我一起格局平安姑娘的家人们
+恭喜大家
+#中国平安[话题]#</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>2488</t>
+        </is>
+      </c>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="M728" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="N728" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O728" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P728" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120227/6516d7d3394e1d5bf821b9191cbbda81/notes_pre_post/1040g3k031q3pr3l87u5g4a7r1e8cb33vu8moqe0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q728" t="inlineStr">
+        <is>
+          <t>['中国平安']</t>
+        </is>
+      </c>
+      <c r="R728" t="inlineStr">
+        <is>
+          <t>2025-12-15 17:10:09</t>
+        </is>
+      </c>
+      <c r="S728" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T728" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>693fc1b2000000000d0367da</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693fc1b2000000000d0367da?xsec_token=ABWIg2ygkFhhHM62ouFjlh2r5PGHcwMCW5V-75WEjPy_s=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>董秘问答</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>1：60％-70％的央国企医疗支付
+2： 保守稳健 保底分红险
+3：养老平台 保费业务  70％
+4：大摩说的 并没有完全看清寿险业绩 还有空间很大
+5：某行业风险基本出清
+6：保险业绩并未达到国际平均水平 60％-70％
+别的慢慢写吧
+大金融符合国家要求 yyds</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>2428</t>
+        </is>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="M729" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="N729" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O729" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P729" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120233/a7d54a1c9cc1b08a2dbb25abb87dfb03/1040g00831q3pqll27u4g4a7r1e8cb33vsmug978!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q729" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R729" t="inlineStr">
+        <is>
+          <t>2025-12-15 16:07:14</t>
+        </is>
+      </c>
+      <c r="S729" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T729" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>693fba07000000001b030342</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693fba07000000001b030342?xsec_token=ABWIg2ygkFhhHM62ouFjlh2qpqh31-SKB2otb1BpWqjtc=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>收集资源中</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>家人们～当天飞深圳来回很累的
+点赞支持起来
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>4788</t>
+        </is>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="M730" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N730" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O730" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P730" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120239/2aa14ab69900c74c838d96f0c2a7b0dc/notes_pre_post/1040g3k031q3pr3l87u3g4a7r1e8cb33vq89c0h8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q730" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R730" t="inlineStr">
+        <is>
+          <t>2025-12-15 15:34:31</t>
+        </is>
+      </c>
+      <c r="S730" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T730" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>693fb8a90000000019025b10</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693fb8a90000000019025b10?xsec_token=ABWIg2ygkFhhHM62ouFjlh2ieu3qZ0Q64BPZ8NKn52GUY=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>YYDS</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>一图流
+#中国平安[话题]#</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>1917</t>
+        </is>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="M731" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N731" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O731" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P731" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120244/0a6ff28e017649853e15bf569dcc2fa8/notes_pre_post/1040g3k031q3pr3l87u2g4a7r1e8cb33v88v0v78!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q731" t="inlineStr">
+        <is>
+          <t>['中国平安']</t>
+        </is>
+      </c>
+      <c r="R731" t="inlineStr">
+        <is>
+          <t>2025-12-15 15:28:41</t>
+        </is>
+      </c>
+      <c r="S731" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T731" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>693fa4d7000000001b026ad3</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693fa4d7000000001b026ad3?xsec_token=ABWIg2ygkFhhHM62ouFjlh2uFYA_l9HrPektibL3-2Zko=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>首突拯救世界[偷笑R]
+宁波突了
+那么接下去就是
+广州卖变异电的拉#</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="M732" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="N732" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O732" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P732" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120250/5460c6fabe3167be237a3eb7cfcbf02d/1040g00831q3pqll27u3g4a7r1e8cb33vce0sfrg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q732" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R732" t="inlineStr">
+        <is>
+          <t>2025-12-15 14:04:07</t>
+        </is>
+      </c>
+      <c r="S732" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T732" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>693fa075000000001b025426</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693fa075000000001b025426?xsec_token=ABWIg2ygkFhhHM62ouFjlh2rIbR6szpsUZ4T8aJF_ydCs=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>高的我腿软了</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>[泪崩R][泪崩R][泪崩R]
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>1726</t>
+        </is>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="M733" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N733" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O733" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P733" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120256/1e657d4415dfd7ae23715469ab1d15cd/notes_pre_post/1040g3k031q3pr3l87u604a7r1e8cb33v5ru1vr0!nd_dft_wlteh_jpg_3', 'http://sns-webpic-qc.xhscdn.com/202602120256/bbd5bf8ec758ce69d882df2ac578f4cf/notes_pre_post/1040g3k031q3pr3l87u4g4a7r1e8cb33vaj983uo!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q733" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R733" t="inlineStr">
+        <is>
+          <t>2025-12-15 13:45:25</t>
+        </is>
+      </c>
+      <c r="S733" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T733" t="inlineStr">
+        <is>
+          <t>图1: OCR超时 | 图2: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>693f9b69000000000d03804b</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693f9b69000000000d03804b?xsec_token=ABWIg2ygkFhhHM62ouFjlh2vDamGLLaFpjbrhsZC69E-4=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>冷知识
+宁波那个银行
+是不是又一次验证了
+我的擒牛大法第一式#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>1833</t>
+        </is>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="M734" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="N734" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O734" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P734" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120302/cc581847ca97c6d6fec2ed26d584428b/1040g00831q3pqll27u604a7r1e8cb33vg9i8mv0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q734" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R734" t="inlineStr">
+        <is>
+          <t>2025-12-15 13:23:53</t>
+        </is>
+      </c>
+      <c r="S734" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T734" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>693f9a70000000000d03c117</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693f9a70000000000d03c117?xsec_token=ABWIg2ygkFhhHM62ouFjlh2iAn72z2iUZ0Tosy0HT1kDs=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>平安大厦啊哈哈哈</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>1744</t>
+        </is>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="M735" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N735" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O735" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P735" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120308/0446a72918cfc8f2db2f5cab953d4651/notes_pre_post/1040g3k031q3pr3l87u6g4a7r1e8cb33vs66l8cg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q735" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R735" t="inlineStr">
+        <is>
+          <t>2025-12-15 13:19:44</t>
+        </is>
+      </c>
+      <c r="S735" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T735" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>693f8685000000001b03300c</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693f8685000000001b03300c?xsec_token=ABWIg2ygkFhhHM62ouFjlh2mZ5FfbUBup2-qHVIUHATMs=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>我又来咯</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>来了就是深圳人
+#走一走看一看[话题]#</t>
+        </is>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>1837</t>
+        </is>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="M736" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N736" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O736" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P736" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120313/119635148b19528f77fbc208edf241e6/notes_pre_post/1040g3k831q3jjinf7go04a7r1e8cb33voocmpp0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q736" t="inlineStr">
+        <is>
+          <t>['走一走看一看']</t>
+        </is>
+      </c>
+      <c r="R736" t="inlineStr">
+        <is>
+          <t>2025-12-15 11:54:45</t>
+        </is>
+      </c>
+      <c r="S736" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T736" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>693f78a00000000019027ce1</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693f78a00000000019027ce1?xsec_token=ABWIg2ygkFhhHM62ouFjlh2nAzmRwTTNcfrMuRzxmRnJo=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>今天是否快乐</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>[偷笑R]#目前精神状态良好[话题]#</t>
+        </is>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>1652</t>
+        </is>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="M737" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N737" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O737" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P737" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120319/cb9ce39c10cefa5d6206b06ee64290c4/notes_pre_post/1040g3k831q3jjinf7gog4a7r1e8cb33vem30hc0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q737" t="inlineStr">
+        <is>
+          <t>['目前精神状态良好']</t>
+        </is>
+      </c>
+      <c r="R737" t="inlineStr">
+        <is>
+          <t>2025-12-15 10:55:28</t>
+        </is>
+      </c>
+      <c r="S737" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T737" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>698d2ce3000000001b0157e2</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/698d2ce3000000001b0157e2?xsec_token=AB4zsq7HWhtx7ZjZE4TlyOPedKeY_w0FFZyIKj5gH0_O0=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>期待✓我来</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>这里要勾起来噢[吐舌头H]
+60现在是✗120
+✓起来就漂亮了
+#我的炒股日记[话题]# #期待[话题]# #一切尽在不言中[话题]# #一整个期待[话题]# #总得找个盼头[话题]# #浅浅的期待[话题]# #该来的总会来[话题]# #迫不及待了[话题]# #啥也不说了[话题]# #一起期待吧[话题]#</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>1322</t>
+        </is>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="M738" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N738" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O738" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P738" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120953/f9fffb8865c8bdcf2acc93d9929a8287/1040g2sg31sev7nsll8105q6h4ijollef0dghr30!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q738" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '期待', '一切尽在不言中', '一整个期待', '总得找个盼头', '浅浅的期待', '该来的总会来', '迫不及待了', '啥也不说了', '一起期待吧']</t>
+        </is>
+      </c>
+      <c r="R738" t="inlineStr">
+        <is>
+          <t>2026-02-12 09:29:07</t>
+        </is>
+      </c>
+      <c r="S738" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="T738" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>698d2ba3000000001b01ca65</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/698d2ba3000000001b01ca65?xsec_token=AB4zsq7HWhtx7ZjZE4TlyOPSgUKSsWyfnX04X3cEeCHo0=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>要等汇率反弹了</t>
+        </is>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>1620</t>
+        </is>
+      </c>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="N739" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O739" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P739" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120959/d4344822d9865102c8e8d4f25658da80/1040g2sg31sev7nsll8005q6h4ijolleff7lr7tg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q739" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R739" t="inlineStr">
+        <is>
+          <t>2026-02-12 09:23:47</t>
+        </is>
+      </c>
+      <c r="S739" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="T739" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>698cb18200000000150202d9</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/698cb18200000000150202d9?xsec_token=ABaM_A3238qO1J2SzOROOauK6iuRBGr1MFDE2ntuV42yw=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>喜欢小红书平台</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>#小红书社区公约由我提议[话题]# #小红书社区公约[话题]# #我的炒股日记[话题]# #作品推广小红书[话题]# #多谢大家的支持[话题]# #优质内容输出者[话题]# #小红书企业号运营[话题]# #小红书笔记[话题]# #自媒‮创体‬业[话题]# #小红书运营[话题]#</t>
+        </is>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>3994</t>
+        </is>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="M740" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N740" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O740" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P740" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121004/2fdc1af3526fe46308d3d0e930c462c7/1040g2sg31sev7nsll8405q6h4ijollef7gn30qo!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q740" t="inlineStr">
+        <is>
+          <t>['小红书社区公约由我提议', '小红书社区公约', '我的炒股日记', '作品推广小红书', '多谢大家的支持', '优质内容输出者', '小红书企业号运营', '小红书笔记', '自媒\u202e创体\u202c业', '小红书运营']</t>
+        </is>
+      </c>
+      <c r="R740" t="inlineStr">
+        <is>
+          <t>2026-02-12 00:42:42</t>
+        </is>
+      </c>
+      <c r="S740" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="T740" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>698c8d72000000001502245f</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/698c8d72000000001502245f?xsec_token=ABaM_A3238qO1J2SzOROOauEunr76gunwnZy6ybCUYyIg=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>我要吃鱼</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>#我的炒股日记[话题]# #鱼[话题]# #展示自己的鱼[话题]# #并不喜欢吃鱼[话题]# #钓鱼人[话题]# #天冷就要多吃鱼[话题]# #钓鱼人的乐趣只有钓鱼人懂[话题]# #吃鱼拯救世界[话题]# #大鱼吃小鱼[话题]# #鲫鱼[话题]#</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>5650</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="M741" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N741" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O741" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P741" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121010/1bbd3980db7347fea3cb484a8b62d1a9/1040g2sg31sepk5thlmhg4a7r1e8cb33vo21842o!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q741" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '鱼', '展示自己的鱼', '并不喜欢吃鱼', '钓鱼人', '天冷就要多吃鱼', '钓鱼人的乐趣只有钓鱼人懂', '吃鱼拯救世界', '大鱼吃小鱼', '鲫鱼']</t>
+        </is>
+      </c>
+      <c r="R741" t="inlineStr">
+        <is>
+          <t>2026-02-11 22:08:50</t>
+        </is>
+      </c>
+      <c r="S741" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="T741" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>698c8d18000000001503b20d</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/698c8d18000000001503b20d?xsec_token=ABaM_A3238qO1J2SzOROOauBbxnXMBUSwFu3Qr7lQNqHM=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>电 电 电</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>领导 我懂了 别再说了
+#科技自立自强[话题]# #我的炒股日记[话题]# #能源[话题]# #电力[话题]# #没别的意思[话题]# #触电的感觉[话题]# #搞错了再来[话题]# #所有人可见[话题]# #脑瓜子嗡嗡嗡嗡[话题]# #我又在乱来[话题]#</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>6626</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="M742" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="N742" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O742" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P742" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121016/325b5cdf2c144afd6bd6850102ffa3fa/1040g2sg31sepk5thlmi04a7r1e8cb33vgoku5n0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q742" t="inlineStr">
+        <is>
+          <t>['科技自立自强', '我的炒股日记', '能源', '电力', '没别的意思', '触电的感觉', '搞错了再来', '所有人可见', '脑瓜子嗡嗡嗡嗡', '我又在乱来']</t>
+        </is>
+      </c>
+      <c r="R742" t="inlineStr">
+        <is>
+          <t>2026-02-11 22:07:20</t>
+        </is>
+      </c>
+      <c r="S742" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="T742" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>698c658e000000001503299b</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/698c658e000000001503299b?xsec_token=ABaM_A3238qO1J2SzOROOauK7yrLLm_4ZhqCmLET4Yqjk=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>红 红 红</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>#我的炒股日记[话题]# #从年头红到年尾[话题]# #时代的红利[话题]# #凭实力大红[话题]# #就要红出圈[话题]# #被红运笼罩[话题]# #中国红[话题]# #红色的起点[话题]# #红色[话题]# #都有一颗红亮的心[话题]#</t>
+        </is>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>5491</t>
+        </is>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="M743" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N743" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O743" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P743" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121021/65b2affe0a10379304761fbeb943e6ec/1040g2sg31sepk5thlmkg4a7r1e8cb33vj5q6ta0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q743" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '从年头红到年尾', '时代的红利', '凭实力大红', '就要红出圈', '被红运笼罩', '中国红', '红色的起点', '红色', '都有一颗红亮的心']</t>
+        </is>
+      </c>
+      <c r="R743" t="inlineStr">
+        <is>
+          <t>2026-02-11 19:18:38</t>
+        </is>
+      </c>
+      <c r="S743" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="T743" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
+++ b/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T743"/>
+  <dimension ref="A1:T757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77294,6 +77294,1453 @@
         </is>
       </c>
     </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>698c10b00000000015032057</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/698c10b00000000015032057?xsec_token=ABaM_A3238qO1J2SzOROOauMtEmtzJ1WzUzh_XXZVnVaI=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>1：可能分红会跌
+2：可能戴维斯双杀
+3：很慢
+4：老登
+5：以后有什么 X七八星云的什么乱七八糟的可以替代你们打电话  连宽带都是免费的
+6：打压权重！！！！不可能涨的
+7：…………
+我都说清楚了
+谁跟后面下面问怎么办
+我肯定要屏蔽你
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>5393</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="M744" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N744" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O744" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P744" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121027/70b9775d5d6f517df03ac438bc6bbd29/1040g00831sef6gmdls6g4a7r1e8cb33vccon8g8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q744" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R744" t="inlineStr">
+        <is>
+          <t>2026-02-11 13:16:32</t>
+        </is>
+      </c>
+      <c r="S744" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="T744" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>698bf51e000000001b01404d</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/698bf51e000000001b01404d?xsec_token=ABUVFGVTYfk4fJsKFLGBXbG2FGh91zj-jNIdhiK24HmMo=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>最新看法</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>#我的炒股日记[话题]# #仅个人见解及分享[话题]# #投资需谨慎[话题]# #就想说点大实[话题]# #我们一起来聊一聊[话题]# #来来来我们一起来讨论[话题]# #希望对大家有帮助[话题]# #形势一片大好[话题]# #个人目前感觉挺好的[话题]# #并且有自己的见解[话题]#</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>5187</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="M745" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N745" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O745" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P745" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121033/15a5f6831d57246f0601e62855458450/1040g00831se5jicllk0g4a7r1e8cb33vt37kck8!nd_dft_wlteh_webp_3']</t>
+        </is>
+      </c>
+      <c r="Q745" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '仅个人见解及分享', '投资需谨慎', '就想说点大实', '我们一起来聊一聊', '来来来我们一起来讨论', '希望对大家有帮助', '形势一片大好', '个人目前感觉挺好的', '并且有自己的见解']</t>
+        </is>
+      </c>
+      <c r="R745" t="inlineStr">
+        <is>
+          <t>2026-02-11 11:18:55</t>
+        </is>
+      </c>
+      <c r="S745" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="T745" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>698bf0b6000000001503bc58</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/698bf0b6000000001503bc58?xsec_token=ABUVFGVTYfk4fJsKFLGBXbG4gT3uZm6qgFNUsajoBKsgc=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>无用的冷知识</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>#我的炒股日记[话题]# #无用的知识[话题]# #有趣的事实[话题]# #奇怪的知识增加了[话题]# #每天一个小知识[话题]# #神奇的知识[话题]# #分享知识[话题]# #奇怪但有用的[话题]# #涨见识[话题]#</t>
+        </is>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>5091</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="M746" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N746" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O746" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P746" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121039/a7d1eb89f12fb7fd334087b10727552d/1040g00831se5jicllk2g4a7r1e8cb33vv3qij6o!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q746" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '无用的知识', '有趣的事实', '奇怪的知识增加了', '每天一个小知识', '神奇的知识', '分享知识', '奇怪但有用的', '涨见识']</t>
+        </is>
+      </c>
+      <c r="R746" t="inlineStr">
+        <is>
+          <t>2026-02-11 11:00:06</t>
+        </is>
+      </c>
+      <c r="S746" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="T746" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>698d2ce3000000001b0157e2</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/698d2ce3000000001b0157e2?xsec_token=AB4zsq7HWhtx7ZjZE4TlyOPedKeY_w0FFZyIKj5gH0_O0=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>期待✓我来</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>这里要勾起来噢[吐舌头H]
+60现在是✗120
+✓起来就漂亮了
+#我的炒股日记[话题]# #期待[话题]# #一切尽在不言中[话题]# #一整个期待[话题]# #总得找个盼头[话题]# #浅浅的期待[话题]# #该来的总会来[话题]# #迫不及待了[话题]# #啥也不说了[话题]# #一起期待吧[话题]#</t>
+        </is>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>1322</t>
+        </is>
+      </c>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="M747" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N747" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O747" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P747" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120953/f9fffb8865c8bdcf2acc93d9929a8287/1040g2sg31sev7nsll8105q6h4ijollef0dghr30!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q747" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '期待', '一切尽在不言中', '一整个期待', '总得找个盼头', '浅浅的期待', '该来的总会来', '迫不及待了', '啥也不说了', '一起期待吧']</t>
+        </is>
+      </c>
+      <c r="R747" t="inlineStr">
+        <is>
+          <t>2026-02-12 09:29:07</t>
+        </is>
+      </c>
+      <c r="S747" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="T747" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>698d2ba3000000001b01ca65</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/698d2ba3000000001b01ca65?xsec_token=AB4zsq7HWhtx7ZjZE4TlyOPSgUKSsWyfnX04X3cEeCHo0=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>要等汇率反弹了</t>
+        </is>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>1620</t>
+        </is>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="N748" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O748" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P748" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602120959/d4344822d9865102c8e8d4f25658da80/1040g2sg31sev7nsll8005q6h4ijolleff7lr7tg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q748" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R748" t="inlineStr">
+        <is>
+          <t>2026-02-12 09:23:47</t>
+        </is>
+      </c>
+      <c r="S748" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="T748" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>698cb18200000000150202d9</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/698cb18200000000150202d9?xsec_token=ABaM_A3238qO1J2SzOROOauK6iuRBGr1MFDE2ntuV42yw=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>喜欢小红书平台</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>#小红书社区公约由我提议[话题]# #小红书社区公约[话题]# #我的炒股日记[话题]# #作品推广小红书[话题]# #多谢大家的支持[话题]# #优质内容输出者[话题]# #小红书企业号运营[话题]# #小红书笔记[话题]# #自媒‮创体‬业[话题]# #小红书运营[话题]#</t>
+        </is>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>3994</t>
+        </is>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="M749" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N749" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O749" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P749" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121004/2fdc1af3526fe46308d3d0e930c462c7/1040g2sg31sev7nsll8405q6h4ijollef7gn30qo!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q749" t="inlineStr">
+        <is>
+          <t>['小红书社区公约由我提议', '小红书社区公约', '我的炒股日记', '作品推广小红书', '多谢大家的支持', '优质内容输出者', '小红书企业号运营', '小红书笔记', '自媒\u202e创体\u202c业', '小红书运营']</t>
+        </is>
+      </c>
+      <c r="R749" t="inlineStr">
+        <is>
+          <t>2026-02-12 00:42:42</t>
+        </is>
+      </c>
+      <c r="S749" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="T749" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>698c8d72000000001502245f</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/698c8d72000000001502245f?xsec_token=ABaM_A3238qO1J2SzOROOauEunr76gunwnZy6ybCUYyIg=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>我要吃鱼</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>#我的炒股日记[话题]# #鱼[话题]# #展示自己的鱼[话题]# #并不喜欢吃鱼[话题]# #钓鱼人[话题]# #天冷就要多吃鱼[话题]# #钓鱼人的乐趣只有钓鱼人懂[话题]# #吃鱼拯救世界[话题]# #大鱼吃小鱼[话题]# #鲫鱼[话题]#</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>5650</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="M750" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N750" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O750" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P750" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121010/1bbd3980db7347fea3cb484a8b62d1a9/1040g2sg31sepk5thlmhg4a7r1e8cb33vo21842o!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q750" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '鱼', '展示自己的鱼', '并不喜欢吃鱼', '钓鱼人', '天冷就要多吃鱼', '钓鱼人的乐趣只有钓鱼人懂', '吃鱼拯救世界', '大鱼吃小鱼', '鲫鱼']</t>
+        </is>
+      </c>
+      <c r="R750" t="inlineStr">
+        <is>
+          <t>2026-02-11 22:08:50</t>
+        </is>
+      </c>
+      <c r="S750" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="T750" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>698c8d18000000001503b20d</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/698c8d18000000001503b20d?xsec_token=ABaM_A3238qO1J2SzOROOauBbxnXMBUSwFu3Qr7lQNqHM=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>电 电 电</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>领导 我懂了 别再说了
+#科技自立自强[话题]# #我的炒股日记[话题]# #能源[话题]# #电力[话题]# #没别的意思[话题]# #触电的感觉[话题]# #搞错了再来[话题]# #所有人可见[话题]# #脑瓜子嗡嗡嗡嗡[话题]# #我又在乱来[话题]#</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>6626</t>
+        </is>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="M751" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="N751" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O751" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P751" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121016/325b5cdf2c144afd6bd6850102ffa3fa/1040g2sg31sepk5thlmi04a7r1e8cb33vgoku5n0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q751" t="inlineStr">
+        <is>
+          <t>['科技自立自强', '我的炒股日记', '能源', '电力', '没别的意思', '触电的感觉', '搞错了再来', '所有人可见', '脑瓜子嗡嗡嗡嗡', '我又在乱来']</t>
+        </is>
+      </c>
+      <c r="R751" t="inlineStr">
+        <is>
+          <t>2026-02-11 22:07:20</t>
+        </is>
+      </c>
+      <c r="S751" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="T751" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>698c658e000000001503299b</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/698c658e000000001503299b?xsec_token=ABaM_A3238qO1J2SzOROOauK7yrLLm_4ZhqCmLET4Yqjk=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>红 红 红</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>#我的炒股日记[话题]# #从年头红到年尾[话题]# #时代的红利[话题]# #凭实力大红[话题]# #就要红出圈[话题]# #被红运笼罩[话题]# #中国红[话题]# #红色的起点[话题]# #红色[话题]# #都有一颗红亮的心[话题]#</t>
+        </is>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>5491</t>
+        </is>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="M752" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N752" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O752" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P752" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121021/65b2affe0a10379304761fbeb943e6ec/1040g2sg31sepk5thlmkg4a7r1e8cb33vj5q6ta0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q752" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '从年头红到年尾', '时代的红利', '凭实力大红', '就要红出圈', '被红运笼罩', '中国红', '红色的起点', '红色', '都有一颗红亮的心']</t>
+        </is>
+      </c>
+      <c r="R752" t="inlineStr">
+        <is>
+          <t>2026-02-11 19:18:38</t>
+        </is>
+      </c>
+      <c r="S752" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="T752" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>698c10b00000000015032057</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/698c10b00000000015032057?xsec_token=ABaM_A3238qO1J2SzOROOauMtEmtzJ1WzUzh_XXZVnVaI=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>1：可能分红会跌
+2：可能戴维斯双杀
+3：很慢
+4：老登
+5：以后有什么 X七八星云的什么乱七八糟的可以替代你们打电话  连宽带都是免费的
+6：打压权重！！！！不可能涨的
+7：…………
+我都说清楚了
+谁跟后面下面问怎么办
+我肯定要屏蔽你
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>5393</t>
+        </is>
+      </c>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="L753" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="M753" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N753" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O753" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P753" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121027/70b9775d5d6f517df03ac438bc6bbd29/1040g00831sef6gmdls6g4a7r1e8cb33vccon8g8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q753" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R753" t="inlineStr">
+        <is>
+          <t>2026-02-11 13:16:32</t>
+        </is>
+      </c>
+      <c r="S753" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="T753" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>698bf51e000000001b01404d</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/698bf51e000000001b01404d?xsec_token=ABUVFGVTYfk4fJsKFLGBXbG2FGh91zj-jNIdhiK24HmMo=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>最新看法</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>#我的炒股日记[话题]# #仅个人见解及分享[话题]# #投资需谨慎[话题]# #就想说点大实[话题]# #我们一起来聊一聊[话题]# #来来来我们一起来讨论[话题]# #希望对大家有帮助[话题]# #形势一片大好[话题]# #个人目前感觉挺好的[话题]# #并且有自己的见解[话题]#</t>
+        </is>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>5187</t>
+        </is>
+      </c>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="M754" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N754" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O754" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P754" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121033/15a5f6831d57246f0601e62855458450/1040g00831se5jicllk0g4a7r1e8cb33vt37kck8!nd_dft_wlteh_webp_3']</t>
+        </is>
+      </c>
+      <c r="Q754" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '仅个人见解及分享', '投资需谨慎', '就想说点大实', '我们一起来聊一聊', '来来来我们一起来讨论', '希望对大家有帮助', '形势一片大好', '个人目前感觉挺好的', '并且有自己的见解']</t>
+        </is>
+      </c>
+      <c r="R754" t="inlineStr">
+        <is>
+          <t>2026-02-11 11:18:55</t>
+        </is>
+      </c>
+      <c r="S754" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="T754" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>698bf0b6000000001503bc58</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/698bf0b6000000001503bc58?xsec_token=ABUVFGVTYfk4fJsKFLGBXbG4gT3uZm6qgFNUsajoBKsgc=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>无用的冷知识</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>#我的炒股日记[话题]# #无用的知识[话题]# #有趣的事实[话题]# #奇怪的知识增加了[话题]# #每天一个小知识[话题]# #神奇的知识[话题]# #分享知识[话题]# #奇怪但有用的[话题]# #涨见识[话题]#</t>
+        </is>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>5091</t>
+        </is>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="L755" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="M755" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N755" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O755" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P755" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121039/a7d1eb89f12fb7fd334087b10727552d/1040g00831se5jicllk2g4a7r1e8cb33vv3qij6o!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q755" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '无用的知识', '有趣的事实', '奇怪的知识增加了', '每天一个小知识', '神奇的知识', '分享知识', '奇怪但有用的', '涨见识']</t>
+        </is>
+      </c>
+      <c r="R755" t="inlineStr">
+        <is>
+          <t>2026-02-11 11:00:06</t>
+        </is>
+      </c>
+      <c r="S755" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="T755" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>698d46ee0000000016009814</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/698d46ee0000000016009814?xsec_token=AB4zsq7HWhtx7ZjZE4TlyOPWa6cDuZACDZreytL8MmEsA=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>个人观点 不一定对的#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="L756" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M756" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N756" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O756" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P756" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121134/2a9713ed73c49c0edd37cfd864369c29/1040g2sg31sfj9au6lsr04a7r1e8cb33vqejluvo!nd_dft_wlteh_webp_3']</t>
+        </is>
+      </c>
+      <c r="Q756" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R756" t="inlineStr">
+        <is>
+          <t>2026-02-12 11:20:14</t>
+        </is>
+      </c>
+      <c r="S756" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="T756" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>698d46ee0000000016009814</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/698d46ee0000000016009814?xsec_token=AB4zsq7HWhtx7ZjZE4TlyOPWa6cDuZACDZreytL8MmEsA=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>个人观点 不一定对的#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L757" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="M757" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N757" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O757" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P757" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121135/f108e642194de9357f3ac1e58060613b/1040g2sg31sfj9au6lsr04a7r1e8cb33vqejluvo!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q757" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R757" t="inlineStr">
+        <is>
+          <t>2026-02-12 11:20:14</t>
+        </is>
+      </c>
+      <c r="S757" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="T757" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
+++ b/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T739"/>
+  <dimension ref="A1:T749"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66559,6 +66559,1034 @@
         </is>
       </c>
     </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>6951e9ab000000002102a2b7</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6951e9ab000000002102a2b7?xsec_token=ABpa8_BEzJhIPqpMGRutI7eQ3py5Gc7NbemyNCDLBZyII&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>1783</t>
+        </is>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="M740" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N740" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O740" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P740" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121226/e205d78d7463832a0e4dc3a9f24d1f0b/1040g2sg31qlm0a9hnudg4a7r1e8cb33vbmamd6o!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q740" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R740" t="inlineStr">
+        <is>
+          <t>2025-12-29 10:38:35</t>
+        </is>
+      </c>
+      <c r="S740" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T740" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>694e5e9f0000000021028cce</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/694e5e9f0000000021028cce?xsec_token=ABdWqMMmZajVh3FFjp67aXMNS8GNSrUaxxtKe8ozmrEJM&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>休息 休息下</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>收益差 只能休息 休息下了
+我太惨了
+#招商银行[话题]#
+#我的炒股日记[话题]#
+#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>1649</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="M741" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N741" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O741" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P741" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121227/db95a3d40184854ce9d70a9e7f618257/notes_pre_post/1040g3k831qi79eh5gadg4a7r1e8cb33vt9gf740!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q741" t="inlineStr">
+        <is>
+          <t>['招商银行', '我的炒股日记', '在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R741" t="inlineStr">
+        <is>
+          <t>2025-12-26 18:08:31</t>
+        </is>
+      </c>
+      <c r="S741" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T741" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>694e5e9f0000000021028cce</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/694e5e9f0000000021028cce?xsec_token=ABdWqMMmZajVh3FFjp67aXMNS8GNSrUaxxtKe8ozmrEJM&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>休息 休息下</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>收益差 只能休息 休息下了
+我太惨了
+#招商银行[话题]#
+#我的炒股日记[话题]#
+#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>1649</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="M742" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N742" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O742" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P742" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121231/bbcbb91f3c18cd578cbcb1f58eba7c86/notes_pre_post/1040g3k831qi79eh5gadg4a7r1e8cb33vt9gf740!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q742" t="inlineStr">
+        <is>
+          <t>['招商银行', '我的炒股日记', '在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R742" t="inlineStr">
+        <is>
+          <t>2025-12-26 18:08:31</t>
+        </is>
+      </c>
+      <c r="S742" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T742" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>694d4ed9000000002200af9e</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/694d4ed9000000002200af9e?xsec_token=ABOezt9_Ys441WVKow8V4tfu5GyuE-dGF0YAN_2n7owmg&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>2098</t>
+        </is>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="M743" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N743" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O743" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P743" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121232/566d92b48ca6c12fdd258aa152bd8eed/1040g2sg31qh5l6ob0ai04a7r1e8cb33vmd6i5v0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q743" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R743" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:48:57</t>
+        </is>
+      </c>
+      <c r="S743" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T743" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>694d4ed9000000002200af9e</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/694d4ed9000000002200af9e?xsec_token=ABOezt9_Ys441WVKow8V4tfu5GyuE-dGF0YAN_2n7owmg&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>2098</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="M744" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N744" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O744" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P744" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121236/d7e5b2f3ed0c6fe733dc5ff020bcaf95/1040g2sg31qh5l6ob0ai04a7r1e8cb33vmd6i5v0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q744" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R744" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:48:57</t>
+        </is>
+      </c>
+      <c r="S744" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T744" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>694bdf32000000001b024f1e</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/694bdf32000000001b024f1e?xsec_token=ABpebqY5EAeh1wTb0F5EWDf9S3RvOLVoT1yAF17O-Tkn0&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>2820</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>553</t>
+        </is>
+      </c>
+      <c r="M745" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N745" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O745" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P745" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121237/f04ad3d55f4fc8368481cea32ae0206f/1040g00831qfn9ef8ngj04a7r1e8cb33v993q2co!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q745" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R745" t="inlineStr">
+        <is>
+          <t>2025-12-24 20:40:18</t>
+        </is>
+      </c>
+      <c r="S745" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T745" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>694bdf32000000001b024f1e</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/694bdf32000000001b024f1e?xsec_token=ABpebqY5EAeh1wTb0F5EWDf9S3RvOLVoT1yAF17O-Tkn0&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>2820</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>553</t>
+        </is>
+      </c>
+      <c r="M746" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N746" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O746" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P746" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121241/3c49310fa98ab79078aad1bcc0bee0b0/1040g00831qfn9ef8ngj04a7r1e8cb33v993q2co!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q746" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R746" t="inlineStr">
+        <is>
+          <t>2025-12-24 20:40:18</t>
+        </is>
+      </c>
+      <c r="S746" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T746" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>694a12fc000000000d03b349</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/694a12fc000000000d03b349?xsec_token=ABpzXWZRKIAnbGjU-cBBSr6wfe8Lb8j-WH19eSUqK6MrQ&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>喜欢澳门美食小吃</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]# #澳门美食[话题]# #文记饼家[话题]#</t>
+        </is>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>1956</t>
+        </is>
+      </c>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="M747" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N747" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O747" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P747" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121242/809be69be05d1302b1174fe041e4dda4/1040g00831qdufhhc7o904a7r1e8cb33vnuq9kog!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q747" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍', '澳门美食', '文记饼家']</t>
+        </is>
+      </c>
+      <c r="R747" t="inlineStr">
+        <is>
+          <t>2025-12-23 11:56:44</t>
+        </is>
+      </c>
+      <c r="S747" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T747" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>694a12fc000000000d03b349</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/694a12fc000000000d03b349?xsec_token=ABpzXWZRKIAnbGjU-cBBSr6wfe8Lb8j-WH19eSUqK6MrQ&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>喜欢澳门美食小吃</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]# #澳门美食[话题]# #文记饼家[话题]#</t>
+        </is>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>1956</t>
+        </is>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="M748" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N748" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O748" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P748" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121246/4c0ab92ff1456731d1dc68fb444a266a/1040g00831qdufhhc7o904a7r1e8cb33vnuq9kog!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q748" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍', '澳门美食', '文记饼家']</t>
+        </is>
+      </c>
+      <c r="R748" t="inlineStr">
+        <is>
+          <t>2025-12-23 11:56:44</t>
+        </is>
+      </c>
+      <c r="S748" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T748" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>694a12510000000019027830</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/694a12510000000019027830?xsec_token=ABpzXWZRKIAnbGjU-cBBSr60t1wufseEVn9bENfokcCBI&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>1960</t>
+        </is>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="M749" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N749" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O749" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P749" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121248/b3d734c199d86ad57c6c5a58fcee6fa2/1040g00831qdufhhc7oc04a7r1e8cb33vjgc6uog!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q749" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R749" t="inlineStr">
+        <is>
+          <t>2025-12-23 11:53:53</t>
+        </is>
+      </c>
+      <c r="S749" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T749" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
+++ b/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T749"/>
+  <dimension ref="A1:T774"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67587,6 +67587,2578 @@
         </is>
       </c>
     </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>694a12510000000019027830</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/694a12510000000019027830?xsec_token=ABpzXWZRKIAnbGjU-cBBSr60t1wufseEVn9bENfokcCBI&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>1960</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="M750" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N750" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O750" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P750" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121251/53cf6e5d6331caed86a8130c5b12a732/1040g00831qdufhhc7oc04a7r1e8cb33vjgc6uog!nd_dft_wlteh_webp_3']</t>
+        </is>
+      </c>
+      <c r="Q750" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R750" t="inlineStr">
+        <is>
+          <t>2025-12-23 11:53:53</t>
+        </is>
+      </c>
+      <c r="S750" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T750" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>6948cc88000000000d03b17f</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6948cc88000000000d03b17f?xsec_token=ABd_DJMaGLNrgWb6BVSyex7Iueov_9CAAy2rgFgWV-NyI&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>节日气氛越来越浓了 休息</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]# #圣诞节礼物[话题]# #圣诞节[话题]#</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>1914</t>
+        </is>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="M751" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N751" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O751" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P751" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121253/2f2b7f47083fed09994c667cc2874d92/1040g2sg31qckds0e0a4g4a7r1e8cb33viph6nv8!nd_dft_wlteh_webp_3']</t>
+        </is>
+      </c>
+      <c r="Q751" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍', '圣诞节礼物', '圣诞节']</t>
+        </is>
+      </c>
+      <c r="R751" t="inlineStr">
+        <is>
+          <t>2025-12-22 12:43:52</t>
+        </is>
+      </c>
+      <c r="S751" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T751" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>6948cc88000000000d03b17f</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6948cc88000000000d03b17f?xsec_token=ABd_DJMaGLNrgWb6BVSyex7Iueov_9CAAy2rgFgWV-NyI&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>节日气氛越来越浓了 休息</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]# #圣诞节礼物[话题]# #圣诞节[话题]#</t>
+        </is>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>1914</t>
+        </is>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="M752" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N752" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O752" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P752" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121257/96c415f0833dbb9b391bda56e86589c1/1040g2sg31qckds0e0a4g4a7r1e8cb33viph6nv8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q752" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍', '圣诞节礼物', '圣诞节']</t>
+        </is>
+      </c>
+      <c r="R752" t="inlineStr">
+        <is>
+          <t>2025-12-22 12:43:52</t>
+        </is>
+      </c>
+      <c r="S752" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T752" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>6947c9b6000000000d03bc3f</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6947c9b6000000000d03bc3f?xsec_token=ABSKCVXQm2yq7JK6mTQgxC2TSmUS8RnWTvgHne-5oJEOI&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>新年吃🐔</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>好吃
+#在小红书随手拍[话题]#@吃货薯 #澳门美食[话题]#</t>
+        </is>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>3191</t>
+        </is>
+      </c>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="L753" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="M753" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N753" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O753" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P753" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121258/d575ad9aedc634dc0a3eaa16f87afc60/1040g2sg31qboqsnr7gi04a7r1e8cb33v4hg7np8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q753" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍', '澳门美食']</t>
+        </is>
+      </c>
+      <c r="R753" t="inlineStr">
+        <is>
+          <t>2025-12-21 18:19:34</t>
+        </is>
+      </c>
+      <c r="S753" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T753" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>6947c9b6000000000d03bc3f</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6947c9b6000000000d03bc3f?xsec_token=ABSKCVXQm2yq7JK6mTQgxC2TSmUS8RnWTvgHne-5oJEOI&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>新年吃🐔</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>好吃
+#在小红书随手拍[话题]#@吃货薯 #澳门美食[话题]#</t>
+        </is>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>3191</t>
+        </is>
+      </c>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="M754" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N754" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O754" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P754" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121302/f5429dea548b752f8e3fc66d86e9ab78/1040g2sg31qboqsnr7gi04a7r1e8cb33v4hg7np8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q754" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍', '澳门美食']</t>
+        </is>
+      </c>
+      <c r="R754" t="inlineStr">
+        <is>
+          <t>2025-12-21 18:19:34</t>
+        </is>
+      </c>
+      <c r="S754" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T754" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>69449d1b000000001b032ea1</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69449d1b000000001b032ea1?xsec_token=ABA_dJKonpO0UDUvXFbSA0n2Pxq1fW76M7e62jZ0J9EaY&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="L755" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="M755" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N755" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O755" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P755" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121303/beba82514cde624fc2ae7e260615dd63/1040g00831q8ke9lqnu3g4a7r1e8cb33vf1seqpo!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q755" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R755" t="inlineStr">
+        <is>
+          <t>2025-12-19 08:32:27</t>
+        </is>
+      </c>
+      <c r="S755" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T755" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>69449d1b000000001b032ea1</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69449d1b000000001b032ea1?xsec_token=ABA_dJKonpO0UDUvXFbSA0n2Pxq1fW76M7e62jZ0J9EaY&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="L756" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="M756" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N756" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O756" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P756" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121307/bff1d1f67db1380a9693cdb4a750d300/1040g00831q8ke9lqnu3g4a7r1e8cb33vf1seqpo!nd_dft_wlteh_webp_3']</t>
+        </is>
+      </c>
+      <c r="Q756" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R756" t="inlineStr">
+        <is>
+          <t>2025-12-19 08:32:27</t>
+        </is>
+      </c>
+      <c r="S756" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T756" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>69449987000000001b03262a</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69449987000000001b03262a?xsec_token=ABA_dJKonpO0UDUvXFbSA0n3ziC0Utsy_01R1ABXdAerc&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="L757" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="M757" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N757" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O757" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P757" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121308/8db7caca55fa14ac0d5e6f6b8b2cb363/1040g00831q8ke9lqnu504a7r1e8cb33vvic4a4g!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q757" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R757" t="inlineStr">
+        <is>
+          <t>2025-12-19 08:17:11</t>
+        </is>
+      </c>
+      <c r="S757" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T757" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>69449987000000001b03262a</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69449987000000001b03262a?xsec_token=ABA_dJKonpO0UDUvXFbSA0n3ziC0Utsy_01R1ABXdAerc&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="L758" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="M758" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N758" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O758" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P758" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121312/b52492ce8a60da46fcbbe3980a8d26e7/1040g00831q8ke9lqnu504a7r1e8cb33vvic4a4g!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q758" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R758" t="inlineStr">
+        <is>
+          <t>2025-12-19 08:17:11</t>
+        </is>
+      </c>
+      <c r="S758" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T758" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>6943e553000000000d037a0c</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6943e553000000000d037a0c?xsec_token=ABcIRDdprh5ih3dc7KnX5T_TY6D0PJB7MMtABUgnsaY6g&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>2377</t>
+        </is>
+      </c>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="L759" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="M759" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N759" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O759" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P759" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121313/179b76ea58b7bb0e0dc8f8f8d189fe59/1040g00831q7vr8f27g5g4a7r1e8cb33vkm4nkm0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q759" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R759" t="inlineStr">
+        <is>
+          <t>2025-12-18 19:28:19</t>
+        </is>
+      </c>
+      <c r="S759" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T759" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>6943e553000000000d037a0c</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6943e553000000000d037a0c?xsec_token=ABcIRDdprh5ih3dc7KnX5T_TY6D0PJB7MMtABUgnsaY6g&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>2377</t>
+        </is>
+      </c>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="L760" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="M760" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N760" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O760" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P760" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121317/e4565610114caaaeb0fe6c01cf1eee84/1040g00831q7vr8f27g5g4a7r1e8cb33vkm4nkm0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q760" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R760" t="inlineStr">
+        <is>
+          <t>2025-12-18 19:28:19</t>
+        </is>
+      </c>
+      <c r="S760" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T760" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>6943c723000000000d00c441</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6943c723000000000d00c441?xsec_token=ABcIRDdprh5ih3dc7KnX5T_dgE6LOoCFCX8XBe7x8USJ4&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>2269</t>
+        </is>
+      </c>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="L761" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="M761" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N761" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O761" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P761" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121318/1f8c958c52bbf5f2f07eadb116ed4c4c/1040g00831q7pe8r00a4g4a7r1e8cb33vsdhmvf0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q761" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R761" t="inlineStr">
+        <is>
+          <t>2025-12-18 17:19:32</t>
+        </is>
+      </c>
+      <c r="S761" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T761" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>6943c723000000000d00c441</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6943c723000000000d00c441?xsec_token=ABcIRDdprh5ih3dc7KnX5T_dgE6LOoCFCX8XBe7x8USJ4&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>2269</t>
+        </is>
+      </c>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="L762" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="M762" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N762" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O762" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P762" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121322/431fd6d7d0686a9baab45b2e4f8a4031/1040g00831q7pe8r00a4g4a7r1e8cb33vsdhmvf0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q762" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R762" t="inlineStr">
+        <is>
+          <t>2025-12-18 17:19:32</t>
+        </is>
+      </c>
+      <c r="S762" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T762" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>6940bf19000000000d03c666</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6940bf19000000000d03c666?xsec_token=ABkxOXMbSwxXcqBz2DU6t2Oa7ha61IhDxiR61rO3-tV1Y&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>1831</t>
+        </is>
+      </c>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="L763" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="M763" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N763" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O763" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P763" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121324/7ccabecdf094d3fd86242bc355e2fa09/1040g00831q4ql4f57o304a7r1e8cb33v8vvd7bo!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q763" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R763" t="inlineStr">
+        <is>
+          <t>2025-12-16 10:08:25</t>
+        </is>
+      </c>
+      <c r="S763" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T763" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>6940bf19000000000d03c666</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6940bf19000000000d03c666?xsec_token=ABkxOXMbSwxXcqBz2DU6t2Oa7ha61IhDxiR61rO3-tV1Y&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>1831</t>
+        </is>
+      </c>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="L764" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="M764" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N764" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O764" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P764" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121327/689a2c506124800ef6c7871f1160c1d8/1040g00831q4ql4f57o304a7r1e8cb33v8vvd7bo!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q764" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R764" t="inlineStr">
+        <is>
+          <t>2025-12-16 10:08:25</t>
+        </is>
+      </c>
+      <c r="S764" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T764" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>693fcdb3000000001b025c52</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693fcdb3000000001b025c52?xsec_token=ABWIg2ygkFhhHM62ouFjlh2nOvHAYsq5L_kQEZnYcA_kQ&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>深圳下次再来</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>牛马的我[泪崩R][泪崩R] 为了家人们 上海 深圳飞一下
+真的饭也没吃  水也没喝 现在回去了
+#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J765" t="inlineStr">
+        <is>
+          <t>1802</t>
+        </is>
+      </c>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="L765" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="M765" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N765" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O765" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P765" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121329/f212ac3bc6a50ea44e1d6f80f9836131/notes_pre_post/1040g3k031q3pr3l87u304a7r1e8cb33vj0helig!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q765" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R765" t="inlineStr">
+        <is>
+          <t>2025-12-15 16:58:27</t>
+        </is>
+      </c>
+      <c r="S765" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T765" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>693fcdb3000000001b025c52</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693fcdb3000000001b025c52?xsec_token=ABWIg2ygkFhhHM62ouFjlh2nOvHAYsq5L_kQEZnYcA_kQ&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>深圳下次再来</t>
+        </is>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>牛马的我[泪崩R][泪崩R] 为了家人们 上海 深圳飞一下
+真的饭也没吃  水也没喝 现在回去了
+#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>1802</t>
+        </is>
+      </c>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="L766" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="M766" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N766" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O766" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P766" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121332/afab683d60f8beb3c4a3b5342efdb3d6/notes_pre_post/1040g3k031q3pr3l87u304a7r1e8cb33vj0helig!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q766" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R766" t="inlineStr">
+        <is>
+          <t>2025-12-15 16:58:27</t>
+        </is>
+      </c>
+      <c r="S766" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T766" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>693f7097000000001b0331de</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693f7097000000001b0331de?xsec_token=ABWIg2ygkFhhHM62ouFjlh2mEqG5msX4JlUS9vy11enqU&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>嗖</t>
+        </is>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>＋5000到帐#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J767" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="L767" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="M767" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N767" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O767" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P767" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121334/bd8c5a4558b796da1e5f32b91eb2e7c4/notes_pre_post/1040g3k831q3jjinf7gpg4a7r1e8cb33vb4hsleo!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q767" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R767" t="inlineStr">
+        <is>
+          <t>2025-12-15 10:21:11</t>
+        </is>
+      </c>
+      <c r="S767" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T767" t="inlineStr">
+        <is>
+          <t>图1: 无</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>693f7097000000001b0331de</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693f7097000000001b0331de?xsec_token=ABWIg2ygkFhhHM62ouFjlh2mEqG5msX4JlUS9vy11enqU&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>嗖</t>
+        </is>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>＋5000到帐#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="L768" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="M768" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N768" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O768" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P768" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121337/8a37da18db3af6c45c5329b727c7c8d9/notes_pre_post/1040g3k831q3jjinf7gpg4a7r1e8cb33vb4hsleo!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q768" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R768" t="inlineStr">
+        <is>
+          <t>2025-12-15 10:21:11</t>
+        </is>
+      </c>
+      <c r="S768" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T768" t="inlineStr">
+        <is>
+          <t>图1: 无</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>693f6edf000000000d035dda</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693f6edf000000000d035dda?xsec_token=ABWIg2ygkFhhHM62ouFjlh2jU2_BDOxR86jVItuu-yha8&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>好巧</t>
+        </is>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>可能是巧合 可能是可能我也不知道
+今天邀请我去参观的上市公司
+确实就是中国平安
+好巧[捂嘴笑R]
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J769" t="inlineStr">
+        <is>
+          <t>1972</t>
+        </is>
+      </c>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="L769" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="M769" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N769" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O769" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P769" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121339/45dd42a3de0cf117b45e85bbcbda08c0/notes_pre_post/1040g3k831q3kg8egg0004a7r1e8cb33vmms1psg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q769" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R769" t="inlineStr">
+        <is>
+          <t>2025-12-15 10:13:51</t>
+        </is>
+      </c>
+      <c r="S769" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T769" t="inlineStr">
+        <is>
+          <t>图1: 无</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>693f6edf000000000d035dda</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693f6edf000000000d035dda?xsec_token=ABWIg2ygkFhhHM62ouFjlh2jU2_BDOxR86jVItuu-yha8&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>好巧</t>
+        </is>
+      </c>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>可能是巧合 可能是可能我也不知道
+今天邀请我去参观的上市公司
+确实就是中国平安
+好巧[捂嘴笑R]
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J770" t="inlineStr">
+        <is>
+          <t>1972</t>
+        </is>
+      </c>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="L770" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="M770" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N770" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O770" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P770" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121342/4dc2cbe04e56c89a63d2f5ab4835e1a0/notes_pre_post/1040g3k831q3kg8egg0004a7r1e8cb33vmms1psg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q770" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R770" t="inlineStr">
+        <is>
+          <t>2025-12-15 10:13:51</t>
+        </is>
+      </c>
+      <c r="S770" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T770" t="inlineStr">
+        <is>
+          <t>图1: 无</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>693f6832000000001b0230b9</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693f6832000000001b0230b9?xsec_token=ABWIg2ygkFhhHM62ouFjlh2ipf8edf74sG-VUou1wIc54&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>好日子</t>
+        </is>
+      </c>
+      <c r="I771" t="inlineStr">
+        <is>
+          <t>再飞机上 喜提平安姑娘突破目标65～
+开心
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J771" t="inlineStr">
+        <is>
+          <t>1810</t>
+        </is>
+      </c>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="L771" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="M771" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N771" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O771" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P771" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121344/6fa4af24ace313d3ff0877e91a44a948/notes_pre_post/1040g3k831q3jjt1jg0004a7r1e8cb33v1t25i20!nd_dft_wgth_jpg_3', 'http://sns-webpic-qc.xhscdn.com/202602121344/f357cc8076f084928b018db99d0082a7/notes_pre_post/1040g3k831q3jjinf7grg4a7r1e8cb33vqlln538!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q771" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R771" t="inlineStr">
+        <is>
+          <t>2025-12-15 09:45:22</t>
+        </is>
+      </c>
+      <c r="S771" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T771" t="inlineStr">
+        <is>
+          <t>图1: 无 | 图2: 无</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>693f6832000000001b0230b9</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693f6832000000001b0230b9?xsec_token=ABWIg2ygkFhhHM62ouFjlh2ipf8edf74sG-VUou1wIc54&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>好日子</t>
+        </is>
+      </c>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>再飞机上 喜提平安姑娘突破目标65～
+开心
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J772" t="inlineStr">
+        <is>
+          <t>1810</t>
+        </is>
+      </c>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="L772" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="M772" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N772" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O772" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P772" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121348/3dc6d960c9e2a9c6107773b9981511e5/notes_pre_post/1040g3k831q3jjt1jg0004a7r1e8cb33v1t25i20!nd_dft_wgth_jpg_3', 'http://sns-webpic-qc.xhscdn.com/202602121348/3b7ca895b151ebbff0eb6a705222ad1b/notes_pre_post/1040g3k831q3jjinf7grg4a7r1e8cb33vqlln538!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q772" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R772" t="inlineStr">
+        <is>
+          <t>2025-12-15 09:45:22</t>
+        </is>
+      </c>
+      <c r="S772" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T772" t="inlineStr">
+        <is>
+          <t>图1: 无 | 图2: 无</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>693f465a000000000d036384</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693f465a000000000d036384?xsec_token=ABWIg2ygkFhhHM62ouFjlh2qgaj8a1yz2N-_w7oeVc0_k&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>收益差～继续吃面</t>
+        </is>
+      </c>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>这周要对抗下市场
+逆势用新策略了
+#吃吃喝喝又一天[话题]# #我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J773" t="inlineStr">
+        <is>
+          <t>1608</t>
+        </is>
+      </c>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="L773" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="M773" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N773" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O773" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P773" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121349/9b05a54af6afa99202863a737a8f02e0/notes_pre_post/1040g3k031q2u5st3no4g4a7r1e8cb33v2gi0n10!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q773" t="inlineStr">
+        <is>
+          <t>['吃吃喝喝又一天', '我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R773" t="inlineStr">
+        <is>
+          <t>2025-12-15 07:20:58</t>
+        </is>
+      </c>
+      <c r="S773" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T773" t="inlineStr">
+        <is>
+          <t>图1: 无</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>693f465a000000000d036384</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693f465a000000000d036384?xsec_token=ABWIg2ygkFhhHM62ouFjlh2qgaj8a1yz2N-_w7oeVc0_k&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>收益差～继续吃面</t>
+        </is>
+      </c>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>这周要对抗下市场
+逆势用新策略了
+#吃吃喝喝又一天[话题]# #我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J774" t="inlineStr">
+        <is>
+          <t>1608</t>
+        </is>
+      </c>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="L774" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="M774" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N774" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O774" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P774" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121353/74001bd516d2b96219ee5156e376f0f1/notes_pre_post/1040g3k031q2u5st3no4g4a7r1e8cb33v2gi0n10!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q774" t="inlineStr">
+        <is>
+          <t>['吃吃喝喝又一天', '我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R774" t="inlineStr">
+        <is>
+          <t>2025-12-15 07:20:58</t>
+        </is>
+      </c>
+      <c r="S774" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T774" t="inlineStr">
+        <is>
+          <t>图1: 无</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
+++ b/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T783"/>
+  <dimension ref="A1:T798"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50012,6 +50012,1572 @@
         </is>
       </c>
     </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>693d084c000000001b025a95</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693d084c000000001b025a95?xsec_token=ABy2m4isaQWo7lzemDfMeoxB-TMt4uTVrSGNxhE_9pGhU&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>每年都有热点 跟爆发点
+2024我的选择#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J784" t="inlineStr">
+        <is>
+          <t>1647</t>
+        </is>
+      </c>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="L784" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="M784" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N784" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O784" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P784" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121632/c015fd802136d82680ff06bc899cf2e6/notes_pre_post/1040g3k831q19f6lcg0cg4a7r1e8cb33vg4r4o6g!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q784" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R784" t="inlineStr">
+        <is>
+          <t>2025-12-13 14:31:40</t>
+        </is>
+      </c>
+      <c r="S784" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T784" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>693d084c000000001b025a95</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693d084c000000001b025a95?xsec_token=ABy2m4isaQWo7lzemDfMeoxB-TMt4uTVrSGNxhE_9pGhU&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>每年都有热点 跟爆发点
+2024我的选择#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J785" t="inlineStr">
+        <is>
+          <t>1647</t>
+        </is>
+      </c>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="L785" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="M785" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N785" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O785" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P785" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121632/c015fd802136d82680ff06bc899cf2e6/notes_pre_post/1040g3k831q19f6lcg0cg4a7r1e8cb33vg4r4o6g!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q785" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R785" t="inlineStr">
+        <is>
+          <t>2025-12-13 14:31:40</t>
+        </is>
+      </c>
+      <c r="S785" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T785" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>693cde02000000001b0313ff</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693cde02000000001b0313ff?xsec_token=ABQbHUKCSRi4YTWdP6Tyky_seyywQyebhM-YfJMUkAlqs&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>明年很一般</t>
+        </is>
+      </c>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>刚复盘测算
+我2026年收益率大概
+13-15％ 成绩不会很好
+会比今年更低 所以私信留言期待超高收益的朋友
+请另寻高明
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J786" t="inlineStr">
+        <is>
+          <t>1913</t>
+        </is>
+      </c>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="L786" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="M786" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="N786" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O786" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P786" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121638/133f0bff00b0d709831ebd0acbc2fc82/1040g00831q11je83g0504a7r1e8cb33vds4r800!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q786" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R786" t="inlineStr">
+        <is>
+          <t>2025-12-13 11:31:14</t>
+        </is>
+      </c>
+      <c r="S786" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T786" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>693cde02000000001b0313ff</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693cde02000000001b0313ff?xsec_token=ABQbHUKCSRi4YTWdP6Tyky_seyywQyebhM-YfJMUkAlqs&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>明年很一般</t>
+        </is>
+      </c>
+      <c r="I787" t="inlineStr">
+        <is>
+          <t>刚复盘测算
+我2026年收益率大概
+13-15％ 成绩不会很好
+会比今年更低 所以私信留言期待超高收益的朋友
+请另寻高明
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J787" t="inlineStr">
+        <is>
+          <t>1913</t>
+        </is>
+      </c>
+      <c r="K787" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="L787" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="M787" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="N787" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O787" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P787" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121638/133f0bff00b0d709831ebd0acbc2fc82/1040g00831q11je83g0504a7r1e8cb33vds4r800!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q787" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R787" t="inlineStr">
+        <is>
+          <t>2025-12-13 11:31:14</t>
+        </is>
+      </c>
+      <c r="S787" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T787" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>693cca8c000000000d038202</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693cca8c000000000d038202?xsec_token=ABQbHUKCSRi4YTWdP6Tyky_snDjPzbG8OLgFlBBonBzfY&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>冷知识
+这么冷的天
+如果停电[黑薯问号R]
+停燃气 会如何
+#冬季用电安全[话题]# #奇妙的知识[话题]# #省电[话题]# #每天一个小知识[话题]# #静电[话题]# #供暖[话题]# #有趣的知识[话题]# #有趣的知识又增长了[话题]# #冷知识[话题]# #每天跟我涨知识[话题]#</t>
+        </is>
+      </c>
+      <c r="J788" t="inlineStr">
+        <is>
+          <t>3530</t>
+        </is>
+      </c>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="L788" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="M788" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="N788" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O788" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P788" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121643/c29e1d0780d987f9f0f8fa3d4d2def37/1040g00831q11je83g0604a7r1e8cb33v0p25vto!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q788" t="inlineStr">
+        <is>
+          <t>['冬季用电安全', '奇妙的知识', '省电', '每天一个小知识', '静电', '供暖', '有趣的知识', '有趣的知识又增长了', '冷知识', '每天跟我涨知识']</t>
+        </is>
+      </c>
+      <c r="R788" t="inlineStr">
+        <is>
+          <t>2025-12-13 10:08:12</t>
+        </is>
+      </c>
+      <c r="S788" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T788" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>693cca8c000000000d038202</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693cca8c000000000d038202?xsec_token=ABQbHUKCSRi4YTWdP6Tyky_snDjPzbG8OLgFlBBonBzfY&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>冷知识
+这么冷的天
+如果停电[黑薯问号R]
+停燃气 会如何
+#冬季用电安全[话题]# #奇妙的知识[话题]# #省电[话题]# #每天一个小知识[话题]# #静电[话题]# #供暖[话题]# #有趣的知识[话题]# #有趣的知识又增长了[话题]# #冷知识[话题]# #每天跟我涨知识[话题]#</t>
+        </is>
+      </c>
+      <c r="J789" t="inlineStr">
+        <is>
+          <t>3530</t>
+        </is>
+      </c>
+      <c r="K789" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="L789" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="M789" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="N789" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O789" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P789" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121643/c29e1d0780d987f9f0f8fa3d4d2def37/1040g00831q11je83g0604a7r1e8cb33v0p25vto!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q789" t="inlineStr">
+        <is>
+          <t>['冬季用电安全', '奇妙的知识', '省电', '每天一个小知识', '静电', '供暖', '有趣的知识', '有趣的知识又增长了', '冷知识', '每天跟我涨知识']</t>
+        </is>
+      </c>
+      <c r="R789" t="inlineStr">
+        <is>
+          <t>2025-12-13 10:08:12</t>
+        </is>
+      </c>
+      <c r="S789" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T789" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>693cc7a7000000001b023605</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693cc7a7000000001b023605?xsec_token=ABQbHUKCSRi4YTWdP6Tyky_hL-YFeAPVfFyTVNZVV-33Q&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>我期待</t>
+        </is>
+      </c>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>放量 一次吧
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J790" t="inlineStr">
+        <is>
+          <t>1591</t>
+        </is>
+      </c>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="L790" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="M790" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N790" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O790" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P790" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121649/3eff7fb5c185eaeb73d1a2dcd5d03b24/notes_pre_post/1040g3k831q11jeeungdg4a7r1e8cb33v07lruhg!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q790" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R790" t="inlineStr">
+        <is>
+          <t>2025-12-13 09:55:51</t>
+        </is>
+      </c>
+      <c r="S790" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T790" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>693cc7a7000000001b023605</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693cc7a7000000001b023605?xsec_token=ABQbHUKCSRi4YTWdP6Tyky_hL-YFeAPVfFyTVNZVV-33Q&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>我期待</t>
+        </is>
+      </c>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>放量 一次吧
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J791" t="inlineStr">
+        <is>
+          <t>1591</t>
+        </is>
+      </c>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="L791" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="M791" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N791" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O791" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P791" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121649/3eff7fb5c185eaeb73d1a2dcd5d03b24/notes_pre_post/1040g3k831q11jeeungdg4a7r1e8cb33v07lruhg!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q791" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R791" t="inlineStr">
+        <is>
+          <t>2025-12-13 09:55:51</t>
+        </is>
+      </c>
+      <c r="S791" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T791" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>693c2bda000000000d0386e9</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693c2bda000000000d0386e9?xsec_token=ABQbHUKCSRi4YTWdP6Tyky_kZFwAazjX7fsO_hr0oOF9w&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t>周末要事
+2025年分享 周上 周下 1％ 买卖call后
+2026年升级一下
+我把2007年-2015年的趋势周滚动法
+会再分享个策略出来
+#我的炒股日记[话题]# #投资理财[话题]# #投资需谨慎[话题]# #风险与回报[话题]# #股票[话题]# #投资[话题]# #小白来理财[话题]# #金融投资[话题]# #财经知识[话题]# #个人投资者[话题]#</t>
+        </is>
+      </c>
+      <c r="J792" t="inlineStr">
+        <is>
+          <t>3096</t>
+        </is>
+      </c>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="L792" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="M792" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N792" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O792" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P792" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121655/698874d348e9012c30c82bec1fa2be4d/1040g2sg31q0dbjg67oig4a7r1e8cb33vunouud0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q792" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '投资理财', '投资需谨慎', '风险与回报', '股票', '投资', '小白来理财', '金融投资', '财经知识', '个人投资者']</t>
+        </is>
+      </c>
+      <c r="R792" t="inlineStr">
+        <is>
+          <t>2025-12-12 22:51:06</t>
+        </is>
+      </c>
+      <c r="S792" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T792" t="inlineStr">
+        <is>
+          <t>图1: n, a, o, t, o, e, e, e, e, e, e, e, i, e, e</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>693c2bda000000000d0386e9</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693c2bda000000000d0386e9?xsec_token=ABQbHUKCSRi4YTWdP6Tyky_kZFwAazjX7fsO_hr0oOF9w&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>周末要事
+2025年分享 周上 周下 1％ 买卖call后
+2026年升级一下
+我把2007年-2015年的趋势周滚动法
+会再分享个策略出来
+#我的炒股日记[话题]# #投资理财[话题]# #投资需谨慎[话题]# #风险与回报[话题]# #股票[话题]# #投资[话题]# #小白来理财[话题]# #金融投资[话题]# #财经知识[话题]# #个人投资者[话题]#</t>
+        </is>
+      </c>
+      <c r="J793" t="inlineStr">
+        <is>
+          <t>3096</t>
+        </is>
+      </c>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="L793" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="M793" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N793" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O793" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P793" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121655/698874d348e9012c30c82bec1fa2be4d/1040g2sg31q0dbjg67oig4a7r1e8cb33vunouud0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q793" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '投资理财', '投资需谨慎', '风险与回报', '股票', '投资', '小白来理财', '金融投资', '财经知识', '个人投资者']</t>
+        </is>
+      </c>
+      <c r="R793" t="inlineStr">
+        <is>
+          <t>2025-12-12 22:51:06</t>
+        </is>
+      </c>
+      <c r="S793" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T793" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>693c25f9000000001b022519</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693c25f9000000001b022519?xsec_token=ABQbHUKCSRi4YTWdP6Tyky_np564oA1k_EDY_TBkaUEIQ&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>公告
+我没小号
+那个以注销
+大家切记
+不要上当</t>
+        </is>
+      </c>
+      <c r="J794" t="inlineStr">
+        <is>
+          <t>1617</t>
+        </is>
+      </c>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="L794" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="N794" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O794" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P794" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121701/d69a0ec82a3d4a1c55251a19e662ad52/1040g2sg31q0dbjg67ohg4a7r1e8cb33v6jh7l0o!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q794" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R794" t="inlineStr">
+        <is>
+          <t>2025-12-12 22:26:01</t>
+        </is>
+      </c>
+      <c r="S794" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T794" t="inlineStr">
+        <is>
+          <t>图1: SNARETUURLIFEHERE.V, 公告, 我没小号, 那个以注销, 大家切记, 不要上当</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>693c25f9000000001b022519</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693c25f9000000001b022519?xsec_token=ABQbHUKCSRi4YTWdP6Tyky_np564oA1k_EDY_TBkaUEIQ&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>公告
+我没小号
+那个以注销
+大家切记
+不要上当</t>
+        </is>
+      </c>
+      <c r="J795" t="inlineStr">
+        <is>
+          <t>1617</t>
+        </is>
+      </c>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="L795" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="N795" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O795" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P795" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121700/810283ee821ca1fc4173bab24f4c6d54/1040g2sg31q0dbjg67ohg4a7r1e8cb33v6jh7l0o!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q795" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R795" t="inlineStr">
+        <is>
+          <t>2025-12-12 22:26:01</t>
+        </is>
+      </c>
+      <c r="S795" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T795" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>693c21c5000000000d03640a</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693c21c5000000000d03640a?xsec_token=ABQbHUKCSRi4YTWdP6Tyky_uA7KRvAnoIM0zwXA0C8axM&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>你们快乐
+所以我快了
+大家周末快乐
+#快乐[话题]# #欢乐[话题]# #快乐是什么[话题]# #快乐的意义[话题]# #快乐哪有那么难[话题]# #寻找快乐能量[话题]# #记录周末事宜[话题]# #周末精神状态[话题]# #周末[话题]# #快乐无极限[话题]#</t>
+        </is>
+      </c>
+      <c r="J796" t="inlineStr">
+        <is>
+          <t>1912</t>
+        </is>
+      </c>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="L796" t="inlineStr">
+        <is>
+          <t>471</t>
+        </is>
+      </c>
+      <c r="M796" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N796" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O796" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P796" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121706/aeff12e755a32120e426ac3510a30344/1040g2sg31q0dbjg67ok04a7r1e8cb33vg83llkg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q796" t="inlineStr">
+        <is>
+          <t>['快乐', '欢乐', '快乐是什么', '快乐的意义', '快乐哪有那么难', '寻找快乐能量', '记录周末事宜', '周末精神状态', '周末', '快乐无极限']</t>
+        </is>
+      </c>
+      <c r="R796" t="inlineStr">
+        <is>
+          <t>2025-12-12 22:08:05</t>
+        </is>
+      </c>
+      <c r="S796" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T796" t="inlineStr">
+        <is>
+          <t>图1: ”, 你们快乐, 所以我快了, 大家周末快乐</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>693c21c5000000000d03640a</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693c21c5000000000d03640a?xsec_token=ABQbHUKCSRi4YTWdP6Tyky_uA7KRvAnoIM0zwXA0C8axM&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I797" t="inlineStr">
+        <is>
+          <t>你们快乐
+所以我快了
+大家周末快乐
+#快乐[话题]# #欢乐[话题]# #快乐是什么[话题]# #快乐的意义[话题]# #快乐哪有那么难[话题]# #寻找快乐能量[话题]# #记录周末事宜[话题]# #周末精神状态[话题]# #周末[话题]# #快乐无极限[话题]#</t>
+        </is>
+      </c>
+      <c r="J797" t="inlineStr">
+        <is>
+          <t>1912</t>
+        </is>
+      </c>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="L797" t="inlineStr">
+        <is>
+          <t>471</t>
+        </is>
+      </c>
+      <c r="M797" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N797" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O797" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P797" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121706/aeff12e755a32120e426ac3510a30344/1040g2sg31q0dbjg67ok04a7r1e8cb33vg83llkg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q797" t="inlineStr">
+        <is>
+          <t>['快乐', '欢乐', '快乐是什么', '快乐的意义', '快乐哪有那么难', '寻找快乐能量', '记录周末事宜', '周末精神状态', '周末', '快乐无极限']</t>
+        </is>
+      </c>
+      <c r="R797" t="inlineStr">
+        <is>
+          <t>2025-12-12 22:08:05</t>
+        </is>
+      </c>
+      <c r="S797" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T797" t="inlineStr">
+        <is>
+          <t>图1: OCR超时</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>693bcc33000000001b020f26</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693bcc33000000001b020f26?xsec_token=ABRlWlQ8-y__HYpWhp1Gi4AGXA9-ELA5L1XQUaA4JVFWc&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J798" t="inlineStr">
+        <is>
+          <t>2232</t>
+        </is>
+      </c>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="L798" t="inlineStr">
+        <is>
+          <t>383</t>
+        </is>
+      </c>
+      <c r="M798" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N798" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O798" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P798" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121712/f786279f1ffa26b267d4ba9f2be09bde/1040g00831q02p64a7g304a7r1e8cb33vekl13uo!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q798" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R798" t="inlineStr">
+        <is>
+          <t>2025-12-12 16:02:59</t>
+        </is>
+      </c>
+      <c r="S798" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T798" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
+++ b/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T798"/>
+  <dimension ref="A1:T814"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51578,6 +51578,1700 @@
         </is>
       </c>
     </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>693bcb7b000000000d00ed61</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693bcb7b000000000d00ed61?xsec_token=ABRlWlQ8-y__HYpWhp1Gi4AB0zeHZwojIIbORhN8d4NtY&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>快乐的周末</t>
+        </is>
+      </c>
+      <c r="I799" t="inlineStr">
+        <is>
+          <t>#愉悦的心情[话题]# #我的炒股日记[话题]# #开启周末模式[话题]# #周末溜自己[话题]# #周末愉快[话题]# #每周出去玩[话题]# #快乐的时光总是短暂的[话题]# #工作之外的乐趣[话题]# #抓住假期的尾巴[话题]# #有趣的周末[话题]#</t>
+        </is>
+      </c>
+      <c r="J799" t="inlineStr">
+        <is>
+          <t>2039</t>
+        </is>
+      </c>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="L799" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="M799" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="N799" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O799" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P799" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121717/5e2dafbe63c3e9dc3422de444ff0508e/1040g00831q02p64a7g6g4a7r1e8cb33vi4n23fg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q799" t="inlineStr">
+        <is>
+          <t>['愉悦的心情', '我的炒股日记', '开启周末模式', '周末溜自己', '周末愉快', '每周出去玩', '快乐的时光总是短暂的', '工作之外的乐趣', '抓住假期的尾巴', '有趣的周末']</t>
+        </is>
+      </c>
+      <c r="R799" t="inlineStr">
+        <is>
+          <t>2025-12-12 15:59:55</t>
+        </is>
+      </c>
+      <c r="S799" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T799" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>693bab15000000001b0323d9</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693bab15000000001b0323d9?xsec_token=ABRlWlQ8-y__HYpWhp1Gi4ADUrFvxIQzWndNWjXA_zoxM&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>控制仙境
+别高调
+休息#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>1758</t>
+        </is>
+      </c>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="L800" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="M800" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N800" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O800" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P800" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121722/f34ea07929314c15e1fb75171932b552/1040g00831pvr75o6nu4g4a7r1e8cb33v7gtten0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q800" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R800" t="inlineStr">
+        <is>
+          <t>2025-12-12 13:41:41</t>
+        </is>
+      </c>
+      <c r="S800" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T800" t="inlineStr">
+        <is>
+          <t>图1: 控制仙境, 别高调, 休息</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>693b9994000000001b026011</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693b9994000000001b026011?xsec_token=ABRlWlQ8-y__HYpWhp1Gi4ABZ5cx0yOmyzZMkIMWWQWKI=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>对抗市场</t>
+        </is>
+      </c>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>继续吃面今天[偷笑R][偷笑R][偷笑R]
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J801" t="inlineStr">
+        <is>
+          <t>1568</t>
+        </is>
+      </c>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="L801" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="M801" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N801" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O801" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P801" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121813/4744c4c1d37205ea2d53aae1c1e36632/notes_pre_post/1040g3k831pvsevf9nod04a7r1e8cb33vrm65coo!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q801" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R801" t="inlineStr">
+        <is>
+          <t>2025-12-12 12:27:00</t>
+        </is>
+      </c>
+      <c r="S801" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T801" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>693b9756000000000d0399be</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693b9756000000000d0399be?xsec_token=ABRlWlQ8-y__HYpWhp1Gi4AGmP5gL6CqfXams8Xj_gbcs=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>收益差 中午只能吃一份蔬菜</t>
+        </is>
+      </c>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>[泪崩R]#我的炒股日记[话题]#
+#招商银行[话题]#</t>
+        </is>
+      </c>
+      <c r="J802" t="inlineStr">
+        <is>
+          <t>1407</t>
+        </is>
+      </c>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="L802" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="M802" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N802" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O802" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P802" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121828/e59700b64941a47cd252a5dfcf973f78/notes_pre_post/1040g3k831pvsevf9nodg4a7r1e8cb33vlkie05g!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q802" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '招商银行']</t>
+        </is>
+      </c>
+      <c r="R802" t="inlineStr">
+        <is>
+          <t>2025-12-12 12:17:26</t>
+        </is>
+      </c>
+      <c r="S802" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T802" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>693b935a000000000d00e6eb</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693b935a000000000d00e6eb?xsec_token=ABRlWlQ8-y__HYpWhp1Gi4AEb3oGED09fF4gSLR57ueco=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>休息 逛街</t>
+        </is>
+      </c>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>最近
+难度很高
+仙境 留好
+好好休息
+暂时休息 休息
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J803" t="inlineStr">
+        <is>
+          <t>1731</t>
+        </is>
+      </c>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="L803" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="M803" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N803" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O803" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P803" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121843/11f05b5377e5a83b52ddeb9665e3c538/1040g00831pvr75o6nu5g4a7r1e8cb33vor4th2o!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q803" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R803" t="inlineStr">
+        <is>
+          <t>2025-12-12 12:00:27</t>
+        </is>
+      </c>
+      <c r="S803" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T803" t="inlineStr">
+        <is>
+          <t>图1: ”, 最近, 难度很高, 仙境, 留好, 好好休息, 暂时休息休息</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>693b8d30000000000d03e1a0</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693b8d30000000000d03e1a0?xsec_token=ABRlWlQ8-y__HYpWhp1Gi4AGVPGZtbv_Zsk8NnTP2mTEI=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I804" t="inlineStr">
+        <is>
+          <t>我再思考人生
+如何心灵自由
+如何屏蔽日线的波动
+如何坚持低波动红利策略
+如何一直赢
+#人生自由基金[话题]#</t>
+        </is>
+      </c>
+      <c r="J804" t="inlineStr">
+        <is>
+          <t>1840</t>
+        </is>
+      </c>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="L804" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="M804" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N804" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O804" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P804" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121849/0a488f0bbf7085faf1635d45a8333241/1040g00831pvr75o6nu6g4a7r1e8cb33vjkan408!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q804" t="inlineStr">
+        <is>
+          <t>['人生自由基金']</t>
+        </is>
+      </c>
+      <c r="R804" t="inlineStr">
+        <is>
+          <t>2025-12-12 11:34:08</t>
+        </is>
+      </c>
+      <c r="S804" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T804" t="inlineStr">
+        <is>
+          <t>图1: ”, 我再思考人生, 如何心灵自由, 如何屏蔽日线的波动, 如何坚持低波动红利, 策略, 如何一直赢</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>693ae336000000001b021a3a</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693ae336000000001b021a3a?xsec_token=AB2YL2nC9NMcXYXtLxjaIxo2sUhQBAuhwxtSYHm9DZoNo=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>写于6月中旬</t>
+        </is>
+      </c>
+      <c r="I805" t="inlineStr">
+        <is>
+          <t>#自己写点自己的东西[话题]# #一些有感而发[话题]#</t>
+        </is>
+      </c>
+      <c r="J805" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="L805" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="M805" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="N805" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O805" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P805" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121854/de5c91814badcffdd61dd9fc3824c345/notes_pre_post/1040g3k031pv6et077a604a7r1e8cb33vhh39fmg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q805" t="inlineStr">
+        <is>
+          <t>['自己写点自己的东西', '一些有感而发']</t>
+        </is>
+      </c>
+      <c r="R805" t="inlineStr">
+        <is>
+          <t>2025-12-11 23:28:54</t>
+        </is>
+      </c>
+      <c r="S805" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T805" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>693ad6b5000000000d039c30</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693ad6b5000000000d039c30?xsec_token=AB2YL2nC9NMcXYXtLxjaIxoyPIzxWLEgFd-3VDLXItjkU=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>离开以后 -300</t>
+        </is>
+      </c>
+      <c r="I806" t="inlineStr">
+        <is>
+          <t>[泪崩R][泪崩R][泪崩R]
+抛开苦痛去解脱自己
+让我那些冷却热情另有生机
+离开以后我会习惯自卑 -300
+明天再偶遇我也不敢偷望你 -300～
+离开以后季节冷暖天气
+我也置诸不理
+愿名字也再不记起 -300
+离开以后我会长留这地
+晨早到午夜扑进漆黑想念你
+离开以后醉了会看到你
+梦中方可永久地
+接近你
+我会回来的[捂嘴笑R]</t>
+        </is>
+      </c>
+      <c r="J806" t="inlineStr">
+        <is>
+          <t>1604</t>
+        </is>
+      </c>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="L806" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="M806" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N806" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O806" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P806" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121859/ab38c2e0aea7fedb018f251d2bcc8fcf/notes_pre_post/1040g3k831puv9e34nuqg4a7r1e8cb33vleg395o!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q806" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R806" t="inlineStr">
+        <is>
+          <t>2025-12-11 22:35:33</t>
+        </is>
+      </c>
+      <c r="S806" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T806" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>693acf9b000000000d03b4a8</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693acf9b000000000d03b4a8?xsec_token=AB2YL2nC9NMcXYXtLxjaIxo7MUvvf6XbQdom5NW8AWjYk=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>安静</t>
+        </is>
+      </c>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>我想我已表现的非常明白
+我懂我也知道
+她没有真的突破
+她说她也会突破我不相信
+买着她套着你
+也只是曾经
+希望她是真的突破放你出来
+我才会逼自己加仓[暗中观察R]#简单的心境[话题]#</t>
+        </is>
+      </c>
+      <c r="J807" t="inlineStr">
+        <is>
+          <t>1587</t>
+        </is>
+      </c>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="L807" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="M807" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N807" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O807" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P807" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121904/d3f923816f6b4f1f0dac99e3b381a837/notes_pre_post/1040g3k831puv9e34nuq04a7r1e8cb33ve7d5nuo!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q807" t="inlineStr">
+        <is>
+          <t>['简单的心境']</t>
+        </is>
+      </c>
+      <c r="R807" t="inlineStr">
+        <is>
+          <t>2025-12-11 22:05:15</t>
+        </is>
+      </c>
+      <c r="S807" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T807" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>693aa858000000001b032e8e</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693aa858000000001b032e8e?xsec_token=AB2YL2nC9NMcXYXtLxjaIxo_KvWIm_zUzNDyIJFHk_6eo=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>加强学习</t>
+        </is>
+      </c>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>30 ✗60休息
+30✓60 格局
+#我的炒股日记[话题]# #继续努力学习[话题]#</t>
+        </is>
+      </c>
+      <c r="J808" t="inlineStr">
+        <is>
+          <t>1892</t>
+        </is>
+      </c>
+      <c r="K808" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="L808" t="inlineStr">
+        <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="M808" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="N808" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O808" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P808" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121909/0af6578c3c11a6f4898059bcdbb60ef7/notes_pre_post/1040g3k831puv9e34nupg4a7r1e8cb33v1j413e8!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q808" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '继续努力学习']</t>
+        </is>
+      </c>
+      <c r="R808" t="inlineStr">
+        <is>
+          <t>2025-12-11 19:17:44</t>
+        </is>
+      </c>
+      <c r="S808" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T808" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>693a831b000000000d00f9d9</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693a831b000000000d00f9d9?xsec_token=AB2YL2nC9NMcXYXtLxjaIxo9pj21hz8oReazAhhA_8dVY=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>勇气</t>
+        </is>
+      </c>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>周下 需要的不光是勇气
+而是对趋势理解
+无数个夜
+我都看图
+年轻时 因为我不断的看 看 看 看 看 天天看
+让我差点看成了宅男
+成了身边朋友的笑柄  你看这人 傻不傻 天天没事看这个无聊的东西  害我当时连女朋友都找不到
+还好 这游戏 玩会了 就跟 金币有点点关系了
+所以年轻人 一定要努力  没事把这个看图 当手游来看  这样  就算成了宅男  也是…有钱的宅男
+#勇气与成长[话题]#</t>
+        </is>
+      </c>
+      <c r="J809" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="L809" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="M809" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N809" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O809" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P809" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121952/1e6dcc5ee7b665c8a6c374def84dba3a/notes_pre_post/1040g3k831pujlsr9ma5g4a7r1e8cb33vge8g810!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q809" t="inlineStr">
+        <is>
+          <t>['勇气与成长']</t>
+        </is>
+      </c>
+      <c r="R809" t="inlineStr">
+        <is>
+          <t>2025-12-11 16:38:51</t>
+        </is>
+      </c>
+      <c r="S809" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T809" t="inlineStr">
+        <is>
+          <t>图1: OCR超时/失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>693a6997000000000d03b52c</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693a6997000000000d03b52c?xsec_token=AB2YL2nC9NMcXYXtLxjaIxo4McXY4OrSJCZ8329SB_ZEs=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>我胆子小</t>
+        </is>
+      </c>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>我依稀记得 前段时间  在我下面留言
+我说N代通讯 我只敢 宽带H
+她笑我胆子小
+结果呢
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J810" t="inlineStr">
+        <is>
+          <t>1555</t>
+        </is>
+      </c>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="L810" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="M810" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N810" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O810" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P810" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602121958/85466747e7d08574f12bad330271641f/notes_pre_post/1040g3k831pujlsr9ma604a7r1e8cb33vek7m2qo!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q810" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R810" t="inlineStr">
+        <is>
+          <t>2025-12-11 14:49:59</t>
+        </is>
+      </c>
+      <c r="S810" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T810" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>693a462d000000000d00da69</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693a462d000000000d00da69?xsec_token=AB2YL2nC9NMcXYXtLxjaIxo0Yjcj5Xqzpst73it_couCw=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>三哥的话
+因为我格局时
+是破位再周下的
+所以上来这段
+成本优势就体现了
+那么反思下
+牙膏呢
+电呢</t>
+        </is>
+      </c>
+      <c r="J811" t="inlineStr">
+        <is>
+          <t>1702</t>
+        </is>
+      </c>
+      <c r="K811" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="L811" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="M811" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N811" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O811" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P811" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122003/d973e7ecf7baa4084084aa09efc32a1f/1040g00831pucftkdl24g4a7r1e8cb33vgc9pb70!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q811" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R811" t="inlineStr">
+        <is>
+          <t>2025-12-11 12:18:53</t>
+        </is>
+      </c>
+      <c r="S811" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T811" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>693a34fd000000000d0368b7</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693a34fd000000000d0368b7?xsec_token=AB2YL2nC9NMcXYXtLxjaIxo5znyA9AFCwW2Ciy0ySwABI=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>牙膏[暗中观察R]</t>
+        </is>
+      </c>
+      <c r="J812" t="inlineStr">
+        <is>
+          <t>1774</t>
+        </is>
+      </c>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="L812" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="M812" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N812" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O812" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P812" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122008/77013fb3a6ffc93a535edf4402b765fc/1040g00831pucftkdl2304a7r1e8cb33vgkji098!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q812" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R812" t="inlineStr">
+        <is>
+          <t>2025-12-11 11:05:33</t>
+        </is>
+      </c>
+      <c r="S812" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T812" t="inlineStr">
+        <is>
+          <t>图1: Info Doc. Recyclable, 牙膏, 8mm/30lines</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>693a2191000000000d00c4ce</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693a2191000000000d00c4ce?xsec_token=AB2YL2nC9NMcXYXtLxjaIxo14TMoE747BmoP8kplSoiGU=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J813" t="inlineStr">
+        <is>
+          <t>2138</t>
+        </is>
+      </c>
+      <c r="K813" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="L813" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="M813" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="N813" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O813" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P813" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122014/9a52157b5a1851cfa7b0a82340e98c67/1040g00831pucftkdl2604a7r1e8cb33vmufaleo!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q813" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R813" t="inlineStr">
+        <is>
+          <t>2025-12-11 09:42:41</t>
+        </is>
+      </c>
+      <c r="S813" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T813" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>693a0e94000000001b021cb3</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693a0e94000000001b021cb3?xsec_token=AB2YL2nC9NMcXYXtLxjaIxo5ZJRjJPS48YU3UtU1ZvG4c=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>示弱≈赢</t>
+        </is>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>60✗30  30✓60
+跟首突60月一样
+如果没资源
+那么跟着大船走
+如果觉得自己天赋异禀 又大心脏  又有资源  又～
+ok的  月下吸你也可以参与   那么先看看 是不是符合咯[暗中观察R][微笑R]
+不要忘记  强到韩老魔  都让柱呢[捂嘴笑R]#我的炒股日记[话题]# #柔弱胜刚强[话题]#</t>
+        </is>
+      </c>
+      <c r="J814" t="inlineStr">
+        <is>
+          <t>2122</t>
+        </is>
+      </c>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="L814" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="M814" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N814" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O814" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P814" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122019/7ba5cfa22b64e9189327dd3d7576bc6a/1040g00831pucftkdl26g4a7r1e8cb33vmiriuog!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q814" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '柔弱胜刚强']</t>
+        </is>
+      </c>
+      <c r="R814" t="inlineStr">
+        <is>
+          <t>2025-12-11 08:21:40</t>
+        </is>
+      </c>
+      <c r="S814" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T814" t="inlineStr">
+        <is>
+          <t>图1: 60×30, 30√60, 跟首突60月一样, 如果没资源, 那么跟着大船走, 如果觉得自己天赋异禀又, 大心脏, 又有资源, 又~, ok的, 月下吸你也可以参, 与, 那么先看看, 是不是符, 合咯</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
+++ b/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T814"/>
+  <dimension ref="A1:T836"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53272,6 +53272,2321 @@
         </is>
       </c>
     </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>69398b38000000000d039467</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69398b38000000000d039467?xsec_token=ABUGOVqIM0l1l-Xm64wbbIPiiej869hZciRXRJJL6aHHw=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>不能把小招猫2021年以前的那张图用到现在来看
+当初50多时赠品 PE
+跟现在完全不同
+就今天 小招猫
+赠品都有5％了</t>
+        </is>
+      </c>
+      <c r="J815" t="inlineStr">
+        <is>
+          <t>1853</t>
+        </is>
+      </c>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="L815" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="M815" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="N815" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O815" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P815" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122024/9729f58fcb9279936f3142c0eeef8a55/1040g2sg31ptn6b8slae04a7r1e8cb33vpfb4uig!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q815" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R815" t="inlineStr">
+        <is>
+          <t>2025-12-10 23:01:12</t>
+        </is>
+      </c>
+      <c r="S815" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T815" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>693970d7000000001b02022f</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693970d7000000001b02022f?xsec_token=ABUGOVqIM0l1l-Xm64wbbIPqrFDEKphoA-E9zKFgj00qM=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>你出来～</t>
+        </is>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>谁昨天祝福我  希望我2026年收入突破100w的[泪崩R]
+#一切尽在不言中[话题]#</t>
+        </is>
+      </c>
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>1802</t>
+        </is>
+      </c>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="L816" t="inlineStr">
+        <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="M816" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N816" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O816" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P816" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122029/2bfa7825dd0d57afe64d1d90afef6716/1040g2sg31ptn6b8slah04a7r1e8cb33via4eqmo!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q816" t="inlineStr">
+        <is>
+          <t>['一切尽在不言中']</t>
+        </is>
+      </c>
+      <c r="R816" t="inlineStr">
+        <is>
+          <t>2025-12-10 21:08:39</t>
+        </is>
+      </c>
+      <c r="S816" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T816" t="inlineStr">
+        <is>
+          <t>图1: “, 谁昨天祝福我, 希望我2026年, 收入突破, 100w的</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>69397022000000000d03bb59</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69397022000000000d03bb59?xsec_token=ABUGOVqIM0l1l-Xm64wbbIPk9A2viDHz4ccB3J0oXfy5E=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>大家别安慰我啊[石化R][石化R][石化R][石化R][石化R]
+我今年还16％呢[泪崩R][泪崩R][泪崩R][泪崩R][泪崩R][泪崩R][泪崩R][泪崩R][泪崩R][泪崩R]</t>
+        </is>
+      </c>
+      <c r="J817" t="inlineStr">
+        <is>
+          <t>1658</t>
+        </is>
+      </c>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="L817" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="M817" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N817" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O817" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P817" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122035/f4babfb02f5fda50b329e8a85ee3f806/1040g2sg31ptn6b8slafg4a7r1e8cb33vvrqal2g!nd_dft_wlteh_webp_3']</t>
+        </is>
+      </c>
+      <c r="Q817" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R817" t="inlineStr">
+        <is>
+          <t>2025-12-10 21:05:38</t>
+        </is>
+      </c>
+      <c r="S817" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T817" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>69396948000000000d03912b</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69396948000000000d03912b?xsec_token=ABUGOVqIM0l1l-Xm64wbbIPg30q8aJ7oyj68nHKOca1Qw=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>运气好</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>我为什么能常保持常年投资好心态
+因为我有阿甘精神
+我会乐呵呵的看到小招猫如果去月小坑
+非常开心 因为
+又能安心拿一年赠品了
+#好运加满100%[话题]# #运气也是实力的一部分[话题]# #感谢上天眷顾[话题]# #好运[话题]# #好运自然来[话题]#</t>
+        </is>
+      </c>
+      <c r="J818" t="inlineStr">
+        <is>
+          <t>1835</t>
+        </is>
+      </c>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="L818" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="M818" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N818" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O818" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P818" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122040/33987e5e76f68f876e1d2e4ed54a5e34/1040g2sg31ptn6b8slagg4a7r1e8cb33vsu72n70!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q818" t="inlineStr">
+        <is>
+          <t>['好运加满100%', '运气也是实力的一部分', '感谢上天眷顾', '好运', '好运自然来']</t>
+        </is>
+      </c>
+      <c r="R818" t="inlineStr">
+        <is>
+          <t>2025-12-10 20:36:24</t>
+        </is>
+      </c>
+      <c r="S818" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T818" t="inlineStr">
+        <is>
+          <t>图1: Info Doc., Recyclable, 我为什么能常保持常年, 投资好心态, 因为我有阿甘精神, 我会乐呵呵的看到招, 猫如果去坑, 常开因为, 又能安拿一年赠品了, 8mm /30lines</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>6939676e000000000d00ea08</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6939676e000000000d00ea08?xsec_token=ABUGOVqIM0l1l-Xm64wbbIPkgTzJp4ottH54IqIXcLdqs=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>梅梅</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>某国神华
+30 ✗60休息
+60✓30格局
+第一次格局点很重要 如果是周下  或 首突
+那么其实  成本低后 可以安安心心休息
+#柳暗花明又一村[话题]#</t>
+        </is>
+      </c>
+      <c r="J819" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="L819" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="M819" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="N819" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O819" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P819" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122046/d29b31e72e9c5578f39125c26dd6ea6f/notes_pre_post/1040g3k831ptn6bfs5ab04a7r1e8cb33vq0b3a4g!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q819" t="inlineStr">
+        <is>
+          <t>['柳暗花明又一村']</t>
+        </is>
+      </c>
+      <c r="R819" t="inlineStr">
+        <is>
+          <t>2025-12-10 20:28:30</t>
+        </is>
+      </c>
+      <c r="S819" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T819" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>693962e7000000000d03ee61</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693962e7000000000d03ee61?xsec_token=ABUGOVqIM0l1l-Xm64wbbIPuxCV_ih4By1DgpWpsck260=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>继续 电呢～</t>
+        </is>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>30✗60结束
+30✓60开始
+so？
+buy and hold
+但股息不高
+所以 你们只是不小心看到
+格局 不格局 跟我无关
+谁下面叫失望 慢  我就屏蔽他
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J820" t="inlineStr">
+        <is>
+          <t>2233</t>
+        </is>
+      </c>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="L820" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="M820" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="N820" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O820" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P820" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122051/0e92b819fbe90920f8540acfd861e385/notes_pre_post/1040g3k831ptn6bfs5abg4a7r1e8cb33v8r8nsjo!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q820" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R820" t="inlineStr">
+        <is>
+          <t>2025-12-10 20:09:11</t>
+        </is>
+      </c>
+      <c r="S820" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T820" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>693961e4000000001b0308d8</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693961e4000000001b0308d8?xsec_token=ABUGOVqIM0l1l-Xm64wbbIPmchwveLVEIhJuceHB6Z1ZA=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>车</t>
+        </is>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>30✗60
+休息
+等60✓30
+干活#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J821" t="inlineStr">
+        <is>
+          <t>1644</t>
+        </is>
+      </c>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="L821" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="M821" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="N821" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O821" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P821" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122056/0462084c4a7f18febd41162966d4d813/notes_pre_post/1040g3k831ptn6bfs5acg4a7r1e8cb33vvhlc01g!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q821" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R821" t="inlineStr">
+        <is>
+          <t>2025-12-10 20:04:52</t>
+        </is>
+      </c>
+      <c r="S821" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T821" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>6939600f000000000d00fd62</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6939600f000000000d00fd62?xsec_token=ABUGOVqIM0l1l-Xm64wbbIPtURhzIzZmebUg6iiadBrsE=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>油 演绎 小招猫</t>
+        </is>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>简单了吗？
+30  60 破了就休息
+回来了 就干活
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J822" t="inlineStr">
+        <is>
+          <t>1546</t>
+        </is>
+      </c>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="L822" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="M822" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="N822" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O822" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P822" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122126/ecbdc1a465032ace525093d87efbf45c/notes_pre_post/1040g3k831ptn6bfs5ad04a7r1e8cb33vqu4vai0!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q822" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R822" t="inlineStr">
+        <is>
+          <t>2025-12-10 19:57:03</t>
+        </is>
+      </c>
+      <c r="S822" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T822" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>69394565000000001b026b2b</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69394565000000001b026b2b?xsec_token=ABUGOVqIM0l1l-Xm64wbbIPqaVHNgH7G2ha2r3hK9QOo8=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J823" t="inlineStr">
+        <is>
+          <t>1894</t>
+        </is>
+      </c>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="L823" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="M823" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="N823" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O823" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P823" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122131/cf823198fc6bc08c1f18ec64023ea134/1040g2sg31ptbtl3ol2tg4a7r1e8cb33vm24dqc8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q823" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R823" t="inlineStr">
+        <is>
+          <t>2025-12-10 18:03:17</t>
+        </is>
+      </c>
+      <c r="S823" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T823" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>69392e73000000000d03990e</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69392e73000000000d03990e?xsec_token=ABUGOVqIM0l1l-Xm64wbbIPis3HBLnKfBELJ47mdSDc7k=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>如果是我</t>
+        </is>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>网格
+周60没了
+30周破了60周 我就不动了
+等30周会到60周 我再动
+就这么简单
+#一切尽在不言中[话题]#</t>
+        </is>
+      </c>
+      <c r="J824" t="inlineStr">
+        <is>
+          <t>2046</t>
+        </is>
+      </c>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="L824" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="M824" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="N824" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O824" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P824" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122136/699e395f021ea0f31753a501e6251942/notes_pre_post/1040g3k031pth599nkk6g4a7r1e8cb33votuqj30!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q824" t="inlineStr">
+        <is>
+          <t>['一切尽在不言中']</t>
+        </is>
+      </c>
+      <c r="R824" t="inlineStr">
+        <is>
+          <t>2025-12-10 16:25:23</t>
+        </is>
+      </c>
+      <c r="S824" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T824" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>69391ab1000000000d039ebb</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69391ab1000000000d039ebb?xsec_token=ABUGOVqIM0l1l-Xm64wbbIPhYJsc-c6kaEePc89ufsmeQ=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>要努力啊</t>
+        </is>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>2026年
+不欢迎下面发市值炫富的
+不欢迎评论区下面喊躺平的价值观
+大家一起努力
+提高自己  学习策略
+这是主旋律</t>
+        </is>
+      </c>
+      <c r="J825" t="inlineStr">
+        <is>
+          <t>2409</t>
+        </is>
+      </c>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="L825" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="M825" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N825" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O825" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P825" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122141/3bb8782344ded4d4ddd5de282330fe34/1040g2sg31ptbtl3ol2ug4a7r1e8cb33vdrocag0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q825" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R825" t="inlineStr">
+        <is>
+          <t>2025-12-10 15:01:05</t>
+        </is>
+      </c>
+      <c r="S825" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T825" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>693918960000000019024a46</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693918960000000019024a46?xsec_token=ABUGOVqIM0l1l-Xm64wbbIPtWeEheUmlvqZA-GFbpojYc=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>难受的一天？
+也还好啊
+这只是我2006年到现在
+很平淡的一天
+可能我这人 比较迟钝
+小招猫还是那个小招猫吗？
+其次 一年赠品会少我吗？</t>
+        </is>
+      </c>
+      <c r="J826" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="L826" t="inlineStr">
+        <is>
+          <t>394</t>
+        </is>
+      </c>
+      <c r="M826" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N826" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O826" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P826" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122146/f892cfdfc6594b2119ac511555e1040f/1040g2sg31ptbtl3ol31g4a7r1e8cb33v0hjfod8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q826" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R826" t="inlineStr">
+        <is>
+          <t>2025-12-10 14:52:06</t>
+        </is>
+      </c>
+      <c r="S826" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T826" t="inlineStr">
+        <is>
+          <t>图1: 难受的一天？, 也还好啊, 这只是我2006年到现在, 很平淡的一天, 可能我这人, 比较迟钝, 小招猫还是那个小招猫吗, ?, 其次, 一年上百万赠品会少, 我吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>6939038b000000000d00c0c0</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6939038b000000000d00c0c0?xsec_token=ABUGOVqIM0l1l-Xm64wbbIPp_HhvTPhFTpcdgP1pQY63s=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>三哥能不能帮忙弥补下</t>
+        </is>
+      </c>
+      <c r="J827" t="inlineStr">
+        <is>
+          <t>1495</t>
+        </is>
+      </c>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="L827" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="M827" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N827" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O827" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P827" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122152/ffe708da9bdc2b418371e7e0607ad3ba/1040g2sg31ptbtl3ol32g4a7r1e8cb33vkorqoq0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q827" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R827" t="inlineStr">
+        <is>
+          <t>2025-12-10 13:22:19</t>
+        </is>
+      </c>
+      <c r="S827" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T827" t="inlineStr">
+        <is>
+          <t>图1: 三哥能不能, 帮忙弥补下</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>6938e604000000001b031f71</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6938e604000000001b031f71?xsec_token=ABj3MyEtsqLMHCM0chB34pdU7FMB2lptaQJmBfp2VBl78=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>冷知识
+说过很多次了
+遇到小招猫今天这种情况
+别去动
+休息下  等3天再考虑
+怎么都忘记了</t>
+        </is>
+      </c>
+      <c r="J828" t="inlineStr">
+        <is>
+          <t>2278</t>
+        </is>
+      </c>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="L828" t="inlineStr">
+        <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="M828" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="N828" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O828" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P828" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122157/b0baa4547ad354ca0debc47e45e81643/1040g2sg31pt43l03kg204a7r1e8cb33vpq4b140!nd_dft_wlteh_webp_3']</t>
+        </is>
+      </c>
+      <c r="Q828" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R828" t="inlineStr">
+        <is>
+          <t>2025-12-10 11:16:20</t>
+        </is>
+      </c>
+      <c r="S828" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T828" t="inlineStr">
+        <is>
+          <t>图1: 冷知识, 说过很多次了, 遇到, 小招猫今天这种, 情况, 别去动, 休息下, 等3天再考虑, 怎么都忘记了</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>6938d488000000000d00f4e5</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6938d488000000000d00f4e5?xsec_token=ABj3MyEtsqLMHCM0chB34pdS6V3RaqZPlktmlIaUntZFI=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>我以后闭嘴</t>
+        </is>
+      </c>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>……哎</t>
+        </is>
+      </c>
+      <c r="J829" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="L829" t="inlineStr">
+        <is>
+          <t>1342</t>
+        </is>
+      </c>
+      <c r="M829" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="N829" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O829" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P829" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122203/4a788795d3d830e2e02cdb4fe3738d96/notes_pre_post/1040g3k031pt43l795a604a7r1e8cb33v5p4olq8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q829" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R829" t="inlineStr">
+        <is>
+          <t>2025-12-10 10:01:44</t>
+        </is>
+      </c>
+      <c r="S829" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T829" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>6938d0bc000000000d03c047</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6938d0bc000000000d03c047?xsec_token=ABj3MyEtsqLMHCM0chB34pdZb6S7dwZyL8lqAQRGwt0uE=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>我好痛[泪崩R]
+昨天谁说 祝我明年收入破百万的…你出来[泪崩R][泪崩R]</t>
+        </is>
+      </c>
+      <c r="J830" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="L830" t="inlineStr">
+        <is>
+          <t>1044</t>
+        </is>
+      </c>
+      <c r="M830" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N830" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O830" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P830" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122208/96236a32e7c40325d3a89b7e8b11a440/1040g2sg31pt43l03kg3g4a7r1e8cb33vdrke1n0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q830" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R830" t="inlineStr">
+        <is>
+          <t>2025-12-10 09:45:32</t>
+        </is>
+      </c>
+      <c r="S830" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T830" t="inlineStr">
+        <is>
+          <t>图1: 我好痛, G</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>6938ceef0000000019027019</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6938ceef0000000019027019?xsec_token=ABj3MyEtsqLMHCM0chB34pdSJ4pV9zC6nYGsxYzNXNV30=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>移不动A先看看
+别乱动#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J831" t="inlineStr">
+        <is>
+          <t>1630</t>
+        </is>
+      </c>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L831" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="M831" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N831" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O831" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P831" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122213/52212707a5dee100b3b73f5b2a2d70af/1040g2sg31pt43l03kg5g4a7r1e8cb33vf6i5s98!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q831" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R831" t="inlineStr">
+        <is>
+          <t>2025-12-10 09:37:51</t>
+        </is>
+      </c>
+      <c r="S831" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T831" t="inlineStr">
+        <is>
+          <t>图1: 移不动A先看看, 别乱动</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>6938c3e5000000001902428b</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6938c3e5000000001902428b?xsec_token=ABj3MyEtsqLMHCM0chB34pdah1K9j1XTju-pLxlphLiWk=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>如果没有如果</t>
+        </is>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>这个是周
+去周30哪怕周30-60附近
+不过份吧
+简单点说  周中到周下  都ok啊
+那么有些企业  月当周看吧
+#如果没有如果[话题]#</t>
+        </is>
+      </c>
+      <c r="J832" t="inlineStr">
+        <is>
+          <t>1642</t>
+        </is>
+      </c>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="L832" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="M832" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N832" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O832" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P832" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122219/37a4c867bb7f3b68d2f424297262c3aa/notes_pre_post/1040g3k031pt43l795a6g4a7r1e8cb33v4usku58!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q832" t="inlineStr">
+        <is>
+          <t>['如果没有如果']</t>
+        </is>
+      </c>
+      <c r="R832" t="inlineStr">
+        <is>
+          <t>2025-12-10 08:50:45</t>
+        </is>
+      </c>
+      <c r="S832" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T832" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>69383db8000000001b020622</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69383db8000000001b020622?xsec_token=ABj3MyEtsqLMHCM0chB34pda9Hc52dr5hQXJP_Y3VZ1B4=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>出海</t>
+        </is>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>#我的炒股日记[话题]# #出海[话题]# #能源[话题]# #助力企业出海发展[话题]#</t>
+        </is>
+      </c>
+      <c r="J833" t="inlineStr">
+        <is>
+          <t>2597</t>
+        </is>
+      </c>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="L833" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="M833" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="N833" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O833" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P833" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122224/dd572ee4153a6c7349f6bf10fa2b7042/notes_pre_post/1040g3k831psjm5a8kg7g4a7r1e8cb33vpgg6tjg!nd_dft_wlteh_jpg_3', 'http://sns-webpic-qc.xhscdn.com/202602122224/10cfc4427e02a9fe15ac996311919653/notes_pre_post/1040g3k831psjonjv4m004a7r1e8cb33ve278lqo!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q833" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '出海', '能源', '助力企业出海发展']</t>
+        </is>
+      </c>
+      <c r="R833" t="inlineStr">
+        <is>
+          <t>2025-12-09 23:18:16</t>
+        </is>
+      </c>
+      <c r="S833" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T833" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过) | 图2: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>693808160000000019024f6b</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693808160000000019024f6b?xsec_token=ABj3MyEtsqLMHCM0chB34pdeffSSDHgkEl2U7R7V-3oEM=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>投资一定要有资源
+没有资源
+就要会看首突 龙回头
+都不会真的存银行吧
+看看前几天谁说看好
+labubu玩具公司的
+这几天如何</t>
+        </is>
+      </c>
+      <c r="J834" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="L834" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="M834" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N834" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O834" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P834" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122229/4828d5bcc699a51a19501112758aa4ba/1040g00831psb7gh6km5g4a7r1e8cb33v6hgiucg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q834" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R834" t="inlineStr">
+        <is>
+          <t>2025-12-09 19:29:26</t>
+        </is>
+      </c>
+      <c r="S834" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T834" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>6937db63000000001b026ead</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6937db63000000001b026ead?xsec_token=AB_318s-eaHdSgLjPcR0ZeMjb_NQEXR1EqV7lgu7kH77k=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>收益差 中午饭现在吃</t>
+        </is>
+      </c>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>#我的炒股日记[话题]# #随便吃一点[话题]#</t>
+        </is>
+      </c>
+      <c r="J835" t="inlineStr">
+        <is>
+          <t>1675</t>
+        </is>
+      </c>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="L835" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="M835" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N835" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O835" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P835" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122234/b38e717227bb7adb2c2477cbd8c89560/notes_pre_post/1040g3k031ps7oq3pl26g4a7r1e8cb33vfmm6eu8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q835" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '随便吃一点']</t>
+        </is>
+      </c>
+      <c r="R835" t="inlineStr">
+        <is>
+          <t>2025-12-09 16:18:43</t>
+        </is>
+      </c>
+      <c r="S835" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T835" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>6937c08d000000000d00f70f</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6937c08d000000000d00f70f?xsec_token=AB_318s-eaHdSgLjPcR0ZeMmka1n70scBb6qyn-TTwPOI=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>休息了
+又不用每天都看的
+平安姑娘不到周中偏下的地方或周下
+我不考虑格局回来
+三哥周上还早
+牙膏周上还早
+渣猫不看了随意
+丑的 宽带H 也都没附近</t>
+        </is>
+      </c>
+      <c r="J836" t="inlineStr">
+        <is>
+          <t>1895</t>
+        </is>
+      </c>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="L836" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="M836" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N836" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O836" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P836" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122239/c3dfdeb2a0ffb3e3a54a8856b86cfd4b/1040g00831ps3iifl4m0g4a7r1e8cb33vlim1bc8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q836" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R836" t="inlineStr">
+        <is>
+          <t>2025-12-09 14:24:13</t>
+        </is>
+      </c>
+      <c r="S836" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T836" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
+++ b/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T836"/>
+  <dimension ref="A1:T894"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55587,6 +55587,6117 @@
         </is>
       </c>
     </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>6937b907000000000d034c40</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6937b907000000000d034c40?xsec_token=AB_318s-eaHdSgLjPcR0ZeMrQ87M95aXkO8e0L3Y90-Zo=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I837" t="inlineStr">
+        <is>
+          <t>这次没人前几天高位去信仰
+平安姑娘了吧
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J837" t="inlineStr">
+        <is>
+          <t>1744</t>
+        </is>
+      </c>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="L837" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="M837" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N837" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O837" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P837" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122244/a409dfb39065bc936aec3d380e9e9ebd/1040g00831ps3iifl4m604a7r1e8cb33vpngm9co!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q837" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R837" t="inlineStr">
+        <is>
+          <t>2025-12-09 13:52:07</t>
+        </is>
+      </c>
+      <c r="S837" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T837" t="inlineStr">
+        <is>
+          <t>图1: 这次没人, 前几天高位去, 信仰, 平安姑娘了吧</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>6937a01e00000000190269b7</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6937a01e00000000190269b7?xsec_token=AB_318s-eaHdSgLjPcR0ZeMmk8Nmh6o67HZwr7MNuuxQ4=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J838" t="inlineStr">
+        <is>
+          <t>2064</t>
+        </is>
+      </c>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="L838" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="M838" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N838" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O838" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P838" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122250/c6b092bc4dd6ca95e7083c032d9410ca/1040g00831prtlr0g4k1g4a7r1e8cb33vqgaj240!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q838" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R838" t="inlineStr">
+        <is>
+          <t>2025-12-09 12:05:50</t>
+        </is>
+      </c>
+      <c r="S838" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T838" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>69378bc400000000190271bc</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69378bc400000000190271bc?xsec_token=AB_318s-eaHdSgLjPcR0ZeMsnds3qoPBa96DeumCN_W_4=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>小渣猫
+一个日线下轨
+洗的真～</t>
+        </is>
+      </c>
+      <c r="J839" t="inlineStr">
+        <is>
+          <t>1708</t>
+        </is>
+      </c>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="L839" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="M839" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N839" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O839" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P839" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122255/980f53b805c2c49e6003c21be0863f71/1040g00831prtlr0g4k3g4a7r1e8cb33vqi6pr2g!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q839" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R839" t="inlineStr">
+        <is>
+          <t>2025-12-09 10:39:00</t>
+        </is>
+      </c>
+      <c r="S839" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T839" t="inlineStr">
+        <is>
+          <t>图1: 小渣猫, 一个日线下轨, 洗的真～</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>693788b8000000000d00c5d1</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693788b8000000000d00c5d1?xsec_token=AB_318s-eaHdSgLjPcR0ZeMjGmLYnzLq0GxPK2U67XHS0=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>逻辑就是这个逻辑
+三兄弟
+总要轮动
+三哥 其实 难度最大
+但信牛牛市
+他就不会缺席#金融不可能三角[话题]#</t>
+        </is>
+      </c>
+      <c r="J840" t="inlineStr">
+        <is>
+          <t>1720</t>
+        </is>
+      </c>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="L840" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="M840" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N840" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O840" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P840" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122300/2714e06dcc4f3f585011b5f09b9fd1f8/1040g00831prtlr0g4k6g4a7r1e8cb33vnoeab98!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q840" t="inlineStr">
+        <is>
+          <t>['金融不可能三角']</t>
+        </is>
+      </c>
+      <c r="R840" t="inlineStr">
+        <is>
+          <t>2025-12-09 10:26:00</t>
+        </is>
+      </c>
+      <c r="S840" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T840" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>6936e9be000000001b03142f</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6936e9be000000001b03142f?xsec_token=ABtyt76By6bcAtcvaPnZgi9PSMjj2hrew1QEj68pAGcvk=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>期待新的一年</t>
+        </is>
+      </c>
+      <c r="I841" t="inlineStr">
+        <is>
+          <t>期待2026
+#愿新的一年越来越好[话题]#</t>
+        </is>
+      </c>
+      <c r="J841" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="L841" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="M841" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="N841" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O841" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P841" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122306/4462f933b8bd15e218035f965a257a91/notes_pre_post/1040g3k831pra8s60ladg4a7r1e8cb33v6085470!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202602122306/df37a2168eb687a75b759f3962cb42e8/notes_pre_post/1040g3k831pra8s60lacg4a7r1e8cb33vbj9ap30!nd_dft_wgth_webp_3']</t>
+        </is>
+      </c>
+      <c r="Q841" t="inlineStr">
+        <is>
+          <t>['愿新的一年越来越好']</t>
+        </is>
+      </c>
+      <c r="R841" t="inlineStr">
+        <is>
+          <t>2025-12-08 23:07:42</t>
+        </is>
+      </c>
+      <c r="S841" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T841" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过) | 图2: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>6936e4f3000000000d0370dd</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6936e4f3000000000d0370dd?xsec_token=ABtyt76By6bcAtcvaPnZgi9IDrsh55wa9LNx-BBkmctzI=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>你不知道的事</t>
+        </is>
+      </c>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>多看 就会 #我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J842" t="inlineStr">
+        <is>
+          <t>1731</t>
+        </is>
+      </c>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="L842" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="M842" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N842" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O842" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P842" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122311/f2a2d436a0b9997e8f82191ccb36447d/notes_pre_post/1040g3k031pr4lqcc5a504a7r1e8cb33vpj3q5ro!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q842" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R842" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:47:15</t>
+        </is>
+      </c>
+      <c r="S842" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T842" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>6936df02000000000d00d630</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6936df02000000000d00d630?xsec_token=ABtyt76By6bcAtcvaPnZgi9MvqF_raWYvhNrt_wf9NwOg=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>以后的以后</t>
+        </is>
+      </c>
+      <c r="I843" t="inlineStr">
+        <is>
+          <t>好了关于电的内容
+往后我继续闭嘴[捂嘴笑R]
+后面
+我继续坚持低波动红利策略啊哈哈哈哈哈
+三哥也是  说过 就可以了
+不能多说
+还好 电还有赠品呢</t>
+        </is>
+      </c>
+      <c r="J843" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="L843" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="M843" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="N843" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O843" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P843" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122316/8fcd4c2cfc70132ca651e23a31260c00/1040g00831pr7dc3r4kh04a7r1e8cb33vp81tio0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q843" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R843" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:21:54</t>
+        </is>
+      </c>
+      <c r="S843" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T843" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>6936dcff0000000019026752</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6936dcff0000000019026752?xsec_token=ABtyt76By6bcAtcvaPnZgi9ADZiL8ur6sBwgMGpONBojg=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t>恭喜我发财2</t>
+        </is>
+      </c>
+      <c r="I844" t="inlineStr">
+        <is>
+          <t>#未来要发财[话题]# #金钱总是向我飞奔而来[话题]# #财从四面八方来[话题]# #期待明天会更好[话题]# #好运自然来[话题]# #我爱钱钱也爱我[话题]#</t>
+        </is>
+      </c>
+      <c r="J844" t="inlineStr">
+        <is>
+          <t>1678</t>
+        </is>
+      </c>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="L844" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="M844" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="N844" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O844" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P844" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122321/ed17186cc7ecefb6b78b08662dbaafd8/notes_pre_post/1040g3k031pr4lqcc5a1g4a7r1e8cb33v7vq2g08!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q844" t="inlineStr">
+        <is>
+          <t>['未来要发财', '金钱总是向我飞奔而来', '财从四面八方来', '期待明天会更好', '好运自然来', '我爱钱钱也爱我']</t>
+        </is>
+      </c>
+      <c r="R844" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:13:19</t>
+        </is>
+      </c>
+      <c r="S844" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T844" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>6936dbf0000000000d00c4e0</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6936dbf0000000000d00c4e0?xsec_token=ABtyt76By6bcAtcvaPnZgi9OWS8Lzcu0AHqY--jtnv9RE=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>恭喜我发财</t>
+        </is>
+      </c>
+      <c r="I845" t="inlineStr">
+        <is>
+          <t>支持AI  支持科技 支持机器人 支持储能
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J845" t="inlineStr">
+        <is>
+          <t>1826</t>
+        </is>
+      </c>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="L845" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="M845" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="N845" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O845" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P845" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122326/750d17495c5424970953b03199ae9225/notes_pre_post/1040g3k031pr4lqcc5a5g4a7r1e8cb33v3t4pdpg!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q845" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R845" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:08:48</t>
+        </is>
+      </c>
+      <c r="S845" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T845" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>6936d2ae000000001b03152d</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6936d2ae000000001b03152d?xsec_token=ABtyt76By6bcAtcvaPnZgi9OBa0OU-ZMzBqS-7qo64atE=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>我很快乐</t>
+        </is>
+      </c>
+      <c r="I846" t="inlineStr">
+        <is>
+          <t>我自己推算
+小招猫还要苦2个月
+正好到2026年了
+没事我很快乐
+我也不会难过 大家不要小看我
+有什么熬不过  大不了唱首歌
+虽然是悲伤的歌  声音有点难受
+也比别人好得多 我还是很快乐
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J846" t="inlineStr">
+        <is>
+          <t>1735</t>
+        </is>
+      </c>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="L846" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="M846" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N846" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O846" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P846" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122331/083ef3da74a09fd9e5e34c0480eed210/1040g00831pr7dc3r4kig4a7r1e8cb33vjms8bco!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q846" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R846" t="inlineStr">
+        <is>
+          <t>2025-12-08 21:29:18</t>
+        </is>
+      </c>
+      <c r="S846" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T846" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>6936c89b000000001b026bd5</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6936c89b000000001b026bd5?xsec_token=ABtyt76By6bcAtcvaPnZgi9Nh4b1ljf-4XRPFhLhOA7dk=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I847" t="inlineStr">
+        <is>
+          <t>花花顺环境还是太X
+计划彻底放弃那边暂时
+从今开始
+哪都不去了
+我就留小红薯
+以后小红薯就是我家</t>
+        </is>
+      </c>
+      <c r="J847" t="inlineStr">
+        <is>
+          <t>2791</t>
+        </is>
+      </c>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="L847" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="M847" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N847" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O847" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P847" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122336/f0f055fa17fbe417e8ca9ae190aad794/1040g2sg31pr14e8mlai04a7r1e8cb33vg116gjo!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q847" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R847" t="inlineStr">
+        <is>
+          <t>2025-12-08 20:46:19</t>
+        </is>
+      </c>
+      <c r="S847" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T847" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>6936bbe6000000001b025e69</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6936bbe6000000001b025e69?xsec_token=ABtyt76By6bcAtcvaPnZgi9FQjYQlbyNyilRVxcINjjJc=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>以后听不听我劝</t>
+        </is>
+      </c>
+      <c r="I848" t="inlineStr">
+        <is>
+          <t>不买不买
+不等你给另一对手擒获
+那时价格
+不会用上余生来量度
+但我拖着躯壳
+发现沿途寻找的快乐
+#别不听劝啊[话题]#</t>
+        </is>
+      </c>
+      <c r="J848" t="inlineStr">
+        <is>
+          <t>1829</t>
+        </is>
+      </c>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="L848" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="M848" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N848" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O848" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P848" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122341/5b717e593555057d36b22de4be507440/notes_pre_post/1040g3k031pr4lqcc5a6g4a7r1e8cb33vs3a59u8!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q848" t="inlineStr">
+        <is>
+          <t>['别不听劝啊']</t>
+        </is>
+      </c>
+      <c r="R848" t="inlineStr">
+        <is>
+          <t>2025-12-08 19:52:06</t>
+        </is>
+      </c>
+      <c r="S848" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T848" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>69369ee1000000001b026c6c</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69369ee1000000001b026c6c?xsec_token=ABtyt76By6bcAtcvaPnZgi9NDgV54nQ_t0h9ddJWWy5lc=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I849" t="inlineStr">
+        <is>
+          <t>冷笑话
+之前有人笑我宽带H格局掉错了
+结果 结果</t>
+        </is>
+      </c>
+      <c r="J849" t="inlineStr">
+        <is>
+          <t>1516</t>
+        </is>
+      </c>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="L849" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="M849" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N849" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O849" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P849" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122347/855dc0e42c4bda0e8709209479ca3935/1040g2sg31pr14e8mlakg4a7r1e8cb33vqlcrs50!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q849" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R849" t="inlineStr">
+        <is>
+          <t>2025-12-08 17:48:17</t>
+        </is>
+      </c>
+      <c r="S849" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T849" t="inlineStr">
+        <is>
+          <t>图1: 冷笑话, 之前有人笑我宽带, H格局掉错了, 结果, 结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>6936881d000000001b0221f8</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6936881d000000001b0221f8?xsec_token=ABtyt76By6bcAtcvaPnZgi9G6SWV2xyzZpk50q2qnXNhA=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>我都有</t>
+        </is>
+      </c>
+      <c r="I850" t="inlineStr">
+        <is>
+          <t>左手 大金融
+右手 基础消费
+AI  储能 科技？
+离得开
+宽带 电 吗？
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J850" t="inlineStr">
+        <is>
+          <t>1927</t>
+        </is>
+      </c>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="L850" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="M850" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="N850" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O850" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P850" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122352/f4b2c385277ea76e07244e3cddd259f4/1040g00831pqil5bf5a004a7r1e8cb33vp8oq41o!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q850" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R850" t="inlineStr">
+        <is>
+          <t>2025-12-08 16:11:09</t>
+        </is>
+      </c>
+      <c r="S850" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T850" t="inlineStr">
+        <is>
+          <t>图1: 左手, 大金融, 右手, 基础消费, 储能, AI, 科技？, 离得开, 宽带电, 电吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>693676b5000000001b02397d</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693676b5000000001b02397d?xsec_token=ABtyt76By6bcAtcvaPnZgi9OKvJrAEkmwEedQnL9wWcZY=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I851" t="inlineStr">
+        <is>
+          <t>小招猫越这样
+我信心越足</t>
+        </is>
+      </c>
+      <c r="J851" t="inlineStr">
+        <is>
+          <t>1876</t>
+        </is>
+      </c>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="L851" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="M851" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N851" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O851" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P851" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602122358/a01b71de441bb325d3eef3b21c2a39cd/1040g00831pqil5bf5a1g4a7r1e8cb33vf4p68d8!nd_dft_wlteh_webp_3']</t>
+        </is>
+      </c>
+      <c r="Q851" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R851" t="inlineStr">
+        <is>
+          <t>2025-12-08 14:56:53</t>
+        </is>
+      </c>
+      <c r="S851" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T851" t="inlineStr">
+        <is>
+          <t>图1: 小招猫越这样, 我信心越足</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>69365ebd000000000d03b461</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69365ebd000000000d03b461?xsec_token=ABtyt76By6bcAtcvaPnZgi9PVkK9CnSMo_BO28w0_4WCE=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I852" t="inlineStr">
+        <is>
+          <t>我就是我
+是颜色不一样的烟火
+天空海阔
+坚决不做最傻的泡沫
+#永远被文字打动的我[话题]#</t>
+        </is>
+      </c>
+      <c r="J852" t="inlineStr">
+        <is>
+          <t>1843</t>
+        </is>
+      </c>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="L852" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="M852" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N852" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O852" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P852" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130003/37d6585ce7ddea30a3c41fe641da0a4f/1040g00831pqil5bf5a4g4a7r1e8cb33v9ud5hr8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q852" t="inlineStr">
+        <is>
+          <t>['永远被文字打动的我']</t>
+        </is>
+      </c>
+      <c r="R852" t="inlineStr">
+        <is>
+          <t>2025-12-08 13:14:37</t>
+        </is>
+      </c>
+      <c r="S852" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T852" t="inlineStr">
+        <is>
+          <t>图1: ”, 我就是我, 是颜色不一样的烟火, 天空海阔, 坚决不做最傻的泡沫</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>69363f0a000000000d00e2c9</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69363f0a000000000d00e2c9?xsec_token=ABtyt76By6bcAtcvaPnZgi9Ezb2R3D-0ehBfh_s1LKd6c=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I853" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J853" t="inlineStr">
+        <is>
+          <t>2085</t>
+        </is>
+      </c>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="L853" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="M853" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N853" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O853" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P853" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130008/c81d45a2de5696a0a6d60ed4e811cf0c/1040g00831pqil5bf5a2g4a7r1e8cb33v6ei4vao!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q853" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R853" t="inlineStr">
+        <is>
+          <t>2025-12-08 10:59:22</t>
+        </is>
+      </c>
+      <c r="S853" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T853" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>69363ba0000000001b0268c9</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69363ba0000000001b0268c9?xsec_token=ABtyt76By6bcAtcvaPnZgi9EPMmI9vkJpL1SFaFuKBD8Q=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>反思下
+或叫思考下
+为什么 我三哥格局的地方 就是最近的低点
+多思考</t>
+        </is>
+      </c>
+      <c r="J854" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
+      </c>
+      <c r="L854" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="M854" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="N854" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O854" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P854" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130014/20f93baaae9b6dcd853fdab61a65467e/1040g00831pqil5bf5a504a7r1e8cb33vjcdg2s8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q854" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R854" t="inlineStr">
+        <is>
+          <t>2025-12-08 10:44:48</t>
+        </is>
+      </c>
+      <c r="S854" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T854" t="inlineStr">
+        <is>
+          <t>图1: 反思下, 或叫思考下, 为什么, 我三哥格局的, 地方, 就是最近的低点, 多思考</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>69362864000000000d00eb68</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69362864000000000d00eb68?xsec_token=ABtyt76By6bcAtcvaPnZgi9AHIcBuE1LVf8Z6MNx40O_I=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>单车快速变不了摩托</t>
+        </is>
+      </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>不要幻想
+不会出现你想的这种
+周上 周下继续
+耐心吧
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J855" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="L855" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="M855" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N855" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O855" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P855" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130019/22143c7902cee6c7aee7d8a310c6489c/1040g00831pqil5bf5a6g4a7r1e8cb33v6rt8j98!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q855" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R855" t="inlineStr">
+        <is>
+          <t>2025-12-08 09:22:44</t>
+        </is>
+      </c>
+      <c r="S855" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T855" t="inlineStr">
+        <is>
+          <t>图1: ”, 不要幻想, 不会出现你想的, 这种, 周上周下继续, 耐心吧</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>69357b93000000000d00c48b</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69357b93000000000d00c48b?xsec_token=ABGTjvX1hM0hmuag98FUYYx34Xf7BHrXHqvf8wpLa-rhQ=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I856" t="inlineStr">
+        <is>
+          <t>冷知识
+我是反对或不同意什么吃赠品攒股这个逻辑的 再我眼里 投资就是 低买 高卖
+赠品率只是用来[doge][doge]的
+所以我不是什么传统攒股…什么吃股息派</t>
+        </is>
+      </c>
+      <c r="J856" t="inlineStr">
+        <is>
+          <t>2185</t>
+        </is>
+      </c>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="L856" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="M856" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="N856" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O856" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P856" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130025/5c8fcaad1aceb71633b0f2135daf8366/1040g00831ppppmkjla5g4a7r1e8cb33vr9v98lg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q856" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R856" t="inlineStr">
+        <is>
+          <t>2025-12-07 21:05:23</t>
+        </is>
+      </c>
+      <c r="S856" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T856" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>69355063000000000d00f706</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69355063000000000d00f706?xsec_token=ABGTjvX1hM0hmuag98FUYYxyZ2f9SDPjLUD9BvNdHyY5s=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>标准</t>
+        </is>
+      </c>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>#我的炒股日记[话题]# #实践是检验真理的唯一标准[话题]#</t>
+        </is>
+      </c>
+      <c r="J857" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="L857" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="M857" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="N857" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O857" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P857" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130030/42ae96c89f257dc070358b4c1d377d14/notes_pre_post/1040g3k031ppgh41m4g204a7r1e8cb33v1crpi9g!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q857" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '实践是检验真理的唯一标准']</t>
+        </is>
+      </c>
+      <c r="R857" t="inlineStr">
+        <is>
+          <t>2025-12-07 18:01:07</t>
+        </is>
+      </c>
+      <c r="S857" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T857" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>693544f9000000001b0338b0</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693544f9000000001b0338b0?xsec_token=ABGTjvX1hM0hmuag98FUYYx9bR8yYVlhLgRg4d7FU0lvc=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J858" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="L858" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="M858" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="N858" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O858" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P858" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130035/e62383905a39fa240602ec6e0872b3d4/1040g2sg31ppgg5kel2bg4a7r1e8cb33vsllku2g!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q858" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R858" t="inlineStr">
+        <is>
+          <t>2025-12-07 17:12:25</t>
+        </is>
+      </c>
+      <c r="S858" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T858" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>693542c8000000001b0279e5</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693542c8000000001b0279e5?xsec_token=ABGTjvX1hM0hmuag98FUYYx3k2fSe9VT06DeDjs8P5C6g=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>我吃面了～</t>
+        </is>
+      </c>
+      <c r="I859" t="inlineStr">
+        <is>
+          <t>想对抗下市场！！明天
+看看如何[暗中观察R][暗中观察R][暗中观察R][暗中观察R]
+我今晚默默吃面了#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J859" t="inlineStr">
+        <is>
+          <t>1507</t>
+        </is>
+      </c>
+      <c r="K859" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L859" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="M859" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N859" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O859" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P859" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130040/235df794d2beca710348c27f47b231b6/notes_pre_post/1040g3k031ppgh41m4g504a7r1e8cb33vlgkmrag!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q859" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R859" t="inlineStr">
+        <is>
+          <t>2025-12-07 17:03:04</t>
+        </is>
+      </c>
+      <c r="S859" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T859" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>69353540000000000d034c2c</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69353540000000000d034c2c?xsec_token=ABGTjvX1hM0hmuag98FUYYx3i9tg1rbJ8ZoXrUtRvjtvY=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>冲动？</t>
+        </is>
+      </c>
+      <c r="I860" t="inlineStr">
+        <is>
+          <t>你瞅啥  冲动试试？
+让你叫很久天塌了</t>
+        </is>
+      </c>
+      <c r="J860" t="inlineStr">
+        <is>
+          <t>1738</t>
+        </is>
+      </c>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="L860" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="M860" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N860" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O860" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P860" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130045/47421b0f842a0f60523d9042356363b0/notes_pre_post/1040g3k031ppgh41m4g5g4a7r1e8cb33vf1ab120!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q860" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R860" t="inlineStr">
+        <is>
+          <t>2025-12-07 16:05:20</t>
+        </is>
+      </c>
+      <c r="S860" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T860" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>69352dac000000000d035f5f</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69352dac000000000d035f5f?xsec_token=ABGTjvX1hM0hmuag98FUYYx6ZZV4nqVFRSl0wG8YNvK20=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>不要盲目自信</t>
+        </is>
+      </c>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>最后再一次提示下
+慢慢牛
+不会出现幻想的那种连续上↑
+so  赠品4.15％的平安姑娘
+之前有了的就有了
+之前没了的就没了
+冷静 要稳
+#不要盲目的相信[话题]#</t>
+        </is>
+      </c>
+      <c r="J861" t="inlineStr">
+        <is>
+          <t>1964</t>
+        </is>
+      </c>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="L861" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="M861" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N861" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O861" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P861" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130050/1034b2467abf74d87b29e84e3c5adc5a/1040g2sg31ppgg5kel2d04a7r1e8cb33v1i6385o!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q861" t="inlineStr">
+        <is>
+          <t>['不要盲目的相信']</t>
+        </is>
+      </c>
+      <c r="R861" t="inlineStr">
+        <is>
+          <t>2025-12-07 15:33:00</t>
+        </is>
+      </c>
+      <c r="S861" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T861" t="inlineStr">
+        <is>
+          <t>图1: 最后再一次 提下, 慢慢牛, 不会出现幻想的那种连续上, 个, 赠品4.15%的平安姑娘, SO, 之前有了的就有了, 之前没了的就没了, 冷静, 要稳</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>693510b7000000000d0375c8</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693510b7000000000d0375c8?xsec_token=ABGTjvX1hM0hmuag98FUYYx8QFLniarj0XQ1CON-BvSVU=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>因为 说以</t>
+        </is>
+      </c>
+      <c r="I862" t="inlineStr">
+        <is>
+          <t>如果 我把这个月 当 周看
+那么现在 是不是 一直说的 周30-周60之间
+boll下轨
+#如果没有如果[话题]#</t>
+        </is>
+      </c>
+      <c r="J862" t="inlineStr">
+        <is>
+          <t>1581</t>
+        </is>
+      </c>
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="L862" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="M862" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="N862" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O862" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P862" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130056/694494346161c7dc2b3ca133933663c9/notes_pre_post/1040g3k031ppgh41m4g604a7r1e8cb33vtgfp63o!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q862" t="inlineStr">
+        <is>
+          <t>['如果没有如果']</t>
+        </is>
+      </c>
+      <c r="R862" t="inlineStr">
+        <is>
+          <t>2025-12-07 13:29:27</t>
+        </is>
+      </c>
+      <c r="S862" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T862" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>6935002c000000000d0357a3</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6935002c000000000d0357a3?xsec_token=ABGTjvX1hM0hmuag98FUYYxwZxJOEjrF6GvQUPDExmH6k=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>4月缘分开始的地方</t>
+        </is>
+      </c>
+      <c r="I863" t="inlineStr">
+        <is>
+          <t>寻找下一个
+缘分
+#我的炒股日记[话题]# #下一个更好[话题]#</t>
+        </is>
+      </c>
+      <c r="J863" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="K863" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="L863" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="M863" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N863" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O863" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P863" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130101/035acb7980be39be08f3b881f56b1900/notes_pre_post/1040g3k831pp764l0kmag4a7r1e8cb33vh4p2g08!nd_dft_wlteh_jpg_3', 'http://sns-webpic-qc.xhscdn.com/202602130101/a3461e17812583c6e28a1e23dd825372/notes_pre_post/1040g3k831pp764l0kma04a7r1e8cb33v8tcbolg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q863" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '下一个更好']</t>
+        </is>
+      </c>
+      <c r="R863" t="inlineStr">
+        <is>
+          <t>2025-12-07 12:18:52</t>
+        </is>
+      </c>
+      <c r="S863" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T863" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过) | 图2: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>6934d2e9000000000d03652b</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6934d2e9000000000d03652b?xsec_token=ABc2CGXrfxO5mAp06OyljFS3DC3IakUHIaMeIE1zGt1WM=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>我新高了</t>
+        </is>
+      </c>
+      <c r="I864" t="inlineStr">
+        <is>
+          <t>也终于跑赢大市了
+虽然错过了 有色金属 科技
+但 这就是我的风格  不懂不碰
+先稳住   股息拿到手再说
+再考虑接下去的事
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J864" t="inlineStr">
+        <is>
+          <t>1907</t>
+        </is>
+      </c>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="L864" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="M864" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N864" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O864" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P864" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130106/de6bd4350e25b41a58199f84e486044b/notes_pre_post/1040g3k831pp764l0kmc04a7r1e8cb33viihebeo!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q864" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R864" t="inlineStr">
+        <is>
+          <t>2025-12-07 09:05:45</t>
+        </is>
+      </c>
+      <c r="S864" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T864" t="inlineStr">
+        <is>
+          <t>图1: OCR超时/失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>6934c500000000000d034244</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6934c500000000000d034244?xsec_token=ABc2CGXrfxO5mAp06OyljFS7BYSv1oaQO3Rnyc91WTj84=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>再发几次 提示下</t>
+        </is>
+      </c>
+      <c r="I865" t="inlineStr">
+        <is>
+          <t>三哥劝你们别抄我作业
+这几天 看到某些留言 说她买三哥体验感好…
+笑死了…哪里好了
+前几个月 别人天天上去 他还再下来  早就天塌了要叫N个月了
+人啊 很奇怪  格局到低点 就开始沾沾自喜
+月 可是一个有一根  三哥回踩了4个月  120天
+120天那么好的市场不上去
+你能受得了？
+#希望大家认真看[话题]#</t>
+        </is>
+      </c>
+      <c r="J865" t="inlineStr">
+        <is>
+          <t>2118</t>
+        </is>
+      </c>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="L865" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="M865" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="N865" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O865" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P865" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130112/20fb2ea9eb0cbdc302b7ab1742f3db9b/notes_pre_post/1040g3k831pp764l0kmcg4a7r1e8cb33v756t5p0!nd_dft_wlteh_jpg_3', 'http://sns-webpic-qc.xhscdn.com/202602130112/1f74db8274210448d14ede5beec07710/notes_pre_post/1040g3k831pp764l0kmdg4a7r1e8cb33vg5h1hvo!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q865" t="inlineStr">
+        <is>
+          <t>['希望大家认真看']</t>
+        </is>
+      </c>
+      <c r="R865" t="inlineStr">
+        <is>
+          <t>2025-12-07 08:06:24</t>
+        </is>
+      </c>
+      <c r="S865" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T865" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过) | 图2: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>693443c1000000001b031b95</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693443c1000000001b031b95?xsec_token=ABc2CGXrfxO5mAp06OyljFS3bo3SuQnLKh8Gtmpk7gyfg=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>复盘</t>
+        </is>
+      </c>
+      <c r="I866" t="inlineStr">
+        <is>
+          <t>有点晚了  我反而更精神了
+仔细观察后 盘算着 赠品率 网格率等等
+先说结论
+如果换我 我会设网格
+这次可能是月小坑的调整了 之前一直月看上去小坑  但周并没有 20周30周去交叉60周  价格走到60周下  但这次样子有点像了  可以参考宽带A  价格去了60周下
+移不动A不是BYD   如果是我的话  我不会什么等着20周 30周站上60周再去动手这种事发生   参考之前的海油A
+每一次周下 都是格局点 前提看清赠品率
+当下boll周下104左右
+每个月电话费～ 赠品4.6％ 不能说非常不错 但也很不错了
+如果继续周下继续延伸去99每月电话费呢？
+那么赠品率4.8％ 😸😸不比小渣猫差了
+所以网格很简单啊
+第一档网格： 月20 自己看看 是不是正好  是周的boll下轨附近
+第二档网格： 月30
+如果继续下去呢？
+简单 下一档 赠品5.5％ 推算88左右
+继续？？  再下去？？？？
+#复盘[话题]#</t>
+        </is>
+      </c>
+      <c r="J866" t="inlineStr">
+        <is>
+          <t>2106</t>
+        </is>
+      </c>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>779</t>
+        </is>
+      </c>
+      <c r="L866" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="M866" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="N866" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O866" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P866" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130117/3803c81b2215a35142408eeaca298d1b/notes_pre_post/1040g3k031pon3rs14k004a7r1e8cb33vrpln8l0!nd_dft_wgth_jpg_3', 'http://sns-webpic-qc.xhscdn.com/202602130117/538dbed95f01fb98f8f6f285f1fdd6c4/notes_pre_post/1040g3k031pon34i3kk5g4a7r1e8cb33voknin9o!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q866" t="inlineStr">
+        <is>
+          <t>['复盘']</t>
+        </is>
+      </c>
+      <c r="R866" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:54:57</t>
+        </is>
+      </c>
+      <c r="S866" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T866" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过) | 图2: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>693411aa0000000019026e4e</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693411aa0000000019026e4e?xsec_token=ABc2CGXrfxO5mAp06OyljFS_pjA-6e4n1aFtZ3JwjMVMg=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I867" t="inlineStr">
+        <is>
+          <t>宽带H性价比
+已经没有
+移不动A高了
+我自己观点</t>
+        </is>
+      </c>
+      <c r="J867" t="inlineStr">
+        <is>
+          <t>1666</t>
+        </is>
+      </c>
+      <c r="K867" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="L867" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="M867" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N867" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O867" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P867" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130122/8ea7a97eaac3dca297c932a40333e9fa/1040g2sg31po986la4mag4a7r1e8cb33v6ub91a8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q867" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R867" t="inlineStr">
+        <is>
+          <t>2025-12-06 19:21:14</t>
+        </is>
+      </c>
+      <c r="S867" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T867" t="inlineStr">
+        <is>
+          <t>图1: ”, 宽带H性价比, 已经没有, 移不动A高了, 我自己观点</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>6934085e00000000190272d0</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6934085e00000000190272d0?xsec_token=ABc2CGXrfxO5mAp06OyljFS76zBDhyCnCNk915j72rb_0=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>4月 5月 这图发了很多次</t>
+        </is>
+      </c>
+      <c r="I868" t="inlineStr">
+        <is>
+          <t>啊哈哈哈哈哈哈哈哈哈哈哈
+#我的炒股日记[话题]# #期待下一年[话题]#</t>
+        </is>
+      </c>
+      <c r="J868" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="L868" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="M868" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="N868" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O868" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P868" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130128/abb1b3ab60034fac507f935e319aa08b/notes_pre_post/1040g3k031po65s8okg404a7r1e8cb33v71icfbg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q868" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '期待下一年']</t>
+        </is>
+      </c>
+      <c r="R868" t="inlineStr">
+        <is>
+          <t>2025-12-06 18:41:34</t>
+        </is>
+      </c>
+      <c r="S868" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T868" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>693405f9000000000d0349f8</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693405f9000000000d0349f8?xsec_token=ABc2CGXrfxO5mAp06OyljFS_ZKtdoaIY94w-MeRqP3cOM=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>金融强国</t>
+        </is>
+      </c>
+      <c r="I869" t="inlineStr">
+        <is>
+          <t>我来时 就一直说的主题
+#我的炒股日记[话题]# #金融[话题]# #金融知识[话题]# #当代中国经济[话题]# #财经知识[话题]# #金融与投资[话题]# #金融求职[话题]# #金融行业[话题]# #企业融资[话题]# #宏观经济[话题]#</t>
+        </is>
+      </c>
+      <c r="J869" t="inlineStr">
+        <is>
+          <t>1719</t>
+        </is>
+      </c>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="L869" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="M869" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="N869" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O869" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P869" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130133/fc8ccf80e2c5db13d7011af5e26d9c4f/notes_pre_post/1040g3k031po65s8okg3g4a7r1e8cb33vekbcth8!nd_dft_wlteh_jpg_3', 'http://sns-webpic-qc.xhscdn.com/202602130133/cb3d6a76a4511b7a2a58e599d73d723b/notes_pre_post/1040g3k031po65s8okg204a7r1e8cb33vn3r30r8!nd_dft_wgth_jpg_3', 'http://sns-webpic-qc.xhscdn.com/202602130133/242f98a732e8cdc0332e726d6e312aeb/notes_pre_post/1040g3k031po65s8okg2g4a7r1e8cb33v0kmkmm0!nd_dft_wlteh_jpg_3', 'http://sns-webpic-qc.xhscdn.com/202602130133/eabdaec605c42934ce223250968b96e7/notes_pre_post/1040g3k031po65s8okg0g4a7r1e8cb33v1k1rahg!nd_dft_wlteh_jpg_3', 'http://sns-webpic-qc.xhscdn.com/202602130133/1c72010273646b5a6e118213ce759a4a/notes_pre_post/1040g3k031po65s8okg304a7r1e8cb33vg9tgmlg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q869" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '金融', '金融知识', '当代中国经济', '财经知识', '金融与投资', '金融求职', '金融行业', '企业融资', '宏观经济']</t>
+        </is>
+      </c>
+      <c r="R869" t="inlineStr">
+        <is>
+          <t>2025-12-06 18:31:21</t>
+        </is>
+      </c>
+      <c r="S869" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T869" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过) | 图2: 非文字图(跳过) | 图3: 非文字图(跳过) | 图4: 非文字图(跳过) | 图5: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>6933f90c000000000d0395bb</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6933f90c000000000d0395bb?xsec_token=ABnkRGF0jbL-R2Mxymit_ZOzDC_bnl5wECFwjmUGdffUU=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>羁绊</t>
+        </is>
+      </c>
+      <c r="I870" t="inlineStr">
+        <is>
+          <t>有些事 再说 与 不说 之间 我选择了说
+但多问就俗了
+还有很多人稍微有点边界感
+凭什么你问了 我就要回答  你谁啊
+我再一次重申
+你们只是再没经过我同意之下 自己看到我的小红书乱写内容
+我既没收28 也没各种稀奇古怪的什么qun
+跟 某号
+所以 我说是好心  不说 也正常
+不要把别人的好心 当应该的
+农夫与蛇这故事 读书时老师教过 我也理解
+但我不是农夫  你是不是🐍  跟我没关系</t>
+        </is>
+      </c>
+      <c r="J870" t="inlineStr">
+        <is>
+          <t>2263</t>
+        </is>
+      </c>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="L870" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="M870" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="N870" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O870" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P870" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130138/9645665ba3a47c6f0c4f4ef609aca0bf/notes_pre_post/1040g3k031po65s8okg104a7r1e8cb33vubojltg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q870" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R870" t="inlineStr">
+        <is>
+          <t>2025-12-06 17:36:12</t>
+        </is>
+      </c>
+      <c r="S870" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T870" t="inlineStr">
+        <is>
+          <t>图1: OCR超时/失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>6933cef40000000019026f69</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6933cef40000000019026f69?xsec_token=ABnkRGF0jbL-R2Mxymit_ZO5pOq5dolX_ocUrEtk4vq7A=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>牙膏是早就突了
+牛奶是没突
+不一样噢</t>
+        </is>
+      </c>
+      <c r="J871" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="L871" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="M871" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="N871" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O871" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P871" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130144/5e30ff917b023be87d1d76bc5915f57b/1040g2sg31po986la4mdg4a7r1e8cb33veh78o18!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q871" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R871" t="inlineStr">
+        <is>
+          <t>2025-12-06 14:36:36</t>
+        </is>
+      </c>
+      <c r="S871" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T871" t="inlineStr">
+        <is>
+          <t>图1: ”', 牙膏是早就突了, 牛奶是没突, 不一样噢</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>6933be9e0000000019024c1e</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6933be9e0000000019024c1e?xsec_token=ABnkRGF0jbL-R2Mxymit_ZO9FdzzyxkopIt0tKgPCht2s=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>丑的 回答 牛奶</t>
+        </is>
+      </c>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>抓紧学 给我学！！！！周末学习！！！！
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J872" t="inlineStr">
+        <is>
+          <t>2246</t>
+        </is>
+      </c>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>723</t>
+        </is>
+      </c>
+      <c r="L872" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="M872" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="N872" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O872" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P872" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130150/063ad52f0c2a0a68576b601791a70085/notes_pre_post/1040g3k031po781s9ku004a7r1e8cb33vu5k3mj8!nd_dft_wgth_jpg_3', 'http://sns-webpic-qc.xhscdn.com/202602130150/a52b07fd137fe3958805775fa0d669e4/notes_pre_post/1040g3k031po65s8okg5g4a7r1e8cb33v9hiplh8!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q872" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R872" t="inlineStr">
+        <is>
+          <t>2025-12-06 13:26:54</t>
+        </is>
+      </c>
+      <c r="S872" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T872" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过) | 图2: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>6933b9e70000000019027058</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6933b9e70000000019027058?xsec_token=ABnkRGF0jbL-R2Mxymit_ZOyv-MCLaMxkI4jH9fECZWr8=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>快突了～</t>
+        </is>
+      </c>
+      <c r="I873" t="inlineStr">
+        <is>
+          <t>一闪一闪亮晶晶
+留下K线的痕迹
+我的心中的自选
+依然还是你
+一年一年又一年
+飞逝尽在一转眼
+唯一永远不改变
+是不停的改变
+#该来的总会来[话题]#</t>
+        </is>
+      </c>
+      <c r="J873" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="L873" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="M873" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="N873" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O873" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P873" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130155/f61934c0a4315d0804a4f85d319d254f/notes_pre_post/1040g3k031po65s8okg604a7r1e8cb33v1vabsd8!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q873" t="inlineStr">
+        <is>
+          <t>['该来的总会来']</t>
+        </is>
+      </c>
+      <c r="R873" t="inlineStr">
+        <is>
+          <t>2025-12-06 13:06:47</t>
+        </is>
+      </c>
+      <c r="S873" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T873" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>6933b637000000000d00fe51</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6933b637000000000d00fe51?xsec_token=ABnkRGF0jbL-R2Mxymit_ZO02zSnWwriuDwuPA8X0Zcb8=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>突错～</t>
+        </is>
+      </c>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>她从来没突过 她会这样说
+从来没突过 所以买错
+她从哪里起飞  从哪里降落
+多少不能原谅的错 却不能重来过
+#差一点就差一点[话题]#</t>
+        </is>
+      </c>
+      <c r="J874" t="inlineStr">
+        <is>
+          <t>1292</t>
+        </is>
+      </c>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="L874" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="M874" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N874" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O874" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P874" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130200/caefa5de105f739c8381f16de47a73aa/notes_pre_post/1040g3k031po65s8okg6g4a7r1e8cb33vv5h1brg!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q874" t="inlineStr">
+        <is>
+          <t>['差一点就差一点']</t>
+        </is>
+      </c>
+      <c r="R874" t="inlineStr">
+        <is>
+          <t>2025-12-06 12:51:03</t>
+        </is>
+      </c>
+      <c r="S874" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T874" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>6933adc70000000019026b4f</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6933adc70000000019026b4f?xsec_token=ABnkRGF0jbL-R2Mxymit_ZOwtY362WtBnZttOz-QCJkyY=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>做 坚持做 就好</t>
+        </is>
+      </c>
+      <c r="I875" t="inlineStr">
+        <is>
+          <t>我发探店不专业
+逻辑是 专业了就限流了家人们能理解了吗
+说到这里应该能懂了吧 那么既然我的使命是分享低波动红利策略 那就垂直吧内容
+但支持实体经济这事
+我可以变相的做
+是水平差 但做 比 不做好</t>
+        </is>
+      </c>
+      <c r="J875" t="inlineStr">
+        <is>
+          <t>1714</t>
+        </is>
+      </c>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="L875" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="M875" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N875" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O875" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P875" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130205/fc9a50fba758689e894a78522cf20868/1040g2sg31po0ruhekuf04a7r1e8cb33vfs01k7o!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q875" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R875" t="inlineStr">
+        <is>
+          <t>2025-12-06 12:15:03</t>
+        </is>
+      </c>
+      <c r="S875" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T875" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>6933a3ad000000000d03b7b2</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6933a3ad000000000d03b7b2?xsec_token=ABnkRGF0jbL-R2Mxymit_ZO-q3XLeDV56e82jVsAABZtY=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>如果哪天别人推荐你说的公司
+他做什么的 你都不知道
+那么大概率 就是错误的
+如果别人说什么 你会想 啊呀不就是大马路上有的吗 且就是行业龙头啊  恭喜你  你解锁了低波动红利策略#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J876" t="inlineStr">
+        <is>
+          <t>1755</t>
+        </is>
+      </c>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="L876" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="M876" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N876" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O876" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P876" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130210/7f3798b5459ea299ef3c321ddf2cbfb6/1040g2sg31po0ruhekufg4a7r1e8cb33v2gjonsg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q876" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R876" t="inlineStr">
+        <is>
+          <t>2025-12-06 11:31:57</t>
+        </is>
+      </c>
+      <c r="S876" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T876" t="inlineStr">
+        <is>
+          <t>图1: 如果哪天别人推荐你说, 的公司, 他做什么的你都不知道, 那么大概率, 率就是错误的, 如果别人说什么你会想, 啊呀不就是大马路上有, 的吗, 且就是行业龙头啊, 恭喜你, 你解锁了低波, 动红利策略</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>6933a2b5000000000d03f585</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6933a2b5000000000d03f585?xsec_token=ABnkRGF0jbL-R2Mxymit_ZOzBr9kxpJ7MJjPeThm3JSnU=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>水 电 煤 买 洗 烧</t>
+        </is>
+      </c>
+      <c r="I877" t="inlineStr">
+        <is>
+          <t>基础设施
+基础消费
+电
+电话宽带
+白色家电
+生活基础消费用品
+暂时 而 不是</t>
+        </is>
+      </c>
+      <c r="J877" t="inlineStr">
+        <is>
+          <t>2041</t>
+        </is>
+      </c>
+      <c r="K877" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="L877" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="M877" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="N877" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O877" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P877" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130216/51e5b5a95346d13a34758a1c4ddae25b/1040g2sg31po0ruhekugg4a7r1e8cb33vsbth5ao!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q877" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R877" t="inlineStr">
+        <is>
+          <t>2025-12-06 11:27:50</t>
+        </is>
+      </c>
+      <c r="S877" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T877" t="inlineStr">
+        <is>
+          <t>图1: 基础设施, 基础消费, 电, 电话宽带, 白色家电, 生活基础消费用品, 暂时而不是</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>6933a14e0000000019025d64</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6933a14e0000000019025d64?xsec_token=ABnkRGF0jbL-R2Mxymit_ZO0XDM_uCWT1iF0IxaQfTa1g=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>问 反问 思考</t>
+        </is>
+      </c>
+      <c r="I878" t="inlineStr">
+        <is>
+          <t>资源这事 有就有
+没有就没有
+有了也不一定肯告诉你
+没有也可以瞎说  反问自己
+是不是央国企
+是不是龙头
+是不是有稳定分红
+是不是永续
+是不是千亿市值
+是不是基础设施离生活不开
+#解决实际问题[话题]# #发自内心的疑问[话题]# #换个角度看问题[话题]# #思维方式转变[话题]# #不同角度看问题[话题]# #一起来探讨[话题]# #换个角度思考[话题]# #打破常规固化思维[话题]# #没有方向感[话题]# #我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J878" t="inlineStr">
+        <is>
+          <t>2113</t>
+        </is>
+      </c>
+      <c r="K878" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="L878" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="M878" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N878" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O878" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P878" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130221/757d7c678206b168015dc7dae696c7c3/1040g2sg31po0ruhekui04a7r1e8cb33vicdpsp8!nd_dft_wlteh_webp_3']</t>
+        </is>
+      </c>
+      <c r="Q878" t="inlineStr">
+        <is>
+          <t>['解决实际问题', '发自内心的疑问', '换个角度看问题', '思维方式转变', '不同角度看问题', '一起来探讨', '换个角度思考', '打破常规固化思维', '没有方向感', '我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R878" t="inlineStr">
+        <is>
+          <t>2025-12-06 11:21:50</t>
+        </is>
+      </c>
+      <c r="S878" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T878" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>69338a4f000000001b0302bb</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69338a4f000000001b0302bb?xsec_token=ABnkRGF0jbL-R2Mxymit_ZO6hKiMCCSb9jRGqbL8-01wk=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>以后的以后</t>
+        </is>
+      </c>
+      <c r="I879" t="inlineStr">
+        <is>
+          <t>水电
+当年赠品率40％
+后面因为设备收回成本了 业绩上去了 那么赠品涨到赠品率80％
+那么清洁电如果现在40％赠品率 以后呢#降本增效新模式[话题]#</t>
+        </is>
+      </c>
+      <c r="J879" t="inlineStr">
+        <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="L879" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="M879" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="N879" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O879" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P879" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130226/2c26a457814d77d555d6250c04882798/1040g2sg31po0ruhekuk04a7r1e8cb33v08b2ubo!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q879" t="inlineStr">
+        <is>
+          <t>['降本增效新模式']</t>
+        </is>
+      </c>
+      <c r="R879" t="inlineStr">
+        <is>
+          <t>2025-12-06 09:43:43</t>
+        </is>
+      </c>
+      <c r="S879" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T879" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>69337288000000000d039777</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69337288000000000d039777?xsec_token=ABnkRGF0jbL-R2Mxymit_ZO3DLiQWe4CwVXNb2RvI6PO4=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I880" t="inlineStr">
+        <is>
+          <t>2026年我自己的计划
+基础消费  牙膏 等待突破后的牛奶
+基础消费  宽带   移不动A等机会
+基础消费   电 电 电！！！
+基础消费   出海产品  等周中
+出海  怎么出海  怎么回来
+大金融继续格局着当安全垫  且每年赠品拿走
+改善流动性   期待 3哥能不能突一下
+港口再观察
+暂时就这些
+一句概括基础生活消费
+#写下自己近期的目标[话题]#</t>
+        </is>
+      </c>
+      <c r="J880" t="inlineStr">
+        <is>
+          <t>4381</t>
+        </is>
+      </c>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>2810</t>
+        </is>
+      </c>
+      <c r="L880" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="M880" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="N880" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O880" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P880" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130232/0f6cb6d76eaea3fcbbefe7e22d94c174/1040g00831pnf1aerku3g4a7r1e8cb33vmooouj0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q880" t="inlineStr">
+        <is>
+          <t>['写下自己近期的目标']</t>
+        </is>
+      </c>
+      <c r="R880" t="inlineStr">
+        <is>
+          <t>2025-12-06 08:02:16</t>
+        </is>
+      </c>
+      <c r="S880" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T880" t="inlineStr">
+        <is>
+          <t>图1: ”, 2026年我, 自己的计划</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>69330354000000000d039085</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69330354000000000d039085?xsec_token=ABnkRGF0jbL-R2Mxymit_ZO-rSIVa7aYIDd3vgKjUtfLE=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>K线之王～</t>
+        </is>
+      </c>
+      <c r="I881" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J881" t="inlineStr">
+        <is>
+          <t>2056</t>
+        </is>
+      </c>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="L881" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="M881" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N881" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O881" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P881" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130237/179e85dda8879d5a82d6a45695504828/1040g00831pnf1aerku504a7r1e8cb33v50l5u80!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q881" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R881" t="inlineStr">
+        <is>
+          <t>2025-12-06 00:07:48</t>
+        </is>
+      </c>
+      <c r="S881" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T881" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>6932f83e000000001b022775</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6932f83e000000001b022775?xsec_token=AB_upEGaSMKcSsc59Jvl3yNmd10-e1xQOz3XGf_G3eeuk=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>我确实 拍照拍不好</t>
+        </is>
+      </c>
+      <c r="I882" t="inlineStr">
+        <is>
+          <t>你们真的不懂
+我发的所谓探店
+都是为了助力所谓的实体经济
+我需要探店吗？[微笑R][微笑R][微笑R]
+我只是想帮助他们罢了
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J882" t="inlineStr">
+        <is>
+          <t>1892</t>
+        </is>
+      </c>
+      <c r="K882" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="L882" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="M882" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N882" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O882" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P882" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130242/9dbb65ca60352bd5b70e1adb2ca414f5/1040g00831pnf1aerku6g4a7r1e8cb33vjj5cup0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q882" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R882" t="inlineStr">
+        <is>
+          <t>2025-12-05 23:20:30</t>
+        </is>
+      </c>
+      <c r="S882" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T882" t="inlineStr">
+        <is>
+          <t>图1: ,, 你们真的不懂, 我发的所谓探店, 都是为了助力所谓的实, 体经济, 我需要探店吗？, 我只是想帮助他们罢了</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>6932b056000000000d00c182</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6932b056000000000d00c182?xsec_token=AB_upEGaSMKcSsc59Jvl3yNm6SAo7LKQ5jApfwVIfJdqA=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>周末放松下</t>
+        </is>
+      </c>
+      <c r="I883" t="inlineStr">
+        <is>
+          <t>大家周末快乐
+[微笑R][微笑R][微笑R][微笑R]#迎接周末的正确打开方式[话题]#</t>
+        </is>
+      </c>
+      <c r="J883" t="inlineStr">
+        <is>
+          <t>1676</t>
+        </is>
+      </c>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L883" t="inlineStr">
+        <is>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="M883" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N883" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O883" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P883" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130248/86573638080b0525fdbd1796fa3e1852/notes_pre_post/1040g3k831pn68k3052dg4a7r1e8cb33vtp4a7u8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q883" t="inlineStr">
+        <is>
+          <t>['迎接周末的正确打开方式']</t>
+        </is>
+      </c>
+      <c r="R883" t="inlineStr">
+        <is>
+          <t>2025-12-05 18:13:42</t>
+        </is>
+      </c>
+      <c r="S883" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T883" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>6932a476000000000d03dc99</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6932a476000000000d03dc99?xsec_token=AB_upEGaSMKcSsc59Jvl3yNh5du6LrKiMP0kfF_WRQlRY=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>十年</t>
+        </is>
+      </c>
+      <c r="I884" t="inlineStr">
+        <is>
+          <t>年底了 好累
+平平安安 稳稳定定就好
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J884" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="L884" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="M884" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="N884" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O884" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P884" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130253/490ebb44d3705f98fd1130994a2e6a70/notes_pre_post/1040g3k031pmte9leku2g4a7r1e8cb33vkfueoog!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q884" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R884" t="inlineStr">
+        <is>
+          <t>2025-12-05 17:23:02</t>
+        </is>
+      </c>
+      <c r="S884" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T884" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>69329239000000000d00ed9d</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69329239000000000d00ed9d?xsec_token=AB_upEGaSMKcSsc59Jvl3yNomkxvy-M6WRTVxhwiRlTaQ=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>🥳在小红书赞和收藏破500万啦！️️</t>
+        </is>
+      </c>
+      <c r="I885" t="inlineStr">
+        <is>
+          <t>#谢谢我的粉丝[话题]# #内容创造者[话题]# #优质内容输出者[话题]# #感谢大家一路支持陪伴[话题]# #多谢大家的支持[话题]# #粉丝[话题]# #专业号助手[话题]# #谢谢大家喜欢[话题]# #作品推广小红书[话题]# #小红书运营[话题]#</t>
+        </is>
+      </c>
+      <c r="J885" t="inlineStr">
+        <is>
+          <t>2252</t>
+        </is>
+      </c>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="L885" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="M885" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N885" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O885" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P885" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130258/1ee87ab29d8791c923b5b963a4c8315c/notes_pre_post/1040g3k031pmte9leku304a7r1e8cb33vi30k670!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q885" t="inlineStr">
+        <is>
+          <t>['谢谢我的粉丝', '内容创造者', '优质内容输出者', '感谢大家一路支持陪伴', '多谢大家的支持', '粉丝', '专业号助手', '谢谢大家喜欢', '作品推广小红书', '小红书运营']</t>
+        </is>
+      </c>
+      <c r="R885" t="inlineStr">
+        <is>
+          <t>2025-12-05 16:05:13</t>
+        </is>
+      </c>
+      <c r="S885" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T885" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>69328c51000000001b0312c0</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69328c51000000001b0312c0?xsec_token=AB_upEGaSMKcSsc59Jvl3yNjP6x1Ju2jNkkdt1yQg3to4=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>周末快乐</t>
+        </is>
+      </c>
+      <c r="I886" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J886" t="inlineStr">
+        <is>
+          <t>2187</t>
+        </is>
+      </c>
+      <c r="K886" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="L886" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="M886" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N886" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O886" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P886" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130303/a9be4b83d467bdadd3c7c573e1fbf45f/1040g00831pn1rpea4k604a7r1e8cb33v70c89ro!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q886" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R886" t="inlineStr">
+        <is>
+          <t>2025-12-05 15:40:01</t>
+        </is>
+      </c>
+      <c r="S886" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T886" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>69327d66000000000d00e9a3</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69327d66000000000d00e9a3?xsec_token=AB_upEGaSMKcSsc59Jvl3yNtn47C7hSIFBEGKvMiehe8o=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>看看 我有错过吗</t>
+        </is>
+      </c>
+      <c r="I887" t="inlineStr">
+        <is>
+          <t>#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J887" t="inlineStr">
+        <is>
+          <t>1783</t>
+        </is>
+      </c>
+      <c r="K887" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="L887" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="M887" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="N887" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O887" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P887" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130308/cf9411e6e07806088235acaaf47b7d63/notes_pre_post/1040g3k031pmte9leku3g4a7r1e8cb33vuu179eg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q887" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R887" t="inlineStr">
+        <is>
+          <t>2025-12-05 14:36:22</t>
+        </is>
+      </c>
+      <c r="S887" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T887" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>69327a11000000001b03211a</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69327a11000000001b03211a?xsec_token=AB_upEGaSMKcSsc59Jvl3yNqQuYyGmrz4vWn56EznCzSc=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I888" t="inlineStr">
+        <is>
+          <t>我的高光时刻 不是现在
+我说过很多次了
+我的高光时刻
+再大金融高低切消费
+现在还有个 电</t>
+        </is>
+      </c>
+      <c r="J888" t="inlineStr">
+        <is>
+          <t>2224</t>
+        </is>
+      </c>
+      <c r="K888" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="L888" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="M888" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="N888" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O888" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P888" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130313/ec6d37f3f62e0a692f58feadbe51eb93/1040g00831pmt9pfajq0g5q6h4ijollef5a1c04g!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q888" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R888" t="inlineStr">
+        <is>
+          <t>2025-12-05 14:22:09</t>
+        </is>
+      </c>
+      <c r="S888" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T888" t="inlineStr">
+        <is>
+          <t>图1: ”, 我的高光时刻, 不是, 现在, 我说过很多次了, 我的高光时刻, 再大金融高低切消费, 现在还有个电</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>6932728d000000000d0392aa</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6932728d000000000d0392aa?xsec_token=AB_upEGaSMKcSsc59Jvl3yNkJQf2I1H_n_BZYgKTE48Ao=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I889" t="inlineStr">
+        <is>
+          <t>家人们 低调点
+赚了金币
+切记 改善家人生活
+不要乱花 再一次提醒
+人品＝财运</t>
+        </is>
+      </c>
+      <c r="J889" t="inlineStr">
+        <is>
+          <t>8760</t>
+        </is>
+      </c>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="L889" t="inlineStr">
+        <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="M889" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="N889" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O889" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P889" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130319/81707fca4395f774a9e6652d84c09dcc/1040g00831pmt9pfajq1g5q6h4ijolleft43fbug!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q889" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R889" t="inlineStr">
+        <is>
+          <t>2025-12-05 13:50:05</t>
+        </is>
+      </c>
+      <c r="S889" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T889" t="inlineStr">
+        <is>
+          <t>图1: ”, 家人们低调点, 赚了金币, 切记改善家人生活, 不要乱花再一次, 提醒, 人品=财运</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>69326fd20000000019027bac</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69326fd20000000019027bac?xsec_token=AB_upEGaSMKcSsc59Jvl3yNuXkQLQJDouulOlpRb_aWPE=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I890" t="inlineStr">
+        <is>
+          <t>嗖
+平安姑娘A＋H
+各格局掉 1％#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J890" t="inlineStr">
+        <is>
+          <t>1553</t>
+        </is>
+      </c>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="L890" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="M890" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="N890" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O890" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P890" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130324/ff82bc3502f5f1bace747bfd22e46e02/1040g00831pmt9pfajq305q6h4ijollefmrsqaoo!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q890" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R890" t="inlineStr">
+        <is>
+          <t>2025-12-05 13:38:26</t>
+        </is>
+      </c>
+      <c r="S890" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T890" t="inlineStr">
+        <is>
+          <t>图1: 嗖, 平安姑娘A+H, 各格局掉1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>6932687d000000000d03e601</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6932687d000000000d03e601?xsec_token=AB_upEGaSMKcSsc59Jvl3yNkrrwNUAXRSs0Y1UPl1utzw=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>让我装下</t>
+        </is>
+      </c>
+      <c r="I891" t="inlineStr">
+        <is>
+          <t>别拦住我#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J891" t="inlineStr">
+        <is>
+          <t>1488</t>
+        </is>
+      </c>
+      <c r="K891" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="L891" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="M891" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N891" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O891" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P891" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130330/eebc44af999b018040f13051b93b7e8e/notes_pre_post/1040g3k031pmte9leku504a7r1e8cb33v17b8ed0!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q891" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R891" t="inlineStr">
+        <is>
+          <t>2025-12-05 13:07:09</t>
+        </is>
+      </c>
+      <c r="S891" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T891" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>6932680f00000000190252bf</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6932680f00000000190252bf?xsec_token=AB_upEGaSMKcSsc59Jvl3yNlEZ3txQRIBdOoFT-wcANhE=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>让我装一下</t>
+        </is>
+      </c>
+      <c r="I892" t="inlineStr">
+        <is>
+          <t>#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J892" t="inlineStr">
+        <is>
+          <t>1645</t>
+        </is>
+      </c>
+      <c r="K892" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="L892" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="M892" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N892" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O892" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P892" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130335/2e856383bf845a49c73eb9ead41646df/notes_pre_post/1040g3k031pmte9leku6g4a7r1e8cb33vhqn9luo!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q892" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R892" t="inlineStr">
+        <is>
+          <t>2025-12-05 13:05:19</t>
+        </is>
+      </c>
+      <c r="S892" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T892" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>693267a8000000001b0253d7</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693267a8000000001b0253d7?xsec_token=AB_upEGaSMKcSsc59Jvl3yNpByQ624DhBr_NaUc0pou48=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>珍惜吧</t>
+        </is>
+      </c>
+      <c r="I893" t="inlineStr">
+        <is>
+          <t>1.83的2倍=3.66
+1.83的2.5倍＝4.575
+1.83的3倍＝5.49
+十年国债最新本1.83#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J893" t="inlineStr">
+        <is>
+          <t>1532</t>
+        </is>
+      </c>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="L893" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="M893" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N893" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O893" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P893" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130340/c7bb87179d96fc479ba062ed0aaed43b/1040g00831pmt9pfajq5g5q6h4ijollefu3a1dj0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q893" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R893" t="inlineStr">
+        <is>
+          <t>2025-12-05 13:03:36</t>
+        </is>
+      </c>
+      <c r="S893" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T893" t="inlineStr">
+        <is>
+          <t>图1: 1.83的2倍=3.66, 1.83的2.5倍=4., 575, 1.83的3倍=5.49, 十年国债最新本1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>693240e8000000000d035630</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693240e8000000000d035630?xsec_token=AB_upEGaSMKcSsc59Jvl3yNmUar1wR8WwJg07H3bFnKBI=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>复盘的魅力</t>
+        </is>
+      </c>
+      <c r="I894" t="inlineStr">
+        <is>
+          <t>是不是
+砸了[斜眼R]
+#逻辑的力量[话题]#</t>
+        </is>
+      </c>
+      <c r="J894" t="inlineStr">
+        <is>
+          <t>1577</t>
+        </is>
+      </c>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="L894" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="M894" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N894" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O894" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P894" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130346/d2a7dc242b4f989e3d251844f37a1ae0/notes_pre_post/1040g3k831pm4jrcol2c04a7r1e8cb33vgc226n8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q894" t="inlineStr">
+        <is>
+          <t>['逻辑的力量']</t>
+        </is>
+      </c>
+      <c r="R894" t="inlineStr">
+        <is>
+          <t>2025-12-05 10:18:16</t>
+        </is>
+      </c>
+      <c r="S894" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T894" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
+++ b/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T894"/>
+  <dimension ref="A1:T908"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61698,6 +61698,1464 @@
         </is>
       </c>
     </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>693230ae000000000d00fe6a</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693230ae000000000d00fe6a?xsec_token=AB_upEGaSMKcSsc59Jvl3yNjSBirepPaYnfPBUH-IxO9A=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>马上平安夜了</t>
+        </is>
+      </c>
+      <c r="I895" t="inlineStr">
+        <is>
+          <t>如果是我 我会设网格了
+特别昨天
+日60附近 其实就是周20附近
+如果是我之前没格局过的
+第一次想格局
+周20 一笔
+周30-周60一笔
+比例 2：5这种
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J895" t="inlineStr">
+        <is>
+          <t>1715</t>
+        </is>
+      </c>
+      <c r="K895" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="L895" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="M895" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="N895" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O895" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P895" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130953/a29a95ff83737cc7647a8070345d06fe/notes_pre_post/1040g3k831pm4jrcol2cg4a7r1e8cb33v01kello!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q895" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R895" t="inlineStr">
+        <is>
+          <t>2025-12-05 09:09:02</t>
+        </is>
+      </c>
+      <c r="S895" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T895" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>6931b3aa000000000d036345</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6931b3aa000000000d036345?xsec_token=ABcGlVj7chOjAwiSxlL6IEs3dlmCRtxxthh0jjPUDxtLU=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>如果 所以</t>
+        </is>
+      </c>
+      <c r="I896" t="inlineStr">
+        <is>
+          <t>20要突120了
+但如果换成我
+我会大阴天再来一次
+然后拉起来[捂嘴笑R]
+但没有如果  随缘吧[斜眼R]</t>
+        </is>
+      </c>
+      <c r="J896" t="inlineStr">
+        <is>
+          <t>1542</t>
+        </is>
+      </c>
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="L896" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="M896" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N896" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O896" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P896" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602130959/c79d88928ef6595b0d4fa56de56d2a47/notes_pre_post/1040g3k831pm4jrcol2b04a7r1e8cb33vdqsv6ag!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q896" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R896" t="inlineStr">
+        <is>
+          <t>2025-12-05 00:15:38</t>
+        </is>
+      </c>
+      <c r="S896" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T896" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>69319cad000000000d039f58</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69319cad000000000d039f58?xsec_token=ABcGlVj7chOjAwiSxlL6IEs5VgDJ6G4fLAcQu3_7yDFmw=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>月 当 周 看</t>
+        </is>
+      </c>
+      <c r="I897" t="inlineStr">
+        <is>
+          <t>如果季是长牛
+月但周看
+你会得到什么
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J897" t="inlineStr">
+        <is>
+          <t>1567</t>
+        </is>
+      </c>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="L897" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="M897" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="N897" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O897" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P897" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602131004/2381e88eaf454c870b9f924f51cd8f02/notes_pre_post/1040g3k831pm4jrcol2dg4a7r1e8cb33vv4k6590!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q897" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R897" t="inlineStr">
+        <is>
+          <t>2025-12-04 22:37:33</t>
+        </is>
+      </c>
+      <c r="S897" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T897" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>69318716000000001b022f86</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69318716000000001b022f86?xsec_token=ABcGlVj7chOjAwiSxlL6IEs3wcqzCge6dc-Tgrg3wz74U=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>说说 聊聊</t>
+        </is>
+      </c>
+      <c r="I898" t="inlineStr">
+        <is>
+          <t>#皮卡丘[话题]# #可爱玩具[话题]# #宝可梦[话题]# #手办周边分享[话题]# #宠物小精灵[话题]# #可爱摆件[话题]# #精灵宝可梦[话题]# #小玩具[话题]# #可达鸭[话题]# #桌面摆件[话题]#</t>
+        </is>
+      </c>
+      <c r="J898" t="inlineStr">
+        <is>
+          <t>2697</t>
+        </is>
+      </c>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>494</t>
+        </is>
+      </c>
+      <c r="L898" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
+      </c>
+      <c r="M898" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="N898" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O898" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P898" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602131009/be5241b71a2e9b87e547ef3d5207cdc6/1040g00831pm1ti0a52604a7r1e8cb33vfdrnd4g!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q898" t="inlineStr">
+        <is>
+          <t>['皮卡丘', '可爱玩具', '宝可梦', '手办周边分享', '宠物小精灵', '可爱摆件', '精灵宝可梦', '小玩具', '可达鸭', '桌面摆件']</t>
+        </is>
+      </c>
+      <c r="R898" t="inlineStr">
+        <is>
+          <t>2025-12-04 21:05:26</t>
+        </is>
+      </c>
+      <c r="S898" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T898" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>6931848c000000001902522d</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6931848c000000001902522d?xsec_token=ABcGlVj7chOjAwiSxlL6IEs_9989QSSeur0tQxa8ZwcS0=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I899" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J899" t="inlineStr">
+        <is>
+          <t>1733</t>
+        </is>
+      </c>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="L899" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="M899" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N899" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O899" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P899" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602131014/d0a13ea66bac35cfad2b432de8e09b70/1040g2sg31plv0h8rkueg4a7r1e8cb33vbmf23r0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q899" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R899" t="inlineStr">
+        <is>
+          <t>2025-12-04 20:54:36</t>
+        </is>
+      </c>
+      <c r="S899" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T899" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>693181f0000000000d03d143</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693181f0000000000d03d143?xsec_token=ABcGlVj7chOjAwiSxlL6IEs1WuWMcuRXh5l5CyS5slmkU=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I900" t="inlineStr">
+        <is>
+          <t>大家来小红书是提升自己
+学习策略后赢到金币
+改善家人生活的
+专注点都[微笑R]
+多看看我最近发的学习帖#我的学习进化论[话题]# #一起进步吧[话题]# #大家一起努力[话题]# #一起学习共同进步[话题]# #持续学习与成长[话题]# #互相学习交流[话题]# #挑战好好学习提升自我[话题]# #写下自己近期的目标[话题]# #终身学习[话题]# #向大佬学习[话题]#</t>
+        </is>
+      </c>
+      <c r="J900" t="inlineStr">
+        <is>
+          <t>2068</t>
+        </is>
+      </c>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="L900" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="M900" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="N900" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O900" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P900" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602131019/11b959aa4738f9feee0df81a335a392d/1040g2sg31plv0h8rkuf04a7r1e8cb33vmqvbkn0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q900" t="inlineStr">
+        <is>
+          <t>['我的学习进化论', '一起进步吧', '大家一起努力', '一起学习共同进步', '持续学习与成长', '互相学习交流', '挑战好好学习提升自我', '写下自己近期的目标', '终身学习', '向大佬学习']</t>
+        </is>
+      </c>
+      <c r="R900" t="inlineStr">
+        <is>
+          <t>2025-12-04 20:43:28</t>
+        </is>
+      </c>
+      <c r="S900" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T900" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>69317cce000000000d00c0d6</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69317cce000000000d00c0d6?xsec_token=ABcGlVj7chOjAwiSxlL6IEs11Z5U_R9iObtLzTxZNNR9o=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>转机</t>
+        </is>
+      </c>
+      <c r="I901" t="inlineStr">
+        <is>
+          <t>如果 只是 如果
+下周 再下周 下下周 不破前面新低
+知道意味着什么吗
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J901" t="inlineStr">
+        <is>
+          <t>1626</t>
+        </is>
+      </c>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="L901" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="M901" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="N901" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O901" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P901" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602131024/05eeb07e930575de7052ca5c1e67204e/notes_pre_post/1040g3k031plrl8shkg604a7r1e8cb33vjoa0er0!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q901" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R901" t="inlineStr">
+        <is>
+          <t>2025-12-04 20:21:34</t>
+        </is>
+      </c>
+      <c r="S901" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T901" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>69317648000000000d03c97e</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69317648000000000d03c97e?xsec_token=ABcGlVj7chOjAwiSxlL6IEsz5nbLe58SaSW_mPYZACPe8=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I902" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J902" t="inlineStr">
+        <is>
+          <t>1717</t>
+        </is>
+      </c>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="L902" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="M902" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="N902" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O902" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P902" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602131029/aa9435c3986f512e78ed0fa3e062e361/1040g2sg31plv0h8rkugg4a7r1e8cb33vavrehj8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q902" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R902" t="inlineStr">
+        <is>
+          <t>2025-12-04 19:53:44</t>
+        </is>
+      </c>
+      <c r="S902" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T902" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>693170fb000000000d0340ce</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693170fb000000000d0340ce?xsec_token=ABcGlVj7chOjAwiSxlL6IEswAlUbH08T-GCZk0q6rjgm0=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H903" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I903" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J903" t="inlineStr">
+        <is>
+          <t>1567</t>
+        </is>
+      </c>
+      <c r="K903" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="L903" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="M903" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N903" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O903" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P903" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602131034/e728754601291707ac5b3e97c3c41e4c/1040g2sg31plv0h8rkuh04a7r1e8cb33v7lp9fsg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q903" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R903" t="inlineStr">
+        <is>
+          <t>2025-12-04 19:31:07</t>
+        </is>
+      </c>
+      <c r="S903" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T903" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>69316ed7000000001b024fc5</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69316ed7000000001b024fc5?xsec_token=ABcGlVj7chOjAwiSxlL6IEs00OB538F3mzhkTsDkRCzL8=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I904" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J904" t="inlineStr">
+        <is>
+          <t>1593</t>
+        </is>
+      </c>
+      <c r="K904" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="L904" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="M904" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="N904" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O904" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P904" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602131039/90efdda98ea1e18a44edd96a4a78a6b7/110/0/01e9316ed625dd850010000000019ae9190038_0.jpg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q904" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R904" t="inlineStr">
+        <is>
+          <t>2025-12-04 19:21:59</t>
+        </is>
+      </c>
+      <c r="S904" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T904" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>69315f6c000000000d03571a</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69315f6c000000000d03571a?xsec_token=ABcGlVj7chOjAwiSxlL6IEs40YKHyLYOIh-sWq8pKjaP4=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>我好无语</t>
+        </is>
+      </c>
+      <c r="I905" t="inlineStr">
+        <is>
+          <t>屏蔽两个
+继续评论区问
+要不要低吸舞娘的朋友
+逻辑：实在是 任何内容不想看 也不想学
+就想留言 要代码
+#我的炒股日记[话题]# #我不能理解[话题]#</t>
+        </is>
+      </c>
+      <c r="J905" t="inlineStr">
+        <is>
+          <t>1487</t>
+        </is>
+      </c>
+      <c r="K905" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="L905" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="M905" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N905" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O905" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P905" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602131045/da7893c0442fd9193ebf54cda6e56880/1040g2sg31plmbcdt4mbg4a7r1e8cb33vov0q1co!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q905" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '我不能理解']</t>
+        </is>
+      </c>
+      <c r="R905" t="inlineStr">
+        <is>
+          <t>2025-12-04 18:16:12</t>
+        </is>
+      </c>
+      <c r="S905" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T905" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>69315350000000001b025e7f</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69315350000000001b025e7f?xsec_token=ABcGlVj7chOjAwiSxlL6IEs_mxOVaQceOO51BzHkuK1pE=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>✓一下好不好</t>
+        </is>
+      </c>
+      <c r="I906" t="inlineStr">
+        <is>
+          <t>像不像小招猫
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J906" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="K906" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="L906" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="M906" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N906" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O906" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P906" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602131050/3bdc6ee353ff426c19bd00fc2ee4de33/notes_pre_post/1040g3k031plrl8shkg6g4a7r1e8cb33vehirkl0!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q906" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R906" t="inlineStr">
+        <is>
+          <t>2025-12-04 17:24:32</t>
+        </is>
+      </c>
+      <c r="S906" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T906" t="inlineStr">
+        <is>
+          <t>图1: OCR超时/失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>69314bac000000000d03faae</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69314bac000000000d03faae?xsec_token=ABcGlVj7chOjAwiSxlL6IEs5OwczFhJswZoq1NTomDxZc=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I907" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J907" t="inlineStr">
+        <is>
+          <t>1561</t>
+        </is>
+      </c>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="L907" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="M907" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N907" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O907" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P907" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602131056/b8428e30f66a28aedd174cb533096e35/1040g2sg31plmbcdt4mcg4a7r1e8cb33vml5kjpg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q907" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R907" t="inlineStr">
+        <is>
+          <t>2025-12-04 16:51:56</t>
+        </is>
+      </c>
+      <c r="S907" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T907" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>69310e16000000001b024957</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69310e16000000001b024957?xsec_token=ABcGlVj7chOjAwiSxlL6IEsyGMhAILTipT82PiRGM9bOE=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>不是我不懂 我只是不愿意</t>
+        </is>
+      </c>
+      <c r="I908" t="inlineStr">
+        <is>
+          <t>看看图1 图2
+江西卖铜的 是不是[斜眼R] 是不是 [斜眼R]突了
+[捂嘴笑R][捂嘴笑R][捂嘴笑R]</t>
+        </is>
+      </c>
+      <c r="J908" t="inlineStr">
+        <is>
+          <t>1464</t>
+        </is>
+      </c>
+      <c r="K908" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="L908" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="M908" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N908" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O908" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P908" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602131101/e50b4186e58c4b7654b533a588bf464c/notes_pre_post/1040g3k831plf85shkm504a7r1e8cb33v6l4fv00!nd_dft_wlteh_jpg_3', 'http://sns-webpic-qc.xhscdn.com/202602131101/c5be732f6a6dbcc8a136b11d3c7528cd/notes_pre_post/1040g3k831plf85shkm3g4a7r1e8cb33vb3h6m90!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q908" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R908" t="inlineStr">
+        <is>
+          <t>2025-12-04 12:29:10</t>
+        </is>
+      </c>
+      <c r="S908" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T908" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过) | 图2: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
+++ b/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T908"/>
+  <dimension ref="A1:T909"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63156,6 +63156,113 @@
         </is>
       </c>
     </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>6930f987000000001b0255ef</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6930f987000000001b0255ef?xsec_token=ABBVGz7v6V8oWb_aiOUlfm_voQvZT89ftS8F7EzNLwkg4=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I909" t="inlineStr">
+        <is>
+          <t>我个人看法
+丑的
+时间 空间
+都需要休息了
+休息是为了更好的成长
+[斜眼R]再来次 周中 周下附近吧</t>
+        </is>
+      </c>
+      <c r="J909" t="inlineStr">
+        <is>
+          <t>1688</t>
+        </is>
+      </c>
+      <c r="K909" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="L909" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="M909" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N909" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O909" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P909" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602131106/1d1f8faf8732a628312b47f7f95abce7/1040g00831plck236kk0g4a7r1e8cb33vn5etkdo!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q909" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R909" t="inlineStr">
+        <is>
+          <t>2025-12-04 11:01:27</t>
+        </is>
+      </c>
+      <c r="S909" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T909" t="inlineStr">
+        <is>
+          <t>图1: 我个人看法, 丑的, 时间, 空间, 都需要休息了, 休息是为了更好的成长, 再来次周中周下附, 近吧</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
+++ b/datas/excel_datas/5b6150c56b58b741e26b8c7f.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T909"/>
+  <dimension ref="A1:T972"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63263,6 +63263,6597 @@
         </is>
       </c>
     </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>6932408a000000000d00cc13</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6932408a000000000d00cc13?xsec_token=AB_upEGaSMKcSsc59Jvl3yNq4_flELnSNLOWWk8nWappM=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>分享</t>
+        </is>
+      </c>
+      <c r="I910" t="inlineStr">
+        <is>
+          <t>我先说明 我绝对不会格局它
+但这个图 可以学习分享
+这是标准
+突 回踩
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J910" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="L910" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="M910" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N910" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O910" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P910" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602140935/1b4d40d4636cdc926359ca4c167682a6/notes_pre_post/1040g3k831pm4jrcol2bg4a7r1e8cb33v2ea1fhg!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q910" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R910" t="inlineStr">
+        <is>
+          <t>2025-12-05 10:16:42</t>
+        </is>
+      </c>
+      <c r="S910" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T910" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>6930f8da0000000019024fb7</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6930f8da0000000019024fb7?xsec_token=ABBVGz7v6V8oWb_aiOUlfm_jPCHZpXyQqxE4I2C9PytCI=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I911" t="inlineStr">
+        <is>
+          <t>小招猫[泪崩R]
+给我次周上吧
+ok bu ok ？</t>
+        </is>
+      </c>
+      <c r="J911" t="inlineStr">
+        <is>
+          <t>1513</t>
+        </is>
+      </c>
+      <c r="K911" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="L911" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="M911" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N911" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O911" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P911" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602140936/148b1af63483f224c802c30d64497958/1040g00831plck236kk404a7r1e8cb33vabplp00!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q911" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R911" t="inlineStr">
+        <is>
+          <t>2025-12-04 10:58:34</t>
+        </is>
+      </c>
+      <c r="S911" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T911" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>6930f1b0000000001b03105e</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6930f1b0000000001b03105e?xsec_token=ABBVGz7v6V8oWb_aiOUlfm_iKp9bP2FL58XpiYyXEgwck=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I912" t="inlineStr">
+        <is>
+          <t>[泪崩R][泪崩R][泪崩R][泪崩R]我太惨了……
+#云南白药[话题]#</t>
+        </is>
+      </c>
+      <c r="J912" t="inlineStr">
+        <is>
+          <t>1396</t>
+        </is>
+      </c>
+      <c r="K912" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="L912" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="M912" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N912" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O912" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P912" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602140941/a92aae821448e9a294f50feeeb2f365d/1040g00831plck236kk304a7r1e8cb33v7go8apo!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q912" t="inlineStr">
+        <is>
+          <t>['云南白药']</t>
+        </is>
+      </c>
+      <c r="R912" t="inlineStr">
+        <is>
+          <t>2025-12-04 10:28:00</t>
+        </is>
+      </c>
+      <c r="S912" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T912" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>6930eda9000000001b0339e5</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6930eda9000000001b0339e5?xsec_token=ABBVGz7v6V8oWb_aiOUlfm_piOE0M2Uudd3utB811vquI=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>又来吃苦了</t>
+        </is>
+      </c>
+      <c r="I913" t="inlineStr">
+        <is>
+          <t>我的牙医
+经常拿捏我的人哎
+我是一点办法都没
+#牙齿[话题]#</t>
+        </is>
+      </c>
+      <c r="J913" t="inlineStr">
+        <is>
+          <t>1356</t>
+        </is>
+      </c>
+      <c r="K913" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L913" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="M913" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N913" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O913" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P913" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602140946/315f0cc928f72259cae454984b920b42/notes_pre_post/1040g3k831plf85shkm5g4a7r1e8cb33vlof7omo!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q913" t="inlineStr">
+        <is>
+          <t>['牙齿']</t>
+        </is>
+      </c>
+      <c r="R913" t="inlineStr">
+        <is>
+          <t>2025-12-04 10:10:49</t>
+        </is>
+      </c>
+      <c r="S913" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T913" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>6930e658000000001b0314a0</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6930e658000000001b0314a0?xsec_token=ABBVGz7v6V8oWb_aiOUlfm_lNMa-aGug5scBMTQL4p8W4=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>信心</t>
+        </is>
+      </c>
+      <c r="I914" t="inlineStr">
+        <is>
+          <t>三哥也好
+牙膏也好
+不正再慢慢的
+周下吸里
+爬上来吗？
+月下吸需要资源
+周下吸 不就是需要耐心跟信心吗
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J914" t="inlineStr">
+        <is>
+          <t>1857</t>
+        </is>
+      </c>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="L914" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="M914" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N914" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O914" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P914" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602140948/9345adc39795d945e8169c6ed4938d0c/1040g00831plck236kk5g4a7r1e8cb33vb61nd40!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q914" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R914" t="inlineStr">
+        <is>
+          <t>2025-12-04 09:39:36</t>
+        </is>
+      </c>
+      <c r="S914" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T914" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>69305789000000000d036cf0</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69305789000000000d036cf0?xsec_token=ABBVGz7v6V8oWb_aiOUlfm_lDex1aoLSguE0PU-Wz3PqQ=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>这一刻稳稳的幸福</t>
+        </is>
+      </c>
+      <c r="I915" t="inlineStr">
+        <is>
+          <t>大冬天 家里一点都不冷
+小狗躺在狗窝里 四脚朝天的睡着
+这一刻的稳稳的幸福
+是国家给的
+能源充足  冬天 电力稳定  燃气稳定
+这是民生问题
+所以宇宙的尽头是科技？
+来 不用电 不用能源 不用银行贷款
+你来试试？
+#谁懂此刻的含金量[话题]# #此刻幸福具象化[话题]#</t>
+        </is>
+      </c>
+      <c r="J915" t="inlineStr">
+        <is>
+          <t>1789</t>
+        </is>
+      </c>
+      <c r="K915" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="L915" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="M915" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N915" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O915" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P915" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602140952/d07b81e78c2b065a1871283e36dfcd21/notes_pre_post/1040g3k031pkqui0e4g204a7r1e8cb33v2qp9mvg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q915" t="inlineStr">
+        <is>
+          <t>['谁懂此刻的含金量', '此刻幸福具象化']</t>
+        </is>
+      </c>
+      <c r="R915" t="inlineStr">
+        <is>
+          <t>2025-12-03 23:30:17</t>
+        </is>
+      </c>
+      <c r="S915" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T915" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>6930545f000000000d035f37</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6930545f000000000d035f37?xsec_token=ABBVGz7v6V8oWb_aiOUlfm_rDdMgEj0PfBmk60h83O1JQ=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I916" t="inlineStr">
+        <is>
+          <t>Y
+buy and hold
+[捂嘴笑R]
+我感觉 我学会了
+[斜眼R] #一起练口语[话题]#</t>
+        </is>
+      </c>
+      <c r="J916" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="K916" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L916" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="M916" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N916" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O916" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P916" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602140957/a338341b4d5bd7712010c45f9779359a/1040g00831pkpqeidkg1g4a7r1e8cb33vnd9skjg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q916" t="inlineStr">
+        <is>
+          <t>['一起练口语']</t>
+        </is>
+      </c>
+      <c r="R916" t="inlineStr">
+        <is>
+          <t>2025-12-03 23:16:48</t>
+        </is>
+      </c>
+      <c r="S916" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T916" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>6930505a000000000d00c453</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6930505a000000000d00c453?xsec_token=ABBVGz7v6V8oWb_aiOUlfm_qqGIf1hzC833Qdg9_NLKS4=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>一眼万年</t>
+        </is>
+      </c>
+      <c r="I917" t="inlineStr">
+        <is>
+          <t>很多图形
+我的脑海里一眼就万边了
+这是条件反射
+也是网络游戏的孰能生巧
+其实把这个当网游来看待
+每天没事就是 练 练 练
+你会打开新的世界
+投资
+天赋 努力 坚持 ＋…信息不对称
+一样都不能少[捂嘴笑R][斜眼R]
+buy and hold？
+瞎搞这是#一眼万年就是这样吧[话题]#</t>
+        </is>
+      </c>
+      <c r="J917" t="inlineStr">
+        <is>
+          <t>1671</t>
+        </is>
+      </c>
+      <c r="K917" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="L917" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="M917" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="N917" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O917" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P917" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141001/1ea7410302e6ea5957985884b25dd86a/notes_pre_post/1040g3k031pkrvd3vkk004a7r1e8cb33v53om900!nd_dft_wgth_webp_3', 'http://sns-webpic-qc.xhscdn.com/202602141001/acde2714c0ded9e62b7e8c1e3f79c17a/notes_pre_post/1040g3k031pkqui0e4g2g4a7r1e8cb33v2oj5bao!nd_dft_wgth_webp_3']</t>
+        </is>
+      </c>
+      <c r="Q917" t="inlineStr">
+        <is>
+          <t>['一眼万年就是这样吧']</t>
+        </is>
+      </c>
+      <c r="R917" t="inlineStr">
+        <is>
+          <t>2025-12-03 22:59:38</t>
+        </is>
+      </c>
+      <c r="S917" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T917" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过) | 图2: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>6930479b000000001b027b20</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/6930479b000000001b027b20?xsec_token=ABBVGz7v6V8oWb_aiOUlfm_jP6hRLocl4cgFGfIBxun-w=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>油 答 电</t>
+        </is>
+      </c>
+      <c r="I918" t="inlineStr">
+        <is>
+          <t>多看看噢 我只能帮到这里了
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J918" t="inlineStr">
+        <is>
+          <t>1583</t>
+        </is>
+      </c>
+      <c r="K918" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="L918" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="M918" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="N918" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O918" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P918" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141005/1fcff3387bf9c8da31d4a70840fa81d5/notes_pre_post/1040g3k031pkqui0e4g504a7r1e8cb33v2vghub0!nd_dft_wgth_jpg_3', 'http://sns-webpic-qc.xhscdn.com/202602141005/f7cfd44b2e0429371a39277bb75ea9fe/notes_pre_post/1040g3k031pkquvfo4u004a7r1e8cb33v3b0g9qg!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q918" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R918" t="inlineStr">
+        <is>
+          <t>2025-12-03 22:22:20</t>
+        </is>
+      </c>
+      <c r="S918" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T918" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过) | 图2: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>69303e1d000000000d03846d</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69303e1d000000000d03846d?xsec_token=ABBVGz7v6V8oWb_aiOUlfm_kFNMDsoTOJgUy1944ZdJPw=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I919" t="inlineStr">
+        <is>
+          <t>最最最后提醒一次
+月下吸白酒
+暂时停下</t>
+        </is>
+      </c>
+      <c r="J919" t="inlineStr">
+        <is>
+          <t>2126</t>
+        </is>
+      </c>
+      <c r="K919" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="L919" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="M919" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="N919" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O919" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P919" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141009/83920d36d74d0bb9672421258178529a/1040g00831pkpqeidkg5g4a7r1e8cb33v2sk32cg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q919" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R919" t="inlineStr">
+        <is>
+          <t>2025-12-03 21:41:49</t>
+        </is>
+      </c>
+      <c r="S919" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T919" t="inlineStr">
+        <is>
+          <t>图1: ”, 最最最后, 提醒一次, 月下吸白酒, 暂时停下</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>693019b6000000001b022fcf</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/693019b6000000001b022fcf?xsec_token=ABBVGz7v6V8oWb_aiOUlfm_qg6qnSvKMEXqoasceHezBA=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>珊瑚海</t>
+        </is>
+      </c>
+      <c r="I920" t="inlineStr">
+        <is>
+          <t>转身离开
+突破说不出来
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J920" t="inlineStr">
+        <is>
+          <t>1461</t>
+        </is>
+      </c>
+      <c r="K920" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="L920" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="M920" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="N920" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O920" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P920" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141014/866895b3b22d0f617f2b157c527dddcb/notes_pre_post/1040g3k831pkdcp2l4m504a7r1e8cb33v9f04co0!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q920" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R920" t="inlineStr">
+        <is>
+          <t>2025-12-03 19:06:30</t>
+        </is>
+      </c>
+      <c r="S920" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T920" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>69300ed6000000001b02665b</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69300ed6000000001b02665b?xsec_token=ABBVGz7v6V8oWb_aiOUlfm_hkV0f6y7gyHC-WIN2VRKpk=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I921" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J921" t="inlineStr">
+        <is>
+          <t>2546</t>
+        </is>
+      </c>
+      <c r="K921" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="L921" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="M921" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N921" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O921" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P921" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141019/fd8e6ade1651b937cab41b5e14085c2e/1040g00831pkjskjs4u104a7r1e8cb33vcboa8cg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q921" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R921" t="inlineStr">
+        <is>
+          <t>2025-12-03 18:20:07</t>
+        </is>
+      </c>
+      <c r="S921" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T921" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>69300ae7000000000d00ea87</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/69300ae7000000000d00ea87?xsec_token=ABBVGz7v6V8oWb_aiOUlfm_iDLZDHEUpj9yRRarz1d0z0=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I922" t="inlineStr">
+        <is>
+          <t>月下吸一定要有别人没有的资源才能月下吸
+首突回踩 人人公平
+悟了吗[斜眼R] #我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J922" t="inlineStr">
+        <is>
+          <t>1839</t>
+        </is>
+      </c>
+      <c r="K922" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="L922" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="M922" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="N922" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O922" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P922" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141023/0d233085ec90f14b2b106bce54df9098/1040g00831pk9bc424u004a7r1e8cb33vnk6q9j8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q922" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R922" t="inlineStr">
+        <is>
+          <t>2025-12-03 18:03:19</t>
+        </is>
+      </c>
+      <c r="S922" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T922" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>692ffd26000000000d03561f</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692ffd26000000000d03561f?xsec_token=ABJFcDPw4O_ln7cbpyQg20ZxTMjIY8CJLTCdpIoZDfnNA=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I923" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J923" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="K923" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="L923" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="M923" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="N923" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O923" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P923" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141027/1468fb199d50116917338a18c0e62ccf/1040g00831pk9bc424u2g4a7r1e8cb33vitgirno!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q923" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R923" t="inlineStr">
+        <is>
+          <t>2025-12-03 17:04:38</t>
+        </is>
+      </c>
+      <c r="S923" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T923" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>692ff36c000000000d03fea6</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692ff36c000000000d03fea6?xsec_token=ABJFcDPw4O_ln7cbpyQg20Z0YWPpwGBNJ1gW2SIBd6Lko=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>用电 回答 BYD</t>
+        </is>
+      </c>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>#我的炒股日记[话题]# #电力[话题]#</t>
+        </is>
+      </c>
+      <c r="J924" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="K924" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="L924" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="M924" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="N924" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O924" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P924" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141055/8a7c8b3124e80cffd370e322b68ba504/notes_pre_post/1040g3k831pkdcp2l4m104a7r1e8cb33v3jpn1bo!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q924" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '电力']</t>
+        </is>
+      </c>
+      <c r="R924" t="inlineStr">
+        <is>
+          <t>2025-12-03 16:23:08</t>
+        </is>
+      </c>
+      <c r="S924" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T924" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>692fe497000000001b02552a</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692fe497000000001b02552a?xsec_token=ABJFcDPw4O_ln7cbpyQg20Z5KRTwJEfi9hkbdqyXbUU7k=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>快乐</t>
+        </is>
+      </c>
+      <c r="I925" t="inlineStr">
+        <is>
+          <t>我很快乐
+因为我懂
+什么叫突 回  突 #快乐起来吧[话题]# #快乐是什么[话题]# #快乐是自找的[话题]# #让自己快乐[话题]# #快乐才是真谛[话题]# #开心快乐才是最重要的[话题]# #快乐最重要[话题]# #做个快乐的人[话题]# #其实快乐很简单[话题]#</t>
+        </is>
+      </c>
+      <c r="J925" t="inlineStr">
+        <is>
+          <t>1466</t>
+        </is>
+      </c>
+      <c r="K925" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="L925" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="M925" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="N925" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O925" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P925" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141059/4b0416224c59093bcf3bd7740d10c828/notes_pre_post/1040g3k831pkdcp2l4m6g4a7r1e8cb33v0afd1lo!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q925" t="inlineStr">
+        <is>
+          <t>['快乐起来吧', '快乐是什么', '快乐是自找的', '让自己快乐', '快乐才是真谛', '开心快乐才是最重要的', '快乐最重要', '做个快乐的人', '其实快乐很简单']</t>
+        </is>
+      </c>
+      <c r="R925" t="inlineStr">
+        <is>
+          <t>2025-12-03 15:19:51</t>
+        </is>
+      </c>
+      <c r="S925" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T925" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>692fd84e000000001b033656</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692fd84e000000001b033656?xsec_token=ABJFcDPw4O_ln7cbpyQg20ZznjyHZbuh-ZpmO8uEDaMSM=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>鼓掌</t>
+        </is>
+      </c>
+      <c r="I926" t="inlineStr">
+        <is>
+          <t>真会玩
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J926" t="inlineStr">
+        <is>
+          <t>1412</t>
+        </is>
+      </c>
+      <c r="K926" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="L926" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="M926" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N926" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O926" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P926" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141104/d9da714bc347a844a40e8c9f33eb7815/notes_pre_post/1040g3k831pkdcp2l4m604a7r1e8cb33vdnposv0!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q926" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R926" t="inlineStr">
+        <is>
+          <t>2025-12-03 14:27:26</t>
+        </is>
+      </c>
+      <c r="S926" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T926" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>692fd3e5000000000d00d281</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692fd3e5000000000d00d281?xsec_token=ABJFcDPw4O_ln7cbpyQg20Z-a7H11yZ-jfjTKHY30V29U=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I927" t="inlineStr">
+        <is>
+          <t>[泪崩R][泪崩R]苦啊#招商银行[话题]#</t>
+        </is>
+      </c>
+      <c r="J927" t="inlineStr">
+        <is>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="K927" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="L927" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="M927" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N927" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O927" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P927" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141108/fbb896369fdb86962119e2d7880dd61c/1040g00831pk9bc424u604a7r1e8cb33vfc8lip8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q927" t="inlineStr">
+        <is>
+          <t>['招商银行']</t>
+        </is>
+      </c>
+      <c r="R927" t="inlineStr">
+        <is>
+          <t>2025-12-03 14:08:37</t>
+        </is>
+      </c>
+      <c r="S927" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T927" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>692fc171000000000d039a53</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692fc171000000000d039a53?xsec_token=ABJFcDPw4O_ln7cbpyQg20Z0QZsOfhdoC49RYf8GuUHp0=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>有的时候 多想想是不是自己问题</t>
+        </is>
+      </c>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>短线英雄这本书
+你们看不懂
+是不是想想 不是书问题   是不是不够努力啊
+而是你自己问题
+我19年前看到这书 瞬间就成练气修士了
+就算不靠低波动红利策略  纯趋势
+我也能年化15％以上#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J928" t="inlineStr">
+        <is>
+          <t>1715</t>
+        </is>
+      </c>
+      <c r="K928" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="L928" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="M928" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N928" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O928" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P928" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141112/4c1d877f616fbaed119c8ba13e6519dd/1040g00831pk9bc424u5g4a7r1e8cb33v74ed0d8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q928" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R928" t="inlineStr">
+        <is>
+          <t>2025-12-03 12:49:53</t>
+        </is>
+      </c>
+      <c r="S928" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T928" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>692fb77a000000000d03f3e5</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692fb77a000000000d03f3e5?xsec_token=ABJFcDPw4O_ln7cbpyQg20Z-XzH_LoRqprw6ByR01O6Uw=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>不走</t>
+        </is>
+      </c>
+      <c r="I929" t="inlineStr">
+        <is>
+          <t>沉默
+完完全全把你放再心中
+有太多的话想对你说
+跌下来都说不出口
+#我的炒股日记[话题]# #没有撤退可言[话题]#</t>
+        </is>
+      </c>
+      <c r="J929" t="inlineStr">
+        <is>
+          <t>1479</t>
+        </is>
+      </c>
+      <c r="K929" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="L929" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="M929" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N929" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O929" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P929" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141117/0226e8cf12a8740982533518b4857d3b/notes_pre_post/1040g3k831pk66s37kmcg4a7r1e8cb33vrqpvr50!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q929" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '没有撤退可言']</t>
+        </is>
+      </c>
+      <c r="R929" t="inlineStr">
+        <is>
+          <t>2025-12-03 12:07:22</t>
+        </is>
+      </c>
+      <c r="S929" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T929" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>692faef1000000000d035c5e</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692faef1000000000d035c5e?xsec_token=ABJFcDPw4O_ln7cbpyQg20Z95qWJcB9Zf19M6N3bMz-lc=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>你不是善良 你是故意的</t>
+        </is>
+      </c>
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>刚屏蔽了一个 非常没有边界感 且以为自己情商很高的网友
+我呢 脾气是好 但下面乱带节奏 说是为了骗回复这种 一次可以 次次这样 就不是故意的了
+#我劝你善良[话题]#</t>
+        </is>
+      </c>
+      <c r="J930" t="inlineStr">
+        <is>
+          <t>1691</t>
+        </is>
+      </c>
+      <c r="K930" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="L930" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="M930" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N930" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O930" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P930" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141121/3e3726a7971f3439d90acb3e9eeef5a6/1040g00831pk3psktku104a7r1e8cb33vqm6uvfg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q930" t="inlineStr">
+        <is>
+          <t>['我劝你善良']</t>
+        </is>
+      </c>
+      <c r="R930" t="inlineStr">
+        <is>
+          <t>2025-12-03 11:30:57</t>
+        </is>
+      </c>
+      <c r="S930" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T930" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>692fa874000000000d03dd6c</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692fa874000000000d03dd6c?xsec_token=ABJFcDPw4O_ln7cbpyQg20ZwqccN0yic9tGUAT5Gg6uFA=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I931" t="inlineStr">
+        <is>
+          <t>嗖～
+丑的再格局掉一半
+[捂嘴笑R]</t>
+        </is>
+      </c>
+      <c r="J931" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="K931" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="L931" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="M931" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N931" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O931" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P931" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141125/e6ccea2c7242e15292ed727d75cd81e0/1040g00831pk3psktku4g4a7r1e8cb33vfis0sp0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q931" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R931" t="inlineStr">
+        <is>
+          <t>2025-12-03 11:03:16</t>
+        </is>
+      </c>
+      <c r="S931" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T931" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>692fa7e4000000001b021331</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692fa7e4000000001b021331?xsec_token=ABJFcDPw4O_ln7cbpyQg20Z38qXUrb25nTDrXL1zQJhwE=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I932" t="inlineStr">
+        <is>
+          <t>打错字个
+结果效果变了
+我意思
+长江电力已经是长江电力了 再说就没成就感了  既然好看科技
+那么我平替看好
+电  但我不看长江电力
+这样表达 简单了吧
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J932" t="inlineStr">
+        <is>
+          <t>1599</t>
+        </is>
+      </c>
+      <c r="K932" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="L932" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="M932" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N932" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O932" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P932" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141129/171b7689095bbc90cf4c996decca9dcf/1040g00831pk3psktku204a7r1e8cb33vj2nin98!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q932" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R932" t="inlineStr">
+        <is>
+          <t>2025-12-03 11:00:52</t>
+        </is>
+      </c>
+      <c r="S932" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T932" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>692f9d73000000001b02168e</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692f9d73000000001b02168e?xsec_token=ABJFcDPw4O_ln7cbpyQg20Z52mBgKGEODS1yeN_4ZcsWM=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>这个叫什么图形啊</t>
+        </is>
+      </c>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>只分享图形
+谁格局
+我阴阳她
+#我的炒股日记[话题]# #奇形怪状的[话题]#</t>
+        </is>
+      </c>
+      <c r="J933" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="K933" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="L933" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="M933" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="N933" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O933" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P933" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141133/31d2e81a78d93b98f5399d474fbe265b/notes_pre_post/1040g3k831pk66s37kmdg4a7r1e8cb33v415qijo!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q933" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '奇形怪状的']</t>
+        </is>
+      </c>
+      <c r="R933" t="inlineStr">
+        <is>
+          <t>2025-12-03 10:16:19</t>
+        </is>
+      </c>
+      <c r="S933" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T933" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>692f0c71000000001b021ee1</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692f0c71000000001b021ee1?xsec_token=ABJFcDPw4O_ln7cbpyQg20Z74ziAIO7SWg-11bTcZT7cM=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J934" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="K934" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="L934" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="M934" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="N934" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O934" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P934" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141516/58ad5a67a113c9e76a9bb9b1e0b9ef52/1040g00831pjapgcikm604a7r1e8cb33v00tja0g!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q934" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R934" t="inlineStr">
+        <is>
+          <t>2025-12-02 23:57:37</t>
+        </is>
+      </c>
+      <c r="S934" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T934" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>692ebcf7000000000d037fa3</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692ebcf7000000000d037fa3?xsec_token=ABhvGCLqwgEs1WDfHf-qzrE0CGuTQgX4dXOXe14tR7b8k=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>收益差 吃点安慰下自己</t>
+        </is>
+      </c>
+      <c r="I935" t="inlineStr">
+        <is>
+          <t>#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J935" t="inlineStr">
+        <is>
+          <t>1496</t>
+        </is>
+      </c>
+      <c r="K935" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L935" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="M935" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N935" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O935" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P935" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141524/e985be80c4d767554fb13ffb38c6ef15/notes_pre_post/1040g3k831pj7s5sf4g3g4a7r1e8cb33vr0mulao!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q935" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R935" t="inlineStr">
+        <is>
+          <t>2025-12-02 18:18:31</t>
+        </is>
+      </c>
+      <c r="S935" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T935" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>692ea4f3000000000d035b11</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692ea4f3000000000d035b11?xsec_token=ABhvGCLqwgEs1WDfHf-qzrE2CCLuN380LcBkWMJYtdcjM=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>苦啊</t>
+        </is>
+      </c>
+      <c r="I936" t="inlineStr">
+        <is>
+          <t>#好苦像生活一样[话题]#</t>
+        </is>
+      </c>
+      <c r="J936" t="inlineStr">
+        <is>
+          <t>1354</t>
+        </is>
+      </c>
+      <c r="K936" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="L936" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="M936" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N936" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O936" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P936" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141528/d8f1248b5ce99139469901fc09f4e250/notes_pre_post/1040g3k831pj7s5sf4g6g4a7r1e8cb33vuohjme8!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q936" t="inlineStr">
+        <is>
+          <t>['好苦像生活一样']</t>
+        </is>
+      </c>
+      <c r="R936" t="inlineStr">
+        <is>
+          <t>2025-12-02 16:36:03</t>
+        </is>
+      </c>
+      <c r="S936" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T936" t="inlineStr">
+        <is>
+          <t>图1: OCR超时/失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>692e9e80000000001b021141</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692e9e80000000001b021141?xsec_token=ABhvGCLqwgEs1WDfHf-qzrE69Wu9OkNNy3Ygn8KQAbcoE=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I937" t="inlineStr">
+        <is>
+          <t>货拉拉A
+香港小儿子
+表现还是可以的</t>
+        </is>
+      </c>
+      <c r="J937" t="inlineStr">
+        <is>
+          <t>1287</t>
+        </is>
+      </c>
+      <c r="K937" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="L937" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="M937" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N937" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O937" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P937" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141533/71b2bf63431cbd5299d14c5188c204b0/1040g2sg31pj49vi54og04a7r1e8cb33v7qhsss8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q937" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R937" t="inlineStr">
+        <is>
+          <t>2025-12-02 16:08:32</t>
+        </is>
+      </c>
+      <c r="S937" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T937" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>692e62a8000000001b027b45</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692e62a8000000001b027b45?xsec_token=ABhvGCLqwgEs1WDfHf-qzrE-CETSGRds_F78GKAgoa7NA=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>我期待</t>
+        </is>
+      </c>
+      <c r="I938" t="inlineStr">
+        <is>
+          <t>我期待  有一天 你会回来～
+#我在期待什么[话题]#</t>
+        </is>
+      </c>
+      <c r="J938" t="inlineStr">
+        <is>
+          <t>1468</t>
+        </is>
+      </c>
+      <c r="K938" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="L938" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="M938" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N938" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O938" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P938" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141537/70c3dd46ef462d9b838b302340e025cf/notes_pre_post/1040g3k031piuqho74o6g4a7r1e8cb33v0olu57o!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q938" t="inlineStr">
+        <is>
+          <t>['我在期待什么']</t>
+        </is>
+      </c>
+      <c r="R938" t="inlineStr">
+        <is>
+          <t>2025-12-02 11:53:12</t>
+        </is>
+      </c>
+      <c r="S938" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T938" t="inlineStr">
+        <is>
+          <t>图1: OCR超时/失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>692e5ace000000001b021627</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692e5ace000000001b021627?xsec_token=ABhvGCLqwgEs1WDfHf-qzrEySYuoQdm8G37IEcbSxfjl0=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>没那么简单</t>
+        </is>
+      </c>
+      <c r="I939" t="inlineStr">
+        <is>
+          <t>没那么简单
+就能找到
+聊的开的公司
+#其实很简单[话题]#</t>
+        </is>
+      </c>
+      <c r="J939" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="K939" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="L939" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="M939" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N939" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O939" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P939" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141542/366979603c70d0c7755b2c918546677f/notes_pre_post/1040g3k031piuqho74o5g4a7r1e8cb33va9ugcig!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q939" t="inlineStr">
+        <is>
+          <t>['其实很简单']</t>
+        </is>
+      </c>
+      <c r="R939" t="inlineStr">
+        <is>
+          <t>2025-12-02 11:19:42</t>
+        </is>
+      </c>
+      <c r="S939" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T939" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>692e54ce000000000d0352f8</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692e54ce000000000d0352f8?xsec_token=ABhvGCLqwgEs1WDfHf-qzrEwGHv7Hs0bFGIE7vnm3mW68=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I940" t="inlineStr">
+        <is>
+          <t>最怕自己被自己感动
+你又不是底部格局的小招猫 别人23   你43 你觉得
+你不是备胎是什么
+简单点 打野就打野
+滚动就滚动
+低格局 高格局掉
+不是基本常识嘛
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J940" t="inlineStr">
+        <is>
+          <t>1685</t>
+        </is>
+      </c>
+      <c r="K940" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="L940" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="M940" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N940" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O940" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P940" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141546/684ba6af01b210bc16ace7f22eb568bc/1040g00831piu33cp4k6g4a7r1e8cb33v1bl1uu8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q940" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R940" t="inlineStr">
+        <is>
+          <t>2025-12-02 10:54:06</t>
+        </is>
+      </c>
+      <c r="S940" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T940" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>692e50d30000000019024e92</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692e50d30000000019024e92?xsec_token=ABhvGCLqwgEs1WDfHf-qzrE_fr5hxs-GnYtJQkXRT6xWo=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>嗖～
+宽带H
+再格局掉一半啊哈哈哈</t>
+        </is>
+      </c>
+      <c r="J941" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="K941" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="L941" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="M941" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N941" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O941" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P941" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141550/2ac5eab64b80188d4f6f1540d26388f3/1040g00831pipdj0eko0g4a7r1e8cb33vhmk3800!nd_dft_wlteh_webp_3']</t>
+        </is>
+      </c>
+      <c r="Q941" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R941" t="inlineStr">
+        <is>
+          <t>2025-12-02 10:37:07</t>
+        </is>
+      </c>
+      <c r="S941" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T941" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>692e4fc0000000001b0212e1</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692e4fc0000000001b0212e1?xsec_token=ABhvGCLqwgEs1WDfHf-qzrE_nJiyTWiVWyosnPgU2WPQc=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I942" t="inlineStr">
+        <is>
+          <t>什么是慢慢牛
+就是
+有周上就会有周下
+而不像你想的这样
+一直上上上上上
+你懂了吗#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J942" t="inlineStr">
+        <is>
+          <t>1516</t>
+        </is>
+      </c>
+      <c r="K942" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="L942" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="M942" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N942" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O942" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P942" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141554/0d92371848e3a45c79792ce24fb023c0/1040g00831pipdj0eko5g4a7r1e8cb33vdqd9pu0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q942" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R942" t="inlineStr">
+        <is>
+          <t>2025-12-02 10:32:32</t>
+        </is>
+      </c>
+      <c r="S942" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T942" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>692e4b36000000000d00d02f</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692e4b36000000000d00d02f?xsec_token=ABhvGCLqwgEs1WDfHf-qzrE5kFxNmZ4ZEi3kWLo6H9rxY=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I943" t="inlineStr">
+        <is>
+          <t>三哥
+你再试盘吗[捂嘴笑R]
+#不断更挑战[话题]#</t>
+        </is>
+      </c>
+      <c r="J943" t="inlineStr">
+        <is>
+          <t>1442</t>
+        </is>
+      </c>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="L943" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="M943" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N943" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O943" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P943" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141558/1bd07f204431aa32393f1a0553697f4f/1040g00831pipdj0eko604a7r1e8cb33v5hnnd80!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q943" t="inlineStr">
+        <is>
+          <t>['不断更挑战']</t>
+        </is>
+      </c>
+      <c r="R943" t="inlineStr">
+        <is>
+          <t>2025-12-02 10:13:10</t>
+        </is>
+      </c>
+      <c r="S943" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T943" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>692e42e1000000001902437c</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692e42e1000000001902437c?xsec_token=ABhvGCLqwgEs1WDfHf-qzrE-OH2EWz2-BcTek-9yVFYpc=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I944" t="inlineStr">
+        <is>
+          <t>想对抗下市场
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J944" t="inlineStr">
+        <is>
+          <t>1379</t>
+        </is>
+      </c>
+      <c r="K944" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="L944" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="M944" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N944" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O944" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P944" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141602/27a64ad5660c9739e4afbd0a88029637/1040g00831pipdj0eko404a7r1e8cb33vce5kkhg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q944" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R944" t="inlineStr">
+        <is>
+          <t>2025-12-02 09:37:37</t>
+        </is>
+      </c>
+      <c r="S944" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T944" t="inlineStr">
+        <is>
+          <t>图1: 想对抗下市场</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>692e2ea1000000001b0209b2</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692e2ea1000000001b0209b2?xsec_token=ABhvGCLqwgEs1WDfHf-qzrE1aqXRLXEQp0YysqSdP7lf0=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I945" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J945" t="inlineStr">
+        <is>
+          <t>1980</t>
+        </is>
+      </c>
+      <c r="K945" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="L945" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="M945" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N945" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O945" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P945" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141607/32ae43166ca673581adeead3c32a76bb/1040g00831pipdj0eko6g4a7r1e8cb33va852eog!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q945" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R945" t="inlineStr">
+        <is>
+          <t>2025-12-02 08:11:13</t>
+        </is>
+      </c>
+      <c r="S945" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T945" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>692da8d5000000001b026602</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692da8d5000000001b026602?xsec_token=ABUXy5YowPZEtj1VuknYwQh6csOxEWfXAZzCrjKKdeXSo=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J946" t="inlineStr">
+        <is>
+          <t>1967</t>
+        </is>
+      </c>
+      <c r="K946" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="L946" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="M946" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N946" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O946" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P946" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141611/bd934956465e475304ed162383c78bc0/1040g00831pi319r3kk004a7r1e8cb33vrcul248!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q946" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R946" t="inlineStr">
+        <is>
+          <t>2025-12-01 22:40:21</t>
+        </is>
+      </c>
+      <c r="S946" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T946" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>692da565000000000d039415</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692da565000000000d039415?xsec_token=ABUXy5YowPZEtj1VuknYwQh8d_w7rc8qoU9_gECg8n3AU=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>are you ok？？？</t>
+        </is>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>#啥也不说了[话题]#</t>
+        </is>
+      </c>
+      <c r="J947" t="inlineStr">
+        <is>
+          <t>1329</t>
+        </is>
+      </c>
+      <c r="K947" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="L947" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="M947" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N947" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O947" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P947" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141615/4d50bf0fdefae1465ea1d45ede4343a9/notes_pre_post/1040g3k031phsf1vhkk304a7r1e8cb33v6huuj4g!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q947" t="inlineStr">
+        <is>
+          <t>['啥也不说了']</t>
+        </is>
+      </c>
+      <c r="R947" t="inlineStr">
+        <is>
+          <t>2025-12-01 22:25:41</t>
+        </is>
+      </c>
+      <c r="S947" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T947" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>692d9378000000000d03a936</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692d9378000000000d03a936?xsec_token=ABUXy5YowPZEtj1VuknYwQhwm7VP8HMUJ_weOq8benl4Q=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>无条件～</t>
+        </is>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>分享图形#都做金融明白人[话题]#</t>
+        </is>
+      </c>
+      <c r="J948" t="inlineStr">
+        <is>
+          <t>1812</t>
+        </is>
+      </c>
+      <c r="K948" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="L948" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="M948" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="N948" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O948" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P948" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141619/70007c570795669c8d53a2a347ec673d/notes_pre_post/1040g3k031phsf1vhkk004a7r1e8cb33vg4kk188!nd_dft_wgth_jpg_3', 'http://sns-webpic-qc.xhscdn.com/202602141619/b16dc180c4a8220c4b67f8f4015d9dce/notes_pre_post/1040g3k031phsf1vhkk3g4a7r1e8cb33vha7ghr0!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q948" t="inlineStr">
+        <is>
+          <t>['都做金融明白人']</t>
+        </is>
+      </c>
+      <c r="R948" t="inlineStr">
+        <is>
+          <t>2025-12-01 21:09:12</t>
+        </is>
+      </c>
+      <c r="S948" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T948" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过) | 图2: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>692d8b2c000000000d03b687</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692d8b2c000000000d03b687?xsec_token=ABUXy5YowPZEtj1VuknYwQhzufsc8ZVfkQ2oVlm-YjYhQ=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>为什么我眼里看出来的移不动A 跟你们再哪里叫的不动 不送 完全不同
+我看出来的 是机会啊[黑薯问号R] #不懂就问系列[话题]#</t>
+        </is>
+      </c>
+      <c r="J949" t="inlineStr">
+        <is>
+          <t>1471</t>
+        </is>
+      </c>
+      <c r="K949" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="L949" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="M949" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N949" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O949" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P949" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141623/291729c0ac62c38ce573a286137313b1/1040g00831pi319r3kk304a7r1e8cb33v6d92jl8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q949" t="inlineStr">
+        <is>
+          <t>['不懂就问系列']</t>
+        </is>
+      </c>
+      <c r="R949" t="inlineStr">
+        <is>
+          <t>2025-12-01 20:33:48</t>
+        </is>
+      </c>
+      <c r="S949" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T949" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>692d8784000000001b025f85</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692d8784000000001b025f85?xsec_token=ABUXy5YowPZEtj1VuknYwQh0uUurwXt1ttdXfw1piwLGU=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>一定要努力啊大家！！！！</t>
+        </is>
+      </c>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J950" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="K950" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="L950" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="M950" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N950" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O950" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P950" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141627/233b1630684e6c7b7c10d371c55c4fa4/1040g00831pi319r3kk4g4a7r1e8cb33v9qi20ng!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q950" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R950" t="inlineStr">
+        <is>
+          <t>2025-12-01 20:18:12</t>
+        </is>
+      </c>
+      <c r="S950" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T950" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>692d78b8000000001b02466e</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692d78b8000000001b02466e?xsec_token=ABUXy5YowPZEtj1VuknYwQh4UCCveQGlAckkZ9x84DMrI=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>周下😯</t>
+        </is>
+      </c>
+      <c r="I951" t="inlineStr">
+        <is>
+          <t>时间上 空间上
+刚看了下牙膏
+感觉还有2周
+就跟我上两周说海上货拉拉A一样
+空间 时间 马上快到了
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J951" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="K951" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="L951" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="M951" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="N951" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O951" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P951" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141631/c082bb0b7c5ebcaff53103fb34c8df3e/1040g00831pi319r3kk604a7r1e8cb33vj6hdgvg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q951" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R951" t="inlineStr">
+        <is>
+          <t>2025-12-01 19:15:04</t>
+        </is>
+      </c>
+      <c r="S951" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T951" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>692d7280000000001b030924</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692d7280000000001b030924?xsec_token=ABUXy5YowPZEtj1VuknYwQhwMuYpuogpBMh49cCxRzS4M=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>猫抬头</t>
+        </is>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>如果我是TVB招猫  该多好  哎
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J952" t="inlineStr">
+        <is>
+          <t>1391</t>
+        </is>
+      </c>
+      <c r="K952" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="L952" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="M952" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N952" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O952" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P952" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141635/27562c7d6009218335de89afc00b4f8e/notes_pre_post/1040g3k031phsf1vhkk404a7r1e8cb33vmgpvhvo!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q952" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R952" t="inlineStr">
+        <is>
+          <t>2025-12-01 18:48:32</t>
+        </is>
+      </c>
+      <c r="S952" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T952" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>692d53af000000000d0397c6</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692d53af000000000d0397c6?xsec_token=ABUXy5YowPZEtj1VuknYwQh3uhrLZrP7-Qhm87jSB5eQE=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J953" t="inlineStr">
+        <is>
+          <t>1894</t>
+        </is>
+      </c>
+      <c r="K953" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="L953" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="M953" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N953" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O953" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P953" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141639/2f75e16e7c5fd22b0eef2a385cf946d8/1040g00831phoqpbv2s0g4a7r1e8cb33vq55kfb8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q953" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R953" t="inlineStr">
+        <is>
+          <t>2025-12-01 16:37:03</t>
+        </is>
+      </c>
+      <c r="S953" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T953" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>692d5333000000001902511f</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692d5333000000001902511f?xsec_token=ABUXy5YowPZEtj1VuknYwQh6e6IGKzy75S8MKWsaQAFn0=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I954" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J954" t="inlineStr">
+        <is>
+          <t>1586</t>
+        </is>
+      </c>
+      <c r="K954" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="L954" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="M954" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N954" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O954" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P954" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141643/a51527caeadf6c1721d586965d4012db/1040g00831phoqpbv2s104a7r1e8cb33vi21tnro!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q954" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R954" t="inlineStr">
+        <is>
+          <t>2025-12-01 16:34:59</t>
+        </is>
+      </c>
+      <c r="S954" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T954" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>692d4ef1000000000d00db38</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692d4ef1000000000d00db38?xsec_token=ABUXy5YowPZEtj1VuknYwQh7q50cbW3x_dGvUuBL83Els=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>收益差 只能吃叠饭了哎</t>
+        </is>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>[泪崩R]哎  我这是中午饭 忙到现在才吃中午饭
+#云南白药[话题]#</t>
+        </is>
+      </c>
+      <c r="J955" t="inlineStr">
+        <is>
+          <t>1329</t>
+        </is>
+      </c>
+      <c r="K955" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="L955" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="M955" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N955" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O955" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P955" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141646/4ac4ca9755230cba74a3e22a7539fac7/notes_pre_post/1040g3k031phsf1vhkk4g4a7r1e8cb33vk9ngs90!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q955" t="inlineStr">
+        <is>
+          <t>['云南白药']</t>
+        </is>
+      </c>
+      <c r="R955" t="inlineStr">
+        <is>
+          <t>2025-12-01 16:16:49</t>
+        </is>
+      </c>
+      <c r="S955" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T955" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>692d4158000000001b023072</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692d4158000000001b023072?xsec_token=ABUXy5YowPZEtj1VuknYwQh8RcHhoA02FTudFn9r-toZw=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>等待</t>
+        </is>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>我随时随地再等待
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J956" t="inlineStr">
+        <is>
+          <t>1439</t>
+        </is>
+      </c>
+      <c r="K956" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="L956" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="M956" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N956" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O956" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P956" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141650/8b178435bd52ca741d2508df49a4b075/notes_pre_post/1040g3k031phsf1vhkk6g4a7r1e8cb33vdlhkt38!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q956" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R956" t="inlineStr">
+        <is>
+          <t>2025-12-01 15:18:48</t>
+        </is>
+      </c>
+      <c r="S956" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T956" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>692d3bd6000000000d00e8f9</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692d3bd6000000000d00e8f9?xsec_token=ABUXy5YowPZEtj1VuknYwQh7phwG0Wi4pqiYuwsd5NVSY=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>稳住 好好过年</t>
+        </is>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>控制
+仙境仓
+别忘记噢
+低调  稳扎稳打
+尽量周下  滚动起来就好了
+切记  NO 周上
+NO buy and hold周上
+勇敢  buy and 滚动 周下
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J957" t="inlineStr">
+        <is>
+          <t>2067</t>
+        </is>
+      </c>
+      <c r="K957" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="L957" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="M957" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="N957" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O957" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P957" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141654/a539883c8ca10896722f64ce84fc28f4/1040g00831phoqpbv2s1g4a7r1e8cb33vcvlni08!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q957" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R957" t="inlineStr">
+        <is>
+          <t>2025-12-01 14:55:18</t>
+        </is>
+      </c>
+      <c r="S957" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T957" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>692d239a000000000d03cfc9</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692d239a000000000d03cfc9?xsec_token=ABUXy5YowPZEtj1VuknYwQh_aezNlrxT1ERxjX3ZzQrY8=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>逻辑</t>
+        </is>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>N代通讯
+出海产品
+怎么出海 等待兑现
+大金融 等待
+基础消费 我有信心</t>
+        </is>
+      </c>
+      <c r="J958" t="inlineStr">
+        <is>
+          <t>1536</t>
+        </is>
+      </c>
+      <c r="K958" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="L958" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="M958" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N958" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O958" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P958" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141658/2f05c839b21ede10f6ec8fac03f76633/1040g00831phoqpbv2s6g4a7r1e8cb33v7j5jajg!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q958" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R958" t="inlineStr">
+        <is>
+          <t>2025-12-01 13:11:54</t>
+        </is>
+      </c>
+      <c r="S958" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T958" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>692d04f0000000000d034c70</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692d04f0000000000d034c70?xsec_token=ABUXy5YowPZEtj1VuknYwQh6wRkbhhYF0egXF8kn6Emdo=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>28～</t>
+        </is>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J959" t="inlineStr">
+        <is>
+          <t>1527</t>
+        </is>
+      </c>
+      <c r="K959" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="L959" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="M959" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N959" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O959" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P959" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141703/59c75fb20d47bca7f6b08d949a9a3c27/notes_pre_post/1040g3k831phjt9vsiocg4a7r1e8cb33vo103eso!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q959" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R959" t="inlineStr">
+        <is>
+          <t>2025-12-01 11:01:04</t>
+        </is>
+      </c>
+      <c r="S959" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T959" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>692d01a6000000000d00f178</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692d01a6000000000d00f178?xsec_token=ABUXy5YowPZEtj1VuknYwQhx9GgcIpBDhlimYSRu0t0ws=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>不冒险</t>
+        </is>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>N代通讯 我很早就说了龙头是谁
+但还是坚持观点
+我不碰
+我极限 N代通讯 就是宽带H了
+投资 要稳</t>
+        </is>
+      </c>
+      <c r="J960" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="K960" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="L960" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="M960" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N960" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O960" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P960" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141707/1bea40ed6bb7e2d80ad105c54d7d401e/1040g2sg31phhsboo3cg04a7r1e8cb33vrvmhafg!nd_dft_wlteh_webp_3']</t>
+        </is>
+      </c>
+      <c r="Q960" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R960" t="inlineStr">
+        <is>
+          <t>2025-12-01 10:47:02</t>
+        </is>
+      </c>
+      <c r="S960" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T960" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>692cfb42000000000d00ce41</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692cfb42000000000d00ce41?xsec_token=ABPYGbP4-zvVuXLr2QqKpT82dharJazYELBhG_zzjfIzI=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>这次或许不一样 或许吧</t>
+        </is>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>希望5突120
+#我的炒股日记[话题]# #不出意外的话[话题]#</t>
+        </is>
+      </c>
+      <c r="J961" t="inlineStr">
+        <is>
+          <t>1362</t>
+        </is>
+      </c>
+      <c r="K961" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="L961" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="M961" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N961" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O961" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P961" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141711/e7dd8c2c9ff9635de54afafba6bad957/notes_pre_post/1040g3k831phjt9vsiodg4a7r1e8cb33vp6o94jg!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q961" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '不出意外的话']</t>
+        </is>
+      </c>
+      <c r="R961" t="inlineStr">
+        <is>
+          <t>2025-12-01 10:19:46</t>
+        </is>
+      </c>
+      <c r="S961" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T961" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>692cfad3000000001b02333e</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692cfad3000000001b02333e?xsec_token=ABPYGbP4-zvVuXLr2QqKpT85ne8OzOit6ZRCeVu8_JNi4=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>牙膏 看样子想对抗下市场
+蛮好 蛮好#牙膏[话题]# #口腔[话题]# #自己的品牌或者其他话题[话题]# #有想法轻松发[话题]# #含氟牙膏[话题]# #有想法随心发[话题]# #守护脆弱口腔[话题]# #牙科[话题]# #美白牙膏[话题]# #保护牙齿[话题]#</t>
+        </is>
+      </c>
+      <c r="J962" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="K962" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="L962" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="M962" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N962" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O962" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P962" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141715/6743c25b8183ac2e95cf710fb4ebc380/1040g2sg31phhsboo3ci04a7r1e8cb33vooqluu8!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q962" t="inlineStr">
+        <is>
+          <t>['牙膏', '口腔', '自己的品牌或者其他话题', '有想法轻松发', '含氟牙膏', '有想法随心发', '守护脆弱口腔', '牙科', '美白牙膏', '保护牙齿']</t>
+        </is>
+      </c>
+      <c r="R962" t="inlineStr">
+        <is>
+          <t>2025-12-01 10:17:55</t>
+        </is>
+      </c>
+      <c r="S962" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T962" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>692cf2eb0000000019027db9</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692cf2eb0000000019027db9?xsec_token=ABPYGbP4-zvVuXLr2QqKpT88ewBFcR0LHm8Nk5yhg5uqk=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>大金融三兄弟
+老大 老二休息
+三哥[黑薯问号R]今天不知道表现会如何#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J963" t="inlineStr">
+        <is>
+          <t>1423</t>
+        </is>
+      </c>
+      <c r="K963" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="L963" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="M963" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N963" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O963" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P963" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141719/b728aa26a17ff5cf8945be923a0d1a71/1040g2sg31phhsboo3cig4a7r1e8cb33vdk4ql8g!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q963" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R963" t="inlineStr">
+        <is>
+          <t>2025-12-01 09:44:11</t>
+        </is>
+      </c>
+      <c r="S963" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T963" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>692ceaa3000000000d03a104</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692ceaa3000000000d03a104?xsec_token=ABPYGbP4-zvVuXLr2QqKpT81EjHobnywX1dWeWsZjFb64=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>这次是慢牛
+到了周上
+总有机会周中 周下
+切记不追
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J964" t="inlineStr">
+        <is>
+          <t>1801</t>
+        </is>
+      </c>
+      <c r="K964" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="L964" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="M964" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N964" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O964" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P964" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141723/a5adb7c97a302dcaa93864143ff98746/1040g2sg31phhsboo3ckg4a7r1e8cb33vfa5ai8g!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q964" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R964" t="inlineStr">
+        <is>
+          <t>2025-12-01 09:08:51</t>
+        </is>
+      </c>
+      <c r="S964" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T964" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>692c58b2000000001b033db6</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692c58b2000000001b033db6?xsec_token=ABPYGbP4-zvVuXLr2QqKpT81ispSMMqdOVZTa90GHWr30=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>momo厉飞雨</t>
+        </is>
+      </c>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>十年后
+坚持低波动红利策略的
+一定会感谢
+今年的自己啊哈哈哈哈哈哈哈
+念头通达吧
+道友们
+momo厉飞雨
+发于： 2025年11月30号
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J965" t="inlineStr">
+        <is>
+          <t>2802</t>
+        </is>
+      </c>
+      <c r="K965" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="L965" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="M965" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="N965" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O965" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P965" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141727/3bcae7299b6a25d9ced7b0adc04f36d6/1040g00831pgl367aig204a7r1e8cb33v9cm7dlo!nd_dft_wlteh_webp_3']</t>
+        </is>
+      </c>
+      <c r="Q965" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R965" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:46:10</t>
+        </is>
+      </c>
+      <c r="S965" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T965" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>692c24b7000000000d0342e6</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692c24b7000000000d0342e6?xsec_token=ABPYGbP4-zvVuXLr2QqKpT80sxkNGhvJNN414a5EDrapo=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>10年</t>
+        </is>
+      </c>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>家人们
+再投资的路上再坚持十年低波动红利策略
+你们一定也可以的
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J966" t="inlineStr">
+        <is>
+          <t>2866</t>
+        </is>
+      </c>
+      <c r="K966" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="L966" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="M966" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="N966" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O966" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P966" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141731/0446180bd6e69acb35d72eb75f1aa003/notes_pre_post/1040g3k031pglbkk4iu5g4a7r1e8cb33vivs7el8!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q966" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R966" t="inlineStr">
+        <is>
+          <t>2025-11-30 19:04:23</t>
+        </is>
+      </c>
+      <c r="S966" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T966" t="inlineStr">
+        <is>
+          <t>图1: OCR超时/失败</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>692bd61b000000001b032346</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692bd61b000000001b032346?xsec_token=AB15gGx3E2ewIv2ajDFDpGES9ipzGbqarT1mbSP_ypa3Y=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>不理解</t>
+        </is>
+      </c>
+      <c r="I967" t="inlineStr">
+        <is>
+          <t>没什么股息
+没突
+那么困境反转？
+又不是基础消费
+博什么？
+期待什么？
+48杯PE？
+难道格局 就为了猜？
+#我不能理解[话题]#</t>
+        </is>
+      </c>
+      <c r="J967" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="K967" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="L967" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="M967" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N967" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O967" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P967" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141736/9c2415747fdb3e9a9fa795b033f6193b/notes_pre_post/1040g3k831pgahioe2cag5q6h4ijollefgopvn88!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q967" t="inlineStr">
+        <is>
+          <t>['我不能理解']</t>
+        </is>
+      </c>
+      <c r="R967" t="inlineStr">
+        <is>
+          <t>2025-11-30 13:28:59</t>
+        </is>
+      </c>
+      <c r="S967" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T967" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>692bc67b000000001b030bb7</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692bc67b000000001b030bb7?xsec_token=AB15gGx3E2ewIv2ajDFDpGEc5BtizJkwuZgyBXx-kkFDw=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>纯分享</t>
+        </is>
+      </c>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>这个谁格局
+我肯定阴阳他！！！！！
+而且我不会碰
+但可以 可以 可以 拿来  去思考BYD呀
+#我的炒股日记[话题]# #单纯分享看看就好[话题]# #希望对大家有帮助[话题]# #分享给大家[话题]# #话不多说明白就好[话题]# #分享是一种快乐[话题]# #其实很简单[话题]# #懂的自然懂[话题]# #知道的人越多越好[话题]# #随便分享真是件好事[话题]#</t>
+        </is>
+      </c>
+      <c r="J968" t="inlineStr">
+        <is>
+          <t>1238</t>
+        </is>
+      </c>
+      <c r="K968" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="L968" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="M968" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N968" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O968" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P968" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141740/4dedeb6d0fd95b052cbc5120639b2e57/notes_pre_post/1040g3k831pgahioe2cbg5q6h4ijollefjbh5eio!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q968" t="inlineStr">
+        <is>
+          <t>['我的炒股日记', '单纯分享看看就好', '希望对大家有帮助', '分享给大家', '话不多说明白就好', '分享是一种快乐', '其实很简单', '懂的自然懂', '知道的人越多越好', '随便分享真是件好事']</t>
+        </is>
+      </c>
+      <c r="R968" t="inlineStr">
+        <is>
+          <t>2025-11-30 12:22:19</t>
+        </is>
+      </c>
+      <c r="S968" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T968" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>692ba9ef000000000d00e26e</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692ba9ef000000000d00e26e?xsec_token=AB15gGx3E2ewIv2ajDFDpGEZ4sjGzs0P3X2NJv4gtPGi0=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>BYD解锁BYD</t>
+        </is>
+      </c>
+      <c r="I969" t="inlineStr">
+        <is>
+          <t>家人们 悟了吗
+两张图一起看
+是不是就不焦虑了
+是不是现在可以休息了
+是不是耐心等待就好了
+#我的炒股日记[话题]#</t>
+        </is>
+      </c>
+      <c r="J969" t="inlineStr">
+        <is>
+          <t>1695</t>
+        </is>
+      </c>
+      <c r="K969" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="L969" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="M969" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="N969" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O969" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P969" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141746/ae883d4d27e2688cc29f990e68211a40/notes_pre_post/1040g3k831pgahioe2ca05q6h4ijollefsrc1kho!nd_dft_wgth_jpg_3', 'http://sns-webpic-qc.xhscdn.com/202602141746/aea2a26944958a6eed75b484b3823a8f/notes_pre_post/1040g3k831pgamdqujc004a7r1e8cb33v46p2qf8!nd_dft_wgth_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q969" t="inlineStr">
+        <is>
+          <t>['我的炒股日记']</t>
+        </is>
+      </c>
+      <c r="R969" t="inlineStr">
+        <is>
+          <t>2025-11-30 10:20:31</t>
+        </is>
+      </c>
+      <c r="S969" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T969" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过) | 图2: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>692ba372000000001b030563</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692ba372000000001b030563?xsec_token=AB15gGx3E2ewIv2ajDFDpGEctfyvTywXeti4X218T6x44=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>#在小红书随手拍[话题]#</t>
+        </is>
+      </c>
+      <c r="J970" t="inlineStr">
+        <is>
+          <t>1518</t>
+        </is>
+      </c>
+      <c r="K970" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="L970" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="M970" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N970" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O970" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P970" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141750/af8fbc95dab3c46fbb6c7a37292f1c2e/1040g2sg31pg92rfviuj04a7r1e8cb33vq3l6u78!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q970" t="inlineStr">
+        <is>
+          <t>['在小红书随手拍']</t>
+        </is>
+      </c>
+      <c r="R970" t="inlineStr">
+        <is>
+          <t>2025-11-30 09:52:50</t>
+        </is>
+      </c>
+      <c r="S970" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T970" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>692b9ca1000000000d0368cc</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692b9ca1000000000d0368cc?xsec_token=AB15gGx3E2ewIv2ajDFDpGEdO8P2knf9kJg2Y98Vv8SdE=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>如何再次避雷</t>
+        </is>
+      </c>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>逆逻辑 就是因为财经博主钱太好赚
+某某星球 文章收费
+动不动一次几十万 上百万  所以没人愿意认认真真研究投资 善于提示
+以后再付金币钱 坚持让它先晒实盘 不管下面课代表再如何三推三就 烘托气氛 都要这样 不然不付
+如果这样  大概率 你能避雷 啊哈哈哈哈哈哈哈
+#纯粹个人想法吐槽[话题]#</t>
+        </is>
+      </c>
+      <c r="J971" t="inlineStr">
+        <is>
+          <t>1755</t>
+        </is>
+      </c>
+      <c r="K971" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="L971" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="M971" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N971" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O971" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P971" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141754/ffd41782a380037e8501684263006859/1040g2sg31pg92rfviukg4a7r1e8cb33vcs5pba0!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q971" t="inlineStr">
+        <is>
+          <t>['纯粹个人想法吐槽']</t>
+        </is>
+      </c>
+      <c r="R971" t="inlineStr">
+        <is>
+          <t>2025-11-30 09:23:45</t>
+        </is>
+      </c>
+      <c r="S971" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T971" t="inlineStr">
+        <is>
+          <t>图1: 逆逻辑, 就是因为财经博主, 钱太好赚, 某某星球, 文章收费, 动不动一次几十万, 上百万, 所以没人愿意认认真真研, 究投资善于提示, 以后再付金币钱, 我坚持让它, 先晒实盘不管下面课代表, 再如何三推三就烘托气氛, 都要这样不然不付</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>692b0ef9000000000d0386fc</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/explore/692b0ef9000000000d0386fc?xsec_token=AB15gGx3E2ewIv2ajDFDpGEeg21KHI3UPOid7Fya4hf4Y=&amp;xsec_source=pc_user</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>图集</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>https://www.xiaohongshu.com/user/profile/5b6150c56b58b741e26b8c7f</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>还是叫吴富贵吧</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>https://sns-avatar-qc.xhscdn.com/avatar/1040g2jo31g9vkplp2s6g4a7r1e8cb33vdvgmpr0</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>无标题</t>
+        </is>
+      </c>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>移动被调出A50
+影响你每年4.5％左右股息吗？</t>
+        </is>
+      </c>
+      <c r="J972" t="inlineStr">
+        <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="K972" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="L972" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="M972" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N972" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O972" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P972" t="inlineStr">
+        <is>
+          <t>['http://sns-webpic-qc.xhscdn.com/202602141759/a5861ce57f2085946567bd67b1ab2f1f/1040g00831pfhqqeuio004a7r1e8cb33v9hlud08!nd_dft_wlteh_jpg_3']</t>
+        </is>
+      </c>
+      <c r="Q972" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R972" t="inlineStr">
+        <is>
+          <t>2025-11-29 23:19:21</t>
+        </is>
+      </c>
+      <c r="S972" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="T972" t="inlineStr">
+        <is>
+          <t>图1: 非文字图(跳过)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
